--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="354">
   <si>
     <t>Component list</t>
   </si>
@@ -360,9 +360,6 @@
     <t>RES SMD 4.7K OHM 5% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES 5.6 OHM 1% 1/8W 0805</t>
-  </si>
-  <si>
     <t>RES 22 OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -483,9 +480,6 @@
     <t>Res-0603</t>
   </si>
   <si>
-    <t>RES-0805</t>
-  </si>
-  <si>
     <t>Solder Bridge</t>
   </si>
   <si>
@@ -618,9 +612,6 @@
     <t>RC0603JR-074K7L</t>
   </si>
   <si>
-    <t>RC0805FR-075R6L</t>
-  </si>
-  <si>
     <t>RC0603FR-0722RL</t>
   </si>
   <si>
@@ -795,9 +786,6 @@
     <t>C277476</t>
   </si>
   <si>
-    <t>C441758</t>
-  </si>
-  <si>
     <t>C326057</t>
   </si>
   <si>
@@ -861,9 +849,6 @@
     <t>C105428</t>
   </si>
   <si>
-    <t>C275644</t>
-  </si>
-  <si>
     <t>C107701</t>
   </si>
   <si>
@@ -1074,7 +1059,28 @@
     <t>C1, C41, C43</t>
   </si>
   <si>
-    <t>R1, R6, R7, R8, R9, R10, R13, R14, R15, R31, R32</t>
+    <t>C0105C0G330J250NTZ</t>
+  </si>
+  <si>
+    <t>C881842</t>
+  </si>
+  <si>
+    <t>C15651</t>
+  </si>
+  <si>
+    <t>R1, R6, R7, R8, R10, R13, R14, R15, R31, R32</t>
+  </si>
+  <si>
+    <t>RES-1206</t>
+  </si>
+  <si>
+    <t>RC1206FR-7W5R6L</t>
+  </si>
+  <si>
+    <t>C137211</t>
+  </si>
+  <si>
+    <t>General Purpose Chip Resistor Thick Film 1206 5.6Ohm 1% Paper T/R</t>
   </si>
 </sst>
 </file>
@@ -1671,6 +1677,68 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1682,6 +1750,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1696,74 +1770,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2141,15 +2147,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="51"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2160,7 +2166,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="46" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2185,7 +2191,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="47" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2199,7 +2205,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="52"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2210,7 +2216,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="47" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2224,7 +2230,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="53"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2249,7 +2255,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="53"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2270,7 +2276,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="53"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2291,7 +2297,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="53"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2312,7 +2318,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="53"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2329,46 +2335,46 @@
         <v>79</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>339</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>340</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2377,32 +2383,32 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -2414,8 +2420,8 @@
       <c r="N10" s="37">
         <v>50</v>
       </c>
-      <c r="O10" s="60" t="s">
-        <v>347</v>
+      <c r="O10" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P10" s="38">
         <v>1.89E-2</v>
@@ -2433,7 +2439,7 @@
         <f t="shared" ref="B11:B67" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="44" t="s">
@@ -2443,22 +2449,22 @@
         <v>81</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="L11" s="44">
         <v>2</v>
@@ -2470,8 +2476,8 @@
       <c r="N11" s="44">
         <v>11</v>
       </c>
-      <c r="O11" s="61" t="s">
-        <v>347</v>
+      <c r="O11" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P11" s="45">
         <v>1.2122999999999999</v>
@@ -2489,7 +2495,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
@@ -2499,22 +2505,22 @@
         <v>82</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="L12" s="37">
         <v>14</v>
@@ -2526,8 +2532,8 @@
       <c r="N12" s="37">
         <v>100</v>
       </c>
-      <c r="O12" s="60" t="s">
-        <v>347</v>
+      <c r="O12" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P12" s="38">
         <v>5.0000000000000001E-3</v>
@@ -2545,7 +2551,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="44" t="s">
@@ -2555,22 +2561,22 @@
         <v>83</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L13" s="44">
         <v>1</v>
@@ -2582,8 +2588,8 @@
       <c r="N13" s="44">
         <v>100</v>
       </c>
-      <c r="O13" s="61" t="s">
-        <v>347</v>
+      <c r="O13" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P13" s="45">
         <v>2.8E-3</v>
@@ -2601,7 +2607,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
@@ -2611,22 +2617,22 @@
         <v>84</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="L14" s="37">
         <v>25</v>
@@ -2638,8 +2644,8 @@
       <c r="N14" s="37">
         <v>200</v>
       </c>
-      <c r="O14" s="60" t="s">
-        <v>347</v>
+      <c r="O14" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P14" s="38">
         <v>1.8E-3</v>
@@ -2657,7 +2663,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="44" t="s">
@@ -2667,22 +2673,22 @@
         <v>85</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L15" s="44">
         <v>2</v>
@@ -2694,8 +2700,8 @@
       <c r="N15" s="44">
         <v>15</v>
       </c>
-      <c r="O15" s="61" t="s">
-        <v>347</v>
+      <c r="O15" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P15" s="45">
         <v>0.16370000000000001</v>
@@ -2713,7 +2719,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
@@ -2723,22 +2729,22 @@
         <v>86</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="L16" s="37">
         <v>2</v>
@@ -2750,8 +2756,8 @@
       <c r="N16" s="37">
         <v>15</v>
       </c>
-      <c r="O16" s="60" t="s">
-        <v>347</v>
+      <c r="O16" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P16" s="38">
         <v>0.42320000000000002</v>
@@ -2769,7 +2775,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="44" t="s">
@@ -2779,22 +2785,22 @@
         <v>87</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="L17" s="44">
         <v>6</v>
@@ -2806,8 +2812,8 @@
       <c r="N17" s="44">
         <v>40</v>
       </c>
-      <c r="O17" s="61" t="s">
-        <v>347</v>
+      <c r="O17" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P17" s="45">
         <v>2.3800000000000002E-2</v>
@@ -2825,7 +2831,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="37" t="s">
@@ -2835,20 +2841,22 @@
         <v>88</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>178</v>
+        <v>140</v>
+      </c>
+      <c r="G18" s="54" t="s">
+        <v>176</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="I18" s="37"/>
+        <v>222</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>346</v>
+      </c>
       <c r="J18" s="37" t="s">
-        <v>258</v>
+        <v>347</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -2857,12 +2865,18 @@
         <f>L18*5</f>
         <v>15</v>
       </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="38"/>
+      <c r="N18" s="37">
+        <v>50</v>
+      </c>
+      <c r="O18" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="P18" s="38">
+        <v>5.4999999999999997E-3</v>
+      </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>0</v>
+        <v>0.27499999999999997</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="49"/>
@@ -2873,7 +2887,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="44" t="s">
@@ -2883,22 +2897,22 @@
         <v>89</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L19" s="44">
         <v>1</v>
@@ -2910,8 +2924,8 @@
       <c r="N19" s="44">
         <v>20</v>
       </c>
-      <c r="O19" s="61" t="s">
-        <v>347</v>
+      <c r="O19" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P19" s="45">
         <v>2.0199999999999999E-2</v>
@@ -2929,7 +2943,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="44" t="s">
@@ -2939,22 +2953,22 @@
         <v>90</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H20" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L20" s="44">
         <v>2</v>
@@ -2966,8 +2980,8 @@
       <c r="N20" s="44">
         <v>100</v>
       </c>
-      <c r="O20" s="61" t="s">
-        <v>347</v>
+      <c r="O20" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P20" s="45">
         <v>3.7000000000000002E-3</v>
@@ -2985,7 +2999,7 @@
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="37" t="s">
@@ -2995,22 +3009,22 @@
         <v>91</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L21" s="37">
         <v>2</v>
@@ -3022,8 +3036,8 @@
       <c r="N21" s="37">
         <v>100</v>
       </c>
-      <c r="O21" s="60" t="s">
-        <v>347</v>
+      <c r="O21" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P21" s="38">
         <v>4.4999999999999997E-3</v>
@@ -3041,7 +3055,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="50" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="44" t="s">
@@ -3051,22 +3065,22 @@
         <v>92</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L22" s="44">
         <v>1</v>
@@ -3078,8 +3092,8 @@
       <c r="N22" s="44">
         <v>100</v>
       </c>
-      <c r="O22" s="61" t="s">
-        <v>347</v>
+      <c r="O22" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P22" s="45">
         <v>3.2000000000000002E-3</v>
@@ -3097,7 +3111,7 @@
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="50" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="37" t="s">
@@ -3107,22 +3121,22 @@
         <v>93</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K23" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L23" s="37">
         <v>1</v>
@@ -3134,8 +3148,8 @@
       <c r="N23" s="37">
         <v>10</v>
       </c>
-      <c r="O23" s="60" t="s">
-        <v>347</v>
+      <c r="O23" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P23" s="38">
         <v>6.6000000000000003E-2</v>
@@ -3153,7 +3167,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="50" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="44" t="s">
@@ -3163,22 +3177,22 @@
         <v>94</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G24" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H24" s="44" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I24" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J24" s="44" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="K24" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L24" s="44">
         <v>1</v>
@@ -3190,8 +3204,8 @@
       <c r="N24" s="44">
         <v>10</v>
       </c>
-      <c r="O24" s="61" t="s">
-        <v>347</v>
+      <c r="O24" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P24" s="45">
         <v>8.6400000000000005E-2</v>
@@ -3209,7 +3223,7 @@
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="50" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="37" t="s">
@@ -3219,22 +3233,22 @@
         <v>95</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K25" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L25" s="37">
         <v>1</v>
@@ -3246,8 +3260,8 @@
       <c r="N25" s="37">
         <v>20</v>
       </c>
-      <c r="O25" s="60" t="s">
-        <v>347</v>
+      <c r="O25" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P25" s="38">
         <v>2.63E-2</v>
@@ -3265,7 +3279,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="51" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="44" t="s">
@@ -3275,22 +3289,22 @@
         <v>96</v>
       </c>
       <c r="F26" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H26" s="44" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I26" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J26" s="44" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L26" s="44">
         <v>1</v>
@@ -3302,8 +3316,8 @@
       <c r="N26" s="44">
         <v>10</v>
       </c>
-      <c r="O26" s="61" t="s">
-        <v>347</v>
+      <c r="O26" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P26" s="45">
         <v>9.8199999999999996E-2</v>
@@ -3321,7 +3335,7 @@
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="50" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="37" t="s">
@@ -3331,22 +3345,22 @@
         <v>97</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J27" s="37" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L27" s="37">
         <v>2</v>
@@ -3358,8 +3372,8 @@
       <c r="N27" s="37">
         <v>20</v>
       </c>
-      <c r="O27" s="60" t="s">
-        <v>347</v>
+      <c r="O27" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P27" s="38">
         <v>3.2199999999999999E-2</v>
@@ -3377,7 +3391,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="51" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="44" t="s">
@@ -3387,22 +3401,22 @@
         <v>98</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H28" s="44" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I28" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J28" s="44" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K28" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L28" s="44">
         <v>1</v>
@@ -3414,8 +3428,8 @@
       <c r="N28" s="44">
         <v>50</v>
       </c>
-      <c r="O28" s="61" t="s">
-        <v>347</v>
+      <c r="O28" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P28" s="45">
         <v>8.8999999999999999E-3</v>
@@ -3433,7 +3447,7 @@
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="50" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3443,22 +3457,22 @@
         <v>99</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="K29" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L29" s="37">
         <v>1</v>
@@ -3470,8 +3484,8 @@
       <c r="N29" s="37">
         <v>10</v>
       </c>
-      <c r="O29" s="60" t="s">
-        <v>347</v>
+      <c r="O29" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P29" s="38">
         <v>0.2213</v>
@@ -3489,7 +3503,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="51" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="44" t="s">
@@ -3499,22 +3513,22 @@
         <v>100</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G30" s="44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H30" s="44" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I30" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J30" s="44" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L30" s="44">
         <v>2</v>
@@ -3526,8 +3540,8 @@
       <c r="N30" s="44">
         <v>20</v>
       </c>
-      <c r="O30" s="61" t="s">
-        <v>347</v>
+      <c r="O30" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P30" s="45">
         <v>3.39E-2</v>
@@ -3545,7 +3559,7 @@
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="58" t="s">
+      <c r="C31" s="50" t="s">
         <v>16</v>
       </c>
       <c r="D31" s="37" t="s">
@@ -3555,22 +3569,22 @@
         <v>101</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L31" s="37">
         <v>1</v>
@@ -3582,8 +3596,8 @@
       <c r="N31" s="37">
         <v>6</v>
       </c>
-      <c r="O31" s="60" t="s">
-        <v>347</v>
+      <c r="O31" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P31" s="38">
         <v>1.4796</v>
@@ -3601,7 +3615,7 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="59"/>
+      <c r="C32" s="51"/>
       <c r="D32" s="44" t="s">
         <v>45</v>
       </c>
@@ -3609,22 +3623,22 @@
         <v>102</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G32" s="44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H32" s="44" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I32" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J32" s="44" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="K32" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L32" s="44">
         <v>1</v>
@@ -3636,8 +3650,8 @@
       <c r="N32" s="44">
         <v>6</v>
       </c>
-      <c r="O32" s="61" t="s">
-        <v>347</v>
+      <c r="O32" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P32" s="45">
         <v>0.9546</v>
@@ -3655,7 +3669,7 @@
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="37" t="s">
@@ -3665,22 +3679,22 @@
         <v>103</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -3692,8 +3706,8 @@
       <c r="N33" s="37">
         <v>10</v>
       </c>
-      <c r="O33" s="60" t="s">
-        <v>347</v>
+      <c r="O33" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P33" s="38">
         <v>4.1300000000000003E-2</v>
@@ -3711,7 +3725,7 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="51" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="44" t="s">
@@ -3721,22 +3735,22 @@
         <v>104</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G34" s="44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H34" s="44" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J34" s="44" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="K34" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L34" s="44">
         <v>1</v>
@@ -3748,8 +3762,8 @@
       <c r="N34" s="44">
         <v>6</v>
       </c>
-      <c r="O34" s="61" t="s">
-        <v>347</v>
+      <c r="O34" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P34" s="45">
         <v>0.29110000000000003</v>
@@ -3767,54 +3781,54 @@
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="62" t="s">
+      <c r="D35" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="62" t="s">
-        <v>334</v>
-      </c>
-      <c r="G35" s="62" t="s">
-        <v>335</v>
-      </c>
-      <c r="H35" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="I35" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="J35" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="K35" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="L35" s="62">
+      <c r="F35" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="G35" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="I35" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="J35" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="K35" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="L35" s="54">
         <v>13</v>
       </c>
-      <c r="M35" s="62">
+      <c r="M35" s="54">
         <f>L35*5</f>
         <v>65</v>
       </c>
-      <c r="N35" s="62" t="s">
-        <v>333</v>
-      </c>
-      <c r="O35" s="62" t="s">
-        <v>333</v>
-      </c>
-      <c r="P35" s="65" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q35" s="65" t="s">
-        <v>333</v>
-      </c>
-      <c r="R35" s="62"/>
-      <c r="S35" s="66"/>
+      <c r="N35" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="O35" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="P35" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q35" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="R35" s="54"/>
+      <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
@@ -3822,7 +3836,7 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="51" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="44" t="s">
@@ -3832,22 +3846,22 @@
         <v>106</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G36" s="44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H36" s="44" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I36" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J36" s="44" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L36" s="44">
         <v>1</v>
@@ -3859,8 +3873,8 @@
       <c r="N36" s="44">
         <v>10</v>
       </c>
-      <c r="O36" s="61" t="s">
-        <v>347</v>
+      <c r="O36" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P36" s="45">
         <v>4.6899999999999997E-2</v>
@@ -3878,7 +3892,7 @@
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="51" t="s">
         <v>18</v>
       </c>
       <c r="D37" s="37" t="s">
@@ -3888,22 +3902,22 @@
         <v>107</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L37" s="37">
         <v>1</v>
@@ -3915,8 +3929,8 @@
       <c r="N37" s="37">
         <v>20</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>347</v>
+      <c r="O37" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P37" s="38">
         <v>3.49E-2</v>
@@ -3934,45 +3948,45 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="44" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E38" s="44" t="s">
         <v>108</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H38" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I38" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J38" s="44" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="L38" s="44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M38" s="44">
         <f t="shared" ref="M38" si="29">L38*5</f>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N38" s="44">
         <v>100</v>
       </c>
-      <c r="O38" s="61" t="s">
-        <v>347</v>
+      <c r="O38" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P38" s="45">
         <v>1E-3</v>
@@ -3990,7 +4004,7 @@
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="37" t="s">
@@ -4000,22 +4014,22 @@
         <v>109</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="K39" s="37" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="L39" s="37">
         <v>3</v>
@@ -4027,8 +4041,8 @@
       <c r="N39" s="37">
         <v>100</v>
       </c>
-      <c r="O39" s="60" t="s">
-        <v>347</v>
+      <c r="O39" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P39" s="38">
         <v>1.1999999999999999E-3</v>
@@ -4046,7 +4060,7 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="44" t="s">
@@ -4056,22 +4070,22 @@
         <v>110</v>
       </c>
       <c r="F40" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G40" s="44" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H40" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I40" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J40" s="44" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K40" s="44" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="L40" s="44">
         <v>3</v>
@@ -4083,8 +4097,8 @@
       <c r="N40" s="44">
         <v>100</v>
       </c>
-      <c r="O40" s="61" t="s">
-        <v>347</v>
+      <c r="O40" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P40" s="45">
         <v>1.1000000000000001E-3</v>
@@ -4102,7 +4116,7 @@
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="37" t="s">
@@ -4112,22 +4126,22 @@
         <v>111</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="K41" s="37" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="L41" s="37">
         <v>1</v>
@@ -4139,8 +4153,8 @@
       <c r="N41" s="37">
         <v>100</v>
       </c>
-      <c r="O41" s="60" t="s">
-        <v>347</v>
+      <c r="O41" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P41" s="38">
         <v>1.1999999999999999E-3</v>
@@ -4158,7 +4172,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="37" t="s">
@@ -4168,22 +4182,22 @@
         <v>112</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L42" s="37">
         <v>2</v>
@@ -4195,8 +4209,8 @@
       <c r="N42" s="37">
         <v>100</v>
       </c>
-      <c r="O42" s="60" t="s">
-        <v>347</v>
+      <c r="O42" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P42" s="38">
         <v>1.1000000000000001E-3</v>
@@ -4208,36 +4222,38 @@
       <c r="R42" s="37"/>
       <c r="S42" s="49"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="40">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="44" t="s">
         <v>55</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>113</v>
+        <v>353</v>
       </c>
       <c r="F43" s="44" t="s">
-        <v>154</v>
+        <v>350</v>
       </c>
       <c r="G43" s="44" t="s">
-        <v>199</v>
+        <v>351</v>
       </c>
       <c r="H43" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="I43" s="44"/>
+        <v>219</v>
+      </c>
+      <c r="I43" s="44" t="s">
+        <v>328</v>
+      </c>
       <c r="J43" s="44" t="s">
-        <v>280</v>
+        <v>352</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L43" s="44">
         <v>1</v>
@@ -4246,12 +4262,18 @@
         <f t="shared" ref="M43" si="33">L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="44"/>
-      <c r="O43" s="44"/>
-      <c r="P43" s="45"/>
+      <c r="N43" s="44">
+        <v>20</v>
+      </c>
+      <c r="O43" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="P43" s="45">
+        <v>2.7699999999999999E-2</v>
+      </c>
       <c r="Q43" s="45">
         <f t="shared" ref="Q43" si="34">P43*N43</f>
-        <v>0</v>
+        <v>0.55399999999999994</v>
       </c>
       <c r="R43" s="44"/>
       <c r="S43" s="49"/>
@@ -4262,32 +4284,32 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="C44" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="37" t="s">
         <v>56</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="L44" s="37">
         <v>5</v>
@@ -4299,8 +4321,8 @@
       <c r="N44" s="37">
         <v>100</v>
       </c>
-      <c r="O44" s="60" t="s">
-        <v>347</v>
+      <c r="O44" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P44" s="38">
         <v>1.1999999999999999E-3</v>
@@ -4318,32 +4340,32 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="44" t="s">
         <v>57</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H45" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L45" s="44">
         <v>2</v>
@@ -4355,8 +4377,8 @@
       <c r="N45" s="44">
         <v>100</v>
       </c>
-      <c r="O45" s="61" t="s">
-        <v>347</v>
+      <c r="O45" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P45" s="45">
         <v>3.0999999999999999E-3</v>
@@ -4374,32 +4396,32 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="37" t="s">
         <v>58</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="L46" s="37">
         <v>3</v>
@@ -4411,8 +4433,8 @@
       <c r="N46" s="37">
         <v>100</v>
       </c>
-      <c r="O46" s="60" t="s">
-        <v>347</v>
+      <c r="O46" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P46" s="38">
         <v>1.1000000000000001E-3</v>
@@ -4430,32 +4452,32 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C47" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D47" s="44" t="s">
         <v>59</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H47" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I47" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J47" s="44" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="L47" s="44">
         <v>2</v>
@@ -4467,8 +4489,8 @@
       <c r="N47" s="44">
         <v>100</v>
       </c>
-      <c r="O47" s="61" t="s">
-        <v>347</v>
+      <c r="O47" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P47" s="45">
         <v>1.1999999999999999E-3</v>
@@ -4486,32 +4508,32 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="58" t="s">
+      <c r="C48" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="37" t="s">
         <v>60</v>
       </c>
       <c r="E48" s="37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K48" s="37" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L48" s="37">
         <v>2</v>
@@ -4523,8 +4545,8 @@
       <c r="N48" s="37">
         <v>100</v>
       </c>
-      <c r="O48" s="60" t="s">
-        <v>347</v>
+      <c r="O48" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P48" s="38">
         <v>1.8E-3</v>
@@ -4542,32 +4564,32 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="58" t="s">
+      <c r="C49" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="44" t="s">
         <v>61</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F49" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G49" s="44" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H49" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I49" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J49" s="44" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="L49" s="44">
         <v>1</v>
@@ -4579,8 +4601,8 @@
       <c r="N49" s="44">
         <v>20</v>
       </c>
-      <c r="O49" s="61" t="s">
-        <v>347</v>
+      <c r="O49" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P49" s="45">
         <v>2.75E-2</v>
@@ -4598,32 +4620,32 @@
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="37" t="s">
         <v>62</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L50" s="37">
         <v>1</v>
@@ -4635,8 +4657,8 @@
       <c r="N50" s="37">
         <v>50</v>
       </c>
-      <c r="O50" s="60" t="s">
-        <v>347</v>
+      <c r="O50" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P50" s="38">
         <v>8.8000000000000005E-3</v>
@@ -4654,32 +4676,32 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D51" s="44" t="s">
         <v>63</v>
       </c>
       <c r="E51" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F51" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G51" s="44" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H51" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I51" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J51" s="44" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="K51" s="44" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="L51" s="44">
         <v>1</v>
@@ -4691,8 +4713,8 @@
       <c r="N51" s="44">
         <v>20</v>
       </c>
-      <c r="O51" s="61" t="s">
-        <v>347</v>
+      <c r="O51" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P51" s="45">
         <v>2.63E-2</v>
@@ -4710,32 +4732,32 @@
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="37" t="s">
         <v>64</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J52" s="37" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="L52" s="37">
         <v>1</v>
@@ -4747,8 +4769,8 @@
       <c r="N52" s="37">
         <v>20</v>
       </c>
-      <c r="O52" s="60" t="s">
-        <v>347</v>
+      <c r="O52" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P52" s="38">
         <v>3.1E-2</v>
@@ -4766,32 +4788,32 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="58" t="s">
+      <c r="C53" s="50" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="44" t="s">
         <v>65</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F53" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G53" s="44" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H53" s="44" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I53" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J53" s="44" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="K53" s="44" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L53" s="44">
         <v>1</v>
@@ -4803,8 +4825,8 @@
       <c r="N53" s="44">
         <v>100</v>
       </c>
-      <c r="O53" s="61" t="s">
-        <v>347</v>
+      <c r="O53" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P53" s="45">
         <v>1.1999999999999999E-3</v>
@@ -4822,54 +4844,54 @@
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="58" t="s">
-        <v>155</v>
-      </c>
-      <c r="D54" s="62" t="s">
+      <c r="C54" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="E54" s="62" t="s">
-        <v>124</v>
-      </c>
-      <c r="F54" s="62" t="s">
-        <v>334</v>
-      </c>
-      <c r="G54" s="62" t="s">
-        <v>155</v>
-      </c>
-      <c r="H54" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="I54" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="J54" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="K54" s="62" t="s">
-        <v>333</v>
-      </c>
-      <c r="L54" s="62">
+      <c r="E54" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="G54" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="H54" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="I54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="J54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="K54" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="L54" s="54">
         <v>3</v>
       </c>
-      <c r="M54" s="62">
+      <c r="M54" s="54">
         <f>L54*5</f>
         <v>15</v>
       </c>
-      <c r="N54" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="O54" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="P54" s="65" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q54" s="65" t="s">
-        <v>333</v>
-      </c>
-      <c r="R54" s="62"/>
-      <c r="S54" s="66"/>
+      <c r="N54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="O54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="P54" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q54" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="R54" s="54"/>
+      <c r="S54" s="58"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
@@ -4877,32 +4899,32 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="59" t="s">
+      <c r="C55" s="51" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="44" t="s">
         <v>67</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F55" s="44" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H55" s="44" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I55" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J55" s="44" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K55" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L55" s="44">
         <v>5</v>
@@ -4914,8 +4936,8 @@
       <c r="N55" s="44">
         <v>30</v>
       </c>
-      <c r="O55" s="61" t="s">
-        <v>347</v>
+      <c r="O55" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P55" s="45">
         <v>0.3135</v>
@@ -4933,32 +4955,32 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="59" t="s">
+      <c r="C56" s="51" t="s">
         <v>20</v>
       </c>
       <c r="D56" s="44" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F56" s="44" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H56" s="44" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I56" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J56" s="44" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L56" s="44">
         <v>1</v>
@@ -4970,8 +4992,8 @@
       <c r="N56" s="44">
         <v>10</v>
       </c>
-      <c r="O56" s="61" t="s">
-        <v>347</v>
+      <c r="O56" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P56" s="45">
         <v>6.2100000000000002E-2</v>
@@ -4989,32 +5011,32 @@
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="58" t="s">
+      <c r="C57" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D57" s="37" t="s">
         <v>68</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L57" s="37">
         <v>1</v>
@@ -5026,8 +5048,8 @@
       <c r="N57" s="37">
         <v>6</v>
       </c>
-      <c r="O57" s="60" t="s">
-        <v>347</v>
+      <c r="O57" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P57" s="38">
         <v>0.16209999999999999</v>
@@ -5045,28 +5067,32 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="59" t="s">
+      <c r="C58" s="51" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="44" t="s">
         <v>69</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F58" s="44" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H58" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="I58" s="44"/>
-      <c r="J58" s="44"/>
+        <v>236</v>
+      </c>
+      <c r="I58" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J58" s="44" t="s">
+        <v>348</v>
+      </c>
       <c r="K58" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L58" s="44">
         <v>1</v>
@@ -5075,12 +5101,18 @@
         <f t="shared" ref="M58" si="49">L58*5</f>
         <v>5</v>
       </c>
-      <c r="N58" s="44"/>
-      <c r="O58" s="44"/>
-      <c r="P58" s="45"/>
+      <c r="N58" s="44">
+        <v>10</v>
+      </c>
+      <c r="O58" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="P58" s="45">
+        <v>0.1341</v>
+      </c>
       <c r="Q58" s="45">
         <f t="shared" ref="Q58" si="50">P58*N58</f>
-        <v>0</v>
+        <v>1.341</v>
       </c>
       <c r="R58" s="44"/>
       <c r="S58" s="49"/>
@@ -5091,32 +5123,32 @@
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="58" t="s">
+      <c r="C59" s="50" t="s">
         <v>18</v>
       </c>
       <c r="D59" s="37" t="s">
         <v>70</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L59" s="37">
         <v>1</v>
@@ -5128,8 +5160,8 @@
       <c r="N59" s="37">
         <v>10</v>
       </c>
-      <c r="O59" s="60" t="s">
-        <v>347</v>
+      <c r="O59" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P59" s="38">
         <v>0.19539999999999999</v>
@@ -5147,32 +5179,32 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="59" t="s">
+      <c r="C60" s="51" t="s">
         <v>21</v>
       </c>
       <c r="D60" s="44" t="s">
         <v>71</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F60" s="44" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G60" s="44" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H60" s="44" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I60" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L60" s="44">
         <v>1</v>
@@ -5184,8 +5216,8 @@
       <c r="N60" s="44">
         <v>6</v>
       </c>
-      <c r="O60" s="61" t="s">
-        <v>347</v>
+      <c r="O60" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P60" s="45">
         <v>0.43909999999999999</v>
@@ -5203,32 +5235,32 @@
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="58" t="s">
+      <c r="C61" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="37" t="s">
         <v>72</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J61" s="37" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L61" s="37">
         <v>1</v>
@@ -5240,8 +5272,8 @@
       <c r="N61" s="37">
         <v>10</v>
       </c>
-      <c r="O61" s="60" t="s">
-        <v>347</v>
+      <c r="O61" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P61" s="38">
         <v>0.15479999999999999</v>
@@ -5259,32 +5291,32 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="58" t="s">
+      <c r="C62" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="37" t="s">
         <v>73</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K62" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -5296,8 +5328,8 @@
       <c r="N62" s="37">
         <v>6</v>
       </c>
-      <c r="O62" s="60" t="s">
-        <v>347</v>
+      <c r="O62" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P62" s="38">
         <v>5.1212</v>
@@ -5315,32 +5347,32 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="59" t="s">
+      <c r="C63" s="51" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="44" t="s">
         <v>74</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F63" s="44" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G63" s="44" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H63" s="44" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I63" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J63" s="44" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="K63" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L63" s="44">
         <v>1</v>
@@ -5352,8 +5384,8 @@
       <c r="N63" s="44">
         <v>10</v>
       </c>
-      <c r="O63" s="61" t="s">
-        <v>347</v>
+      <c r="O63" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P63" s="45">
         <v>0.15670000000000001</v>
@@ -5371,32 +5403,32 @@
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
-      <c r="C64" s="58" t="s">
+      <c r="C64" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D64" s="37" t="s">
         <v>75</v>
       </c>
       <c r="E64" s="37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J64" s="37" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="K64" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L64" s="37">
         <v>1</v>
@@ -5408,8 +5440,8 @@
       <c r="N64" s="37">
         <v>6</v>
       </c>
-      <c r="O64" s="60" t="s">
-        <v>347</v>
+      <c r="O64" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P64" s="38">
         <v>0.96889999999999998</v>
@@ -5427,32 +5459,32 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="59" t="s">
+      <c r="C65" s="51" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="44" t="s">
         <v>76</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F65" s="44" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G65" s="44" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H65" s="44" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I65" s="44" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J65" s="44" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="K65" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L65" s="44">
         <v>1</v>
@@ -5464,8 +5496,8 @@
       <c r="N65" s="44">
         <v>6</v>
       </c>
-      <c r="O65" s="61" t="s">
-        <v>347</v>
+      <c r="O65" s="53" t="s">
+        <v>342</v>
       </c>
       <c r="P65" s="45">
         <v>0.28870000000000001</v>
@@ -5483,32 +5515,32 @@
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="58" t="s">
+      <c r="C66" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>77</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K66" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L66" s="37">
         <v>1</v>
@@ -5520,8 +5552,8 @@
       <c r="N66" s="37">
         <v>6</v>
       </c>
-      <c r="O66" s="60" t="s">
-        <v>347</v>
+      <c r="O66" s="52" t="s">
+        <v>342</v>
       </c>
       <c r="P66" s="38">
         <v>2.0651000000000002</v>
@@ -5535,36 +5567,36 @@
     </row>
     <row r="67" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
-      <c r="B67" s="67">
+      <c r="B67" s="59">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="60" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="49" t="s">
         <v>78</v>
       </c>
       <c r="E67" s="49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F67" s="49" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G67" s="49" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I67" s="49" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J67" s="49" t="s">
-        <v>302</v>
-      </c>
-      <c r="K67" s="69" t="s">
-        <v>333</v>
+        <v>297</v>
+      </c>
+      <c r="K67" s="61" t="s">
+        <v>328</v>
       </c>
       <c r="L67" s="49">
         <v>1</v>
@@ -5576,13 +5608,13 @@
       <c r="N67" s="49">
         <v>6</v>
       </c>
-      <c r="O67" s="70" t="s">
-        <v>347</v>
-      </c>
-      <c r="P67" s="71">
+      <c r="O67" s="62" t="s">
+        <v>342</v>
+      </c>
+      <c r="P67" s="63">
         <v>1.2919</v>
       </c>
-      <c r="Q67" s="71">
+      <c r="Q67" s="63">
         <f t="shared" ref="Q67" si="58">P67*N67</f>
         <v>7.7514000000000003</v>
       </c>
@@ -5591,29 +5623,29 @@
     </row>
     <row r="68" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
-      <c r="B68" s="72"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="75"/>
-      <c r="F68" s="76"/>
-      <c r="G68" s="77"/>
-      <c r="H68" s="76"/>
-      <c r="I68" s="77"/>
-      <c r="J68" s="76"/>
-      <c r="K68" s="77"/>
-      <c r="L68" s="77"/>
-      <c r="M68" s="77"/>
-      <c r="N68" s="56" t="s">
+      <c r="B68" s="64"/>
+      <c r="C68" s="65"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="69"/>
+      <c r="L68" s="69"/>
+      <c r="M68" s="69"/>
+      <c r="N68" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="O68" s="57"/>
-      <c r="P68" s="57"/>
+      <c r="O68" s="79"/>
+      <c r="P68" s="79"/>
       <c r="Q68" s="41">
         <f>SUM(Q10:Q67)</f>
-        <v>132.43659999999997</v>
-      </c>
-      <c r="R68" s="78"/>
-      <c r="S68" s="79"/>
+        <v>134.60659999999996</v>
+      </c>
+      <c r="R68" s="74"/>
+      <c r="S68" s="75"/>
     </row>
     <row r="69" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -5629,17 +5661,17 @@
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
       <c r="M69" s="10"/>
-      <c r="N69" s="56" t="s">
+      <c r="N69" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="O69" s="57"/>
-      <c r="P69" s="57"/>
+      <c r="O69" s="79"/>
+      <c r="P69" s="79"/>
       <c r="Q69" s="42">
         <f>Q68/5</f>
-        <v>26.487319999999993</v>
-      </c>
-      <c r="R69" s="54"/>
-      <c r="S69" s="55"/>
+        <v>26.921319999999991</v>
+      </c>
+      <c r="R69" s="76"/>
+      <c r="S69" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5703,9 +5735,12 @@
     <hyperlink ref="O65" r:id="rId51"/>
     <hyperlink ref="O66" r:id="rId52"/>
     <hyperlink ref="O67" r:id="rId53"/>
+    <hyperlink ref="O18" r:id="rId54"/>
+    <hyperlink ref="O58" r:id="rId55"/>
+    <hyperlink ref="O43" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId54"/>
-  <drawing r:id="rId55"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
+  <drawing r:id="rId58"/>
 </worksheet>
 </file>
--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -12,14 +12,15 @@
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
+    <sheet name="1 Board" sheetId="2" r:id="rId1"/>
+    <sheet name="5 Boards" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="358">
   <si>
     <t>Component list</t>
   </si>
@@ -1081,6 +1082,18 @@
   </si>
   <si>
     <t>General Purpose Chip Resistor Thick Film 1206 5.6Ohm 1% Paper T/R</t>
+  </si>
+  <si>
+    <t>LCSC/MOQ</t>
+  </si>
+  <si>
+    <t>UnitCost (1 Boards)</t>
+  </si>
+  <si>
+    <t>TotalCost (1 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R9 = DNP that’s why not added in BOM </t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1105,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1254,6 +1267,14 @@
     </font>
     <font>
       <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1548,7 +1569,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1771,6 +1792,65 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1796,6 +1876,60 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20783550" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2112,8 +2246,3371 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" customWidth="1"/>
+    <col min="18" max="18" width="26.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="71"/>
+    </row>
+    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="46" t="s">
+        <v>340</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="72"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="73"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="73"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="73"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="73"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="73"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="80"/>
+      <c r="B10" s="39">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="L10" s="37">
+        <v>3</v>
+      </c>
+      <c r="M10" s="37">
+        <v>50</v>
+      </c>
+      <c r="N10" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O10" s="38">
+        <v>1.89E-2</v>
+      </c>
+      <c r="P10" s="38">
+        <f>O10*M10</f>
+        <v>0.94500000000000006</v>
+      </c>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="81"/>
+    </row>
+    <row r="11" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="80"/>
+      <c r="B11" s="40">
+        <f t="shared" ref="B11:B67" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="I11" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J11" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="K11" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="L11" s="44">
+        <v>2</v>
+      </c>
+      <c r="M11" s="44">
+        <v>3</v>
+      </c>
+      <c r="N11" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O11" s="45">
+        <v>1.4064000000000001</v>
+      </c>
+      <c r="P11" s="45">
+        <f t="shared" ref="P11" si="1">O11*M11</f>
+        <v>4.2192000000000007</v>
+      </c>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+    </row>
+    <row r="12" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="80"/>
+      <c r="B12" s="39">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="L12" s="37">
+        <v>14</v>
+      </c>
+      <c r="M12" s="37">
+        <v>100</v>
+      </c>
+      <c r="N12" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O12" s="38">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P12" s="38">
+        <f>O12*M12</f>
+        <v>0.5</v>
+      </c>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="49"/>
+    </row>
+    <row r="13" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="80"/>
+      <c r="B13" s="40">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="K13" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="L13" s="44">
+        <v>1</v>
+      </c>
+      <c r="M13" s="44">
+        <v>100</v>
+      </c>
+      <c r="N13" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="45">
+        <v>2.8E-3</v>
+      </c>
+      <c r="P13" s="45">
+        <f t="shared" ref="P13" si="2">O13*M13</f>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="49"/>
+    </row>
+    <row r="14" spans="1:18" s="82" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A14" s="80"/>
+      <c r="B14" s="39">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="L14" s="37">
+        <v>25</v>
+      </c>
+      <c r="M14" s="37">
+        <v>100</v>
+      </c>
+      <c r="N14" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O14" s="38">
+        <v>1.8E-3</v>
+      </c>
+      <c r="P14" s="38">
+        <f>O14*M14</f>
+        <v>0.18</v>
+      </c>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="49"/>
+    </row>
+    <row r="15" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="80"/>
+      <c r="B15" s="40">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="K15" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L15" s="44">
+        <v>2</v>
+      </c>
+      <c r="M15" s="44">
+        <v>5</v>
+      </c>
+      <c r="N15" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O15" s="45">
+        <v>0.16370000000000001</v>
+      </c>
+      <c r="P15" s="45">
+        <f t="shared" ref="P15" si="3">O15*M15</f>
+        <v>0.81850000000000001</v>
+      </c>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="49"/>
+    </row>
+    <row r="16" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="80"/>
+      <c r="B16" s="39">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="L16" s="37">
+        <v>2</v>
+      </c>
+      <c r="M16" s="37">
+        <v>5</v>
+      </c>
+      <c r="N16" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O16" s="38">
+        <v>0.42320000000000002</v>
+      </c>
+      <c r="P16" s="38">
+        <f>O16*M16</f>
+        <v>2.1160000000000001</v>
+      </c>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="49"/>
+    </row>
+    <row r="17" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="80"/>
+      <c r="B17" s="40">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="L17" s="44">
+        <v>6</v>
+      </c>
+      <c r="M17" s="44">
+        <v>20</v>
+      </c>
+      <c r="N17" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O17" s="45">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="P17" s="45">
+        <f t="shared" ref="P17" si="4">O17*M17</f>
+        <v>0.47600000000000003</v>
+      </c>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="49"/>
+    </row>
+    <row r="18" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="80"/>
+      <c r="B18" s="39">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="L18" s="37">
+        <v>3</v>
+      </c>
+      <c r="M18" s="37">
+        <v>50</v>
+      </c>
+      <c r="N18" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O18" s="38">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="P18" s="38">
+        <f>O18*M18</f>
+        <v>0.27499999999999997</v>
+      </c>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="49"/>
+    </row>
+    <row r="19" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="80"/>
+      <c r="B19" s="40">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J19" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="K19" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="L19" s="44">
+        <v>1</v>
+      </c>
+      <c r="M19" s="44">
+        <v>20</v>
+      </c>
+      <c r="N19" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O19" s="45">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="P19" s="45">
+        <f t="shared" ref="P19:P20" si="5">O19*M19</f>
+        <v>0.40399999999999997</v>
+      </c>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="49"/>
+    </row>
+    <row r="20" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="80"/>
+      <c r="B20" s="40">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="K20" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="L20" s="44">
+        <v>2</v>
+      </c>
+      <c r="M20" s="44">
+        <v>100</v>
+      </c>
+      <c r="N20" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O20" s="45">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="P20" s="45">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="49"/>
+    </row>
+    <row r="21" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="80"/>
+      <c r="B21" s="39">
+        <f>ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="L21" s="37">
+        <v>2</v>
+      </c>
+      <c r="M21" s="37">
+        <v>100</v>
+      </c>
+      <c r="N21" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O21" s="38">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="P21" s="38">
+        <f>O21*M21</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="49"/>
+    </row>
+    <row r="22" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="80"/>
+      <c r="B22" s="40">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I22" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="K22" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="L22" s="44">
+        <v>1</v>
+      </c>
+      <c r="M22" s="44">
+        <v>100</v>
+      </c>
+      <c r="N22" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O22" s="45">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="P22" s="45">
+        <f t="shared" ref="P22" si="6">O22*M22</f>
+        <v>0.32</v>
+      </c>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="49"/>
+    </row>
+    <row r="23" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="80"/>
+      <c r="B23" s="39">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L23" s="37">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <v>10</v>
+      </c>
+      <c r="N23" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O23" s="38">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="P23" s="38">
+        <f>O23*M23</f>
+        <v>0.66</v>
+      </c>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="49"/>
+    </row>
+    <row r="24" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="80"/>
+      <c r="B24" s="40">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>260</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L24" s="44">
+        <v>1</v>
+      </c>
+      <c r="M24" s="44">
+        <v>5</v>
+      </c>
+      <c r="N24" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O24" s="45">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="P24" s="45">
+        <f t="shared" ref="P24" si="7">O24*M24</f>
+        <v>0.43200000000000005</v>
+      </c>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="49"/>
+    </row>
+    <row r="25" spans="1:18" s="82" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A25" s="80"/>
+      <c r="B25" s="39">
+        <f>ROW(B25) - ROW($B$9)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L25" s="37">
+        <v>1</v>
+      </c>
+      <c r="M25" s="37">
+        <v>20</v>
+      </c>
+      <c r="N25" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O25" s="38">
+        <v>2.63E-2</v>
+      </c>
+      <c r="P25" s="38">
+        <f>O25*M25</f>
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="49"/>
+    </row>
+    <row r="26" spans="1:18" s="82" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="80"/>
+      <c r="B26" s="40">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="H26" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="I26" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J26" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="K26" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L26" s="44">
+        <v>1</v>
+      </c>
+      <c r="M26" s="44">
+        <v>5</v>
+      </c>
+      <c r="N26" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O26" s="45">
+        <v>9.8199999999999996E-2</v>
+      </c>
+      <c r="P26" s="45">
+        <f t="shared" ref="P26" si="8">O26*M26</f>
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="49"/>
+    </row>
+    <row r="27" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="80"/>
+      <c r="B27" s="39">
+        <f>ROW(B27) - ROW($B$9)</f>
+        <v>18</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="K27" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L27" s="37">
+        <v>2</v>
+      </c>
+      <c r="M27" s="37">
+        <v>20</v>
+      </c>
+      <c r="N27" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O27" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="P27" s="38">
+        <f>O27*M27</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="49"/>
+    </row>
+    <row r="28" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="80"/>
+      <c r="B28" s="40">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>222</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="K28" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L28" s="44">
+        <v>1</v>
+      </c>
+      <c r="M28" s="44">
+        <v>50</v>
+      </c>
+      <c r="N28" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O28" s="45">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="P28" s="45">
+        <f t="shared" ref="P28" si="9">O28*M28</f>
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="49"/>
+    </row>
+    <row r="29" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="80"/>
+      <c r="B29" s="39">
+        <f>ROW(B29) - ROW($B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="K29" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L29" s="37">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <v>5</v>
+      </c>
+      <c r="N29" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O29" s="38">
+        <v>0.2213</v>
+      </c>
+      <c r="P29" s="38">
+        <f>O29*M29</f>
+        <v>1.1065</v>
+      </c>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="49"/>
+    </row>
+    <row r="30" spans="1:18" s="82" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A30" s="80"/>
+      <c r="B30" s="40">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="I30" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J30" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="K30" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L30" s="44">
+        <v>2</v>
+      </c>
+      <c r="M30" s="44">
+        <v>20</v>
+      </c>
+      <c r="N30" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O30" s="45">
+        <v>3.39E-2</v>
+      </c>
+      <c r="P30" s="45">
+        <f t="shared" ref="P30" si="10">O30*M30</f>
+        <v>0.67799999999999994</v>
+      </c>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="49"/>
+    </row>
+    <row r="31" spans="1:18" s="82" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="80"/>
+      <c r="B31" s="39">
+        <f>ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="K31" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L31" s="37">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <v>2</v>
+      </c>
+      <c r="N31" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O31" s="38">
+        <v>1.4796</v>
+      </c>
+      <c r="P31" s="38">
+        <f>O31*M31</f>
+        <v>2.9592000000000001</v>
+      </c>
+      <c r="Q31" s="37"/>
+      <c r="R31" s="49"/>
+    </row>
+    <row r="32" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="80"/>
+      <c r="B32" s="40">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="51"/>
+      <c r="D32" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J32" s="44" t="s">
+        <v>343</v>
+      </c>
+      <c r="K32" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L32" s="44">
+        <v>1</v>
+      </c>
+      <c r="M32" s="44">
+        <v>2</v>
+      </c>
+      <c r="N32" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O32" s="45">
+        <v>0.9546</v>
+      </c>
+      <c r="P32" s="45">
+        <f t="shared" ref="P32" si="11">O32*M32</f>
+        <v>1.9092</v>
+      </c>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="49"/>
+    </row>
+    <row r="33" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="80"/>
+      <c r="B33" s="39">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="K33" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <v>10</v>
+      </c>
+      <c r="N33" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O33" s="38">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="P33" s="38">
+        <f>O33*M33</f>
+        <v>0.41300000000000003</v>
+      </c>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="49"/>
+    </row>
+    <row r="34" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="80"/>
+      <c r="B34" s="40">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J34" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="K34" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L34" s="44">
+        <v>1</v>
+      </c>
+      <c r="M34" s="44">
+        <v>2</v>
+      </c>
+      <c r="N34" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O34" s="45">
+        <v>0.29110000000000003</v>
+      </c>
+      <c r="P34" s="45">
+        <f t="shared" ref="P34" si="12">O34*M34</f>
+        <v>0.58220000000000005</v>
+      </c>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="49"/>
+    </row>
+    <row r="35" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="80"/>
+      <c r="B35" s="39">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="G35" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="I35" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="J35" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="K35" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="L35" s="54">
+        <v>13</v>
+      </c>
+      <c r="M35" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="N35" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="O35" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="P35" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="58"/>
+    </row>
+    <row r="36" spans="1:18" s="82" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A36" s="80"/>
+      <c r="B36" s="40">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="H36" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="I36" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J36" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="K36" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L36" s="44">
+        <v>1</v>
+      </c>
+      <c r="M36" s="44">
+        <v>10</v>
+      </c>
+      <c r="N36" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O36" s="45">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="P36" s="45">
+        <f t="shared" ref="P36" si="13">O36*M36</f>
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="49"/>
+    </row>
+    <row r="37" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="80"/>
+      <c r="B37" s="39">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="K37" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="L37" s="37">
+        <v>1</v>
+      </c>
+      <c r="M37" s="37">
+        <v>20</v>
+      </c>
+      <c r="N37" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O37" s="38">
+        <v>3.49E-2</v>
+      </c>
+      <c r="P37" s="38">
+        <f>O37*M37</f>
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="Q37" s="37"/>
+      <c r="R37" s="49"/>
+    </row>
+    <row r="38" spans="1:18" s="82" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A38" s="80"/>
+      <c r="B38" s="40">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="E38" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="H38" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I38" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J38" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="K38" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="L38" s="44">
+        <v>10</v>
+      </c>
+      <c r="M38" s="44">
+        <v>100</v>
+      </c>
+      <c r="N38" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O38" s="45">
+        <v>1E-3</v>
+      </c>
+      <c r="P38" s="45">
+        <f t="shared" ref="P38" si="14">O38*M38</f>
+        <v>0.1</v>
+      </c>
+      <c r="Q38" s="91" t="s">
+        <v>357</v>
+      </c>
+      <c r="R38" s="49"/>
+    </row>
+    <row r="39" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="80"/>
+      <c r="B39" s="39">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="L39" s="37">
+        <v>3</v>
+      </c>
+      <c r="M39" s="37">
+        <v>100</v>
+      </c>
+      <c r="N39" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O39" s="38">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P39" s="38">
+        <f>O39*M39</f>
+        <v>0.12</v>
+      </c>
+      <c r="Q39" s="37"/>
+      <c r="R39" s="49"/>
+    </row>
+    <row r="40" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="80"/>
+      <c r="B40" s="40">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="H40" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I40" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J40" s="44" t="s">
+        <v>344</v>
+      </c>
+      <c r="K40" s="44" t="s">
+        <v>312</v>
+      </c>
+      <c r="L40" s="44">
+        <v>3</v>
+      </c>
+      <c r="M40" s="44">
+        <v>100</v>
+      </c>
+      <c r="N40" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O40" s="45">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P40" s="45">
+        <f t="shared" ref="P40" si="15">O40*M40</f>
+        <v>0.11</v>
+      </c>
+      <c r="Q40" s="44"/>
+      <c r="R40" s="49"/>
+    </row>
+    <row r="41" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="80"/>
+      <c r="B41" s="39">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="K41" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="L41" s="37">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <v>100</v>
+      </c>
+      <c r="N41" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O41" s="38">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P41" s="38">
+        <f>O41*M41</f>
+        <v>0.12</v>
+      </c>
+      <c r="Q41" s="37"/>
+      <c r="R41" s="49"/>
+    </row>
+    <row r="42" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="80"/>
+      <c r="B42" s="39">
+        <f>ROW(B42) - ROW($B$9)</f>
+        <v>33</v>
+      </c>
+      <c r="C42" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I42" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="K42" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="L42" s="37">
+        <v>2</v>
+      </c>
+      <c r="M42" s="37">
+        <v>100</v>
+      </c>
+      <c r="N42" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O42" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P42" s="38">
+        <f>O42*M42</f>
+        <v>0.11</v>
+      </c>
+      <c r="Q42" s="37"/>
+      <c r="R42" s="49"/>
+    </row>
+    <row r="43" spans="1:18" s="82" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A43" s="80"/>
+      <c r="B43" s="40">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C43" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="44" t="s">
+        <v>353</v>
+      </c>
+      <c r="F43" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="H43" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I43" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J43" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="K43" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="L43" s="44">
+        <v>1</v>
+      </c>
+      <c r="M43" s="44">
+        <v>20</v>
+      </c>
+      <c r="N43" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O43" s="45">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="P43" s="45">
+        <f t="shared" ref="P43" si="16">O43*M43</f>
+        <v>0.55399999999999994</v>
+      </c>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="49"/>
+    </row>
+    <row r="44" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="80"/>
+      <c r="B44" s="39">
+        <f>ROW(B44) - ROW($B$9)</f>
+        <v>35</v>
+      </c>
+      <c r="C44" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G44" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H44" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I44" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J44" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="K44" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="L44" s="37">
+        <v>5</v>
+      </c>
+      <c r="M44" s="37">
+        <v>100</v>
+      </c>
+      <c r="N44" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O44" s="38">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P44" s="38">
+        <f>O44*M44</f>
+        <v>0.12</v>
+      </c>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="49"/>
+    </row>
+    <row r="45" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="80"/>
+      <c r="B45" s="40">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="F45" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G45" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H45" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I45" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J45" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="K45" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="L45" s="44">
+        <v>2</v>
+      </c>
+      <c r="M45" s="44">
+        <v>100</v>
+      </c>
+      <c r="N45" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O45" s="45">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="P45" s="45">
+        <f t="shared" ref="P45" si="17">O45*M45</f>
+        <v>0.31</v>
+      </c>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="49"/>
+    </row>
+    <row r="46" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="80"/>
+      <c r="B46" s="39">
+        <f>ROW(B46) - ROW($B$9)</f>
+        <v>37</v>
+      </c>
+      <c r="C46" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="L46" s="37">
+        <v>3</v>
+      </c>
+      <c r="M46" s="37">
+        <v>100</v>
+      </c>
+      <c r="N46" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O46" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="P46" s="38">
+        <f>O46*M46</f>
+        <v>0.11</v>
+      </c>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="49"/>
+    </row>
+    <row r="47" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="80"/>
+      <c r="B47" s="40">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C47" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F47" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="H47" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I47" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J47" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="K47" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="L47" s="44">
+        <v>2</v>
+      </c>
+      <c r="M47" s="44">
+        <v>100</v>
+      </c>
+      <c r="N47" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O47" s="45">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P47" s="45">
+        <f t="shared" ref="P47" si="18">O47*M47</f>
+        <v>0.12</v>
+      </c>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="49"/>
+    </row>
+    <row r="48" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="80"/>
+      <c r="B48" s="39">
+        <f>ROW(B48) - ROW($B$9)</f>
+        <v>39</v>
+      </c>
+      <c r="C48" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="F48" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G48" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="H48" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I48" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J48" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="K48" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="L48" s="37">
+        <v>2</v>
+      </c>
+      <c r="M48" s="37">
+        <v>100</v>
+      </c>
+      <c r="N48" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O48" s="38">
+        <v>1.8E-3</v>
+      </c>
+      <c r="P48" s="38">
+        <f>O48*M48</f>
+        <v>0.18</v>
+      </c>
+      <c r="Q48" s="37"/>
+      <c r="R48" s="49"/>
+    </row>
+    <row r="49" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="80"/>
+      <c r="B49" s="40">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C49" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="F49" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="H49" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I49" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J49" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="K49" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="L49" s="44">
+        <v>1</v>
+      </c>
+      <c r="M49" s="44">
+        <v>20</v>
+      </c>
+      <c r="N49" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O49" s="45">
+        <v>2.75E-2</v>
+      </c>
+      <c r="P49" s="45">
+        <f t="shared" ref="P49" si="19">O49*M49</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Q49" s="44"/>
+      <c r="R49" s="49"/>
+    </row>
+    <row r="50" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="80"/>
+      <c r="B50" s="39">
+        <f>ROW(B50) - ROW($B$9)</f>
+        <v>41</v>
+      </c>
+      <c r="C50" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F50" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="H50" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I50" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J50" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="K50" s="37" t="s">
+        <v>322</v>
+      </c>
+      <c r="L50" s="37">
+        <v>1</v>
+      </c>
+      <c r="M50" s="37">
+        <v>50</v>
+      </c>
+      <c r="N50" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O50" s="38">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="P50" s="38">
+        <f>O50*M50</f>
+        <v>0.44</v>
+      </c>
+      <c r="Q50" s="37"/>
+      <c r="R50" s="49"/>
+    </row>
+    <row r="51" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="80"/>
+      <c r="B51" s="40">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C51" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="F51" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="H51" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="I51" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J51" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="K51" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="L51" s="44">
+        <v>1</v>
+      </c>
+      <c r="M51" s="44">
+        <v>20</v>
+      </c>
+      <c r="N51" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O51" s="45">
+        <v>2.63E-2</v>
+      </c>
+      <c r="P51" s="45">
+        <f t="shared" ref="P51" si="20">O51*M51</f>
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="49"/>
+    </row>
+    <row r="52" spans="1:18" s="90" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="83"/>
+      <c r="B52" s="84">
+        <f>ROW(B52) - ROW($B$9)</f>
+        <v>43</v>
+      </c>
+      <c r="C52" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="F52" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="G52" s="86" t="s">
+        <v>205</v>
+      </c>
+      <c r="H52" s="86" t="s">
+        <v>219</v>
+      </c>
+      <c r="I52" s="86" t="s">
+        <v>328</v>
+      </c>
+      <c r="J52" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="K52" s="86" t="s">
+        <v>324</v>
+      </c>
+      <c r="L52" s="86">
+        <v>1</v>
+      </c>
+      <c r="M52" s="86">
+        <v>20</v>
+      </c>
+      <c r="N52" s="87" t="s">
+        <v>342</v>
+      </c>
+      <c r="O52" s="88">
+        <v>3.1E-2</v>
+      </c>
+      <c r="P52" s="88">
+        <f>O52*M52</f>
+        <v>0.62</v>
+      </c>
+      <c r="Q52" s="86"/>
+      <c r="R52" s="89"/>
+    </row>
+    <row r="53" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="80"/>
+      <c r="B53" s="40">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="F53" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="H53" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="I53" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J53" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="K53" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="L53" s="44">
+        <v>1</v>
+      </c>
+      <c r="M53" s="44">
+        <v>100</v>
+      </c>
+      <c r="N53" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O53" s="45">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P53" s="45">
+        <f t="shared" ref="P53" si="21">O53*M53</f>
+        <v>0.12</v>
+      </c>
+      <c r="Q53" s="44"/>
+      <c r="R53" s="49"/>
+    </row>
+    <row r="54" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="80"/>
+      <c r="B54" s="39">
+        <f>ROW(B54) - ROW($B$9)</f>
+        <v>45</v>
+      </c>
+      <c r="C54" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="54" t="s">
+        <v>329</v>
+      </c>
+      <c r="G54" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="H54" s="55" t="s">
+        <v>328</v>
+      </c>
+      <c r="I54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="J54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="K54" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="L54" s="54">
+        <v>3</v>
+      </c>
+      <c r="M54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="N54" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="O54" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="P54" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q54" s="54"/>
+      <c r="R54" s="58"/>
+    </row>
+    <row r="55" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="80"/>
+      <c r="B55" s="40">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="F55" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="G55" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="H55" s="44" t="s">
+        <v>234</v>
+      </c>
+      <c r="I55" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J55" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="K55" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L55" s="44">
+        <v>5</v>
+      </c>
+      <c r="M55" s="44">
+        <v>10</v>
+      </c>
+      <c r="N55" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O55" s="45">
+        <v>0.3135</v>
+      </c>
+      <c r="P55" s="45">
+        <f t="shared" ref="P55:P56" si="22">O55*M55</f>
+        <v>3.1349999999999998</v>
+      </c>
+      <c r="Q55" s="44"/>
+      <c r="R55" s="49"/>
+    </row>
+    <row r="56" spans="1:18" s="82" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A56" s="80"/>
+      <c r="B56" s="40">
+        <f>ROW(B56) - ROW($B$9)</f>
+        <v>47</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="E56" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F56" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="H56" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="I56" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J56" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="K56" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L56" s="44">
+        <v>1</v>
+      </c>
+      <c r="M56" s="44">
+        <v>10</v>
+      </c>
+      <c r="N56" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O56" s="45">
+        <v>6.2100000000000002E-2</v>
+      </c>
+      <c r="P56" s="45">
+        <f t="shared" si="22"/>
+        <v>0.621</v>
+      </c>
+      <c r="Q56" s="44"/>
+      <c r="R56" s="49"/>
+    </row>
+    <row r="57" spans="1:18" s="82" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A57" s="80"/>
+      <c r="B57" s="39">
+        <f>ROW(B57) - ROW($B$9)</f>
+        <v>48</v>
+      </c>
+      <c r="C57" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="G57" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L57" s="37">
+        <v>1</v>
+      </c>
+      <c r="M57" s="37">
+        <v>2</v>
+      </c>
+      <c r="N57" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O57" s="38">
+        <v>0.16209999999999999</v>
+      </c>
+      <c r="P57" s="38">
+        <f>O57*M57</f>
+        <v>0.32419999999999999</v>
+      </c>
+      <c r="Q57" s="37"/>
+      <c r="R57" s="49"/>
+    </row>
+    <row r="58" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="80"/>
+      <c r="B58" s="40">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C58" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="F58" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="G58" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="H58" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="I58" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J58" s="44" t="s">
+        <v>348</v>
+      </c>
+      <c r="K58" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L58" s="44">
+        <v>1</v>
+      </c>
+      <c r="M58" s="44">
+        <v>5</v>
+      </c>
+      <c r="N58" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O58" s="45">
+        <v>0.1341</v>
+      </c>
+      <c r="P58" s="45">
+        <f t="shared" ref="P58" si="23">O58*M58</f>
+        <v>0.67049999999999998</v>
+      </c>
+      <c r="Q58" s="44"/>
+      <c r="R58" s="49"/>
+    </row>
+    <row r="59" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A59" s="80"/>
+      <c r="B59" s="39">
+        <f>ROW(B59) - ROW($B$9)</f>
+        <v>50</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="G59" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="H59" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="I59" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J59" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="K59" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L59" s="37">
+        <v>1</v>
+      </c>
+      <c r="M59" s="37">
+        <v>5</v>
+      </c>
+      <c r="N59" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O59" s="38">
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="P59" s="38">
+        <f>O59*M59</f>
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="Q59" s="37"/>
+      <c r="R59" s="49"/>
+    </row>
+    <row r="60" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A60" s="80"/>
+      <c r="B60" s="40">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="G60" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="H60" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="I60" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J60" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="K60" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L60" s="44">
+        <v>1</v>
+      </c>
+      <c r="M60" s="44">
+        <v>2</v>
+      </c>
+      <c r="N60" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O60" s="45">
+        <v>0.43909999999999999</v>
+      </c>
+      <c r="P60" s="45">
+        <f t="shared" ref="P60" si="24">O60*M60</f>
+        <v>0.87819999999999998</v>
+      </c>
+      <c r="Q60" s="44"/>
+      <c r="R60" s="49"/>
+    </row>
+    <row r="61" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A61" s="80"/>
+      <c r="B61" s="39">
+        <f>ROW(B61) - ROW($B$9)</f>
+        <v>52</v>
+      </c>
+      <c r="C61" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="G61" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J61" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="K61" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L61" s="37">
+        <v>1</v>
+      </c>
+      <c r="M61" s="37">
+        <v>5</v>
+      </c>
+      <c r="N61" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O61" s="38">
+        <v>0.15479999999999999</v>
+      </c>
+      <c r="P61" s="38">
+        <f>O61*M61</f>
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="Q61" s="37"/>
+      <c r="R61" s="49"/>
+    </row>
+    <row r="62" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A62" s="80"/>
+      <c r="B62" s="39">
+        <f>ROW(B62) - ROW($B$9)</f>
+        <v>53</v>
+      </c>
+      <c r="C62" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F62" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="G62" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="H62" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="I62" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J62" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="K62" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L62" s="37">
+        <v>1</v>
+      </c>
+      <c r="M62" s="37">
+        <v>2</v>
+      </c>
+      <c r="N62" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O62" s="38">
+        <v>5.1212</v>
+      </c>
+      <c r="P62" s="38">
+        <f>O62*M62</f>
+        <v>10.2424</v>
+      </c>
+      <c r="Q62" s="37"/>
+      <c r="R62" s="49"/>
+    </row>
+    <row r="63" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A63" s="80"/>
+      <c r="B63" s="40">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C63" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="E63" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="F63" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="G63" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="H63" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="I63" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J63" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="K63" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L63" s="44">
+        <v>1</v>
+      </c>
+      <c r="M63" s="44">
+        <v>5</v>
+      </c>
+      <c r="N63" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O63" s="45">
+        <v>0.15670000000000001</v>
+      </c>
+      <c r="P63" s="45">
+        <f t="shared" ref="P63" si="25">O63*M63</f>
+        <v>0.78350000000000009</v>
+      </c>
+      <c r="Q63" s="44"/>
+      <c r="R63" s="49"/>
+    </row>
+    <row r="64" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A64" s="80"/>
+      <c r="B64" s="39">
+        <f>ROW(B64) - ROW($B$9)</f>
+        <v>55</v>
+      </c>
+      <c r="C64" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="F64" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="G64" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="H64" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="I64" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J64" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="K64" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L64" s="37">
+        <v>1</v>
+      </c>
+      <c r="M64" s="37">
+        <v>2</v>
+      </c>
+      <c r="N64" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O64" s="38">
+        <v>0.96889999999999998</v>
+      </c>
+      <c r="P64" s="38">
+        <f>O64*M64</f>
+        <v>1.9378</v>
+      </c>
+      <c r="Q64" s="37"/>
+      <c r="R64" s="49"/>
+    </row>
+    <row r="65" spans="1:18" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="80"/>
+      <c r="B65" s="40">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C65" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="F65" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="G65" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="H65" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="I65" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="J65" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="K65" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L65" s="44">
+        <v>1</v>
+      </c>
+      <c r="M65" s="44">
+        <v>2</v>
+      </c>
+      <c r="N65" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O65" s="45">
+        <v>0.28870000000000001</v>
+      </c>
+      <c r="P65" s="45">
+        <f t="shared" ref="P65" si="26">O65*M65</f>
+        <v>0.57740000000000002</v>
+      </c>
+      <c r="Q65" s="44"/>
+      <c r="R65" s="49"/>
+    </row>
+    <row r="66" spans="1:18" s="82" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A66" s="80"/>
+      <c r="B66" s="39">
+        <f>ROW(B66) - ROW($B$9)</f>
+        <v>57</v>
+      </c>
+      <c r="C66" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="F66" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="G66" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="I66" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="K66" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="L66" s="37">
+        <v>1</v>
+      </c>
+      <c r="M66" s="37">
+        <v>2</v>
+      </c>
+      <c r="N66" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="O66" s="38">
+        <v>2.0651000000000002</v>
+      </c>
+      <c r="P66" s="38">
+        <f>O66*M66</f>
+        <v>4.1302000000000003</v>
+      </c>
+      <c r="Q66" s="37"/>
+      <c r="R66" s="49"/>
+    </row>
+    <row r="67" spans="1:18" s="82" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="80"/>
+      <c r="B67" s="59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C67" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="G67" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="H67" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="I67" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="J67" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="K67" s="61" t="s">
+        <v>328</v>
+      </c>
+      <c r="L67" s="49">
+        <v>1</v>
+      </c>
+      <c r="M67" s="49">
+        <v>2</v>
+      </c>
+      <c r="N67" s="62" t="s">
+        <v>342</v>
+      </c>
+      <c r="O67" s="63">
+        <v>1.2919</v>
+      </c>
+      <c r="P67" s="63">
+        <f t="shared" ref="P67" si="27">O67*M67</f>
+        <v>2.5838000000000001</v>
+      </c>
+      <c r="Q67" s="49"/>
+      <c r="R67" s="49"/>
+    </row>
+    <row r="68" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="93"/>
+      <c r="C68" s="94"/>
+      <c r="D68" s="95"/>
+      <c r="E68" s="96"/>
+      <c r="F68" s="97"/>
+      <c r="G68" s="98"/>
+      <c r="H68" s="97"/>
+      <c r="I68" s="98"/>
+      <c r="J68" s="97"/>
+      <c r="K68" s="98"/>
+      <c r="L68" s="98"/>
+      <c r="M68" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="N68" s="79"/>
+      <c r="O68" s="79"/>
+      <c r="P68" s="41">
+        <f>SUM(P10:P67)</f>
+        <v>55.211800000000011</v>
+      </c>
+      <c r="Q68" s="99"/>
+      <c r="R68" s="100"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="R3:R8"/>
+    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="Q68:R68"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="N10" r:id="rId1"/>
+    <hyperlink ref="N11" r:id="rId2"/>
+    <hyperlink ref="N12" r:id="rId3"/>
+    <hyperlink ref="N13" r:id="rId4"/>
+    <hyperlink ref="N14" r:id="rId5"/>
+    <hyperlink ref="N15" r:id="rId6"/>
+    <hyperlink ref="N16" r:id="rId7"/>
+    <hyperlink ref="N17" r:id="rId8"/>
+    <hyperlink ref="N19" r:id="rId9"/>
+    <hyperlink ref="N20" r:id="rId10"/>
+    <hyperlink ref="N21" r:id="rId11"/>
+    <hyperlink ref="N22" r:id="rId12"/>
+    <hyperlink ref="N23" r:id="rId13"/>
+    <hyperlink ref="N24" r:id="rId14"/>
+    <hyperlink ref="N25" r:id="rId15"/>
+    <hyperlink ref="N26" r:id="rId16"/>
+    <hyperlink ref="N27" r:id="rId17"/>
+    <hyperlink ref="N28" r:id="rId18"/>
+    <hyperlink ref="N29" r:id="rId19"/>
+    <hyperlink ref="N30" r:id="rId20"/>
+    <hyperlink ref="N31" r:id="rId21"/>
+    <hyperlink ref="N32" r:id="rId22"/>
+    <hyperlink ref="N33" r:id="rId23"/>
+    <hyperlink ref="N34" r:id="rId24"/>
+    <hyperlink ref="N36" r:id="rId25"/>
+    <hyperlink ref="N37" r:id="rId26"/>
+    <hyperlink ref="N38" r:id="rId27"/>
+    <hyperlink ref="N39" r:id="rId28"/>
+    <hyperlink ref="N40" r:id="rId29"/>
+    <hyperlink ref="N41" r:id="rId30"/>
+    <hyperlink ref="N42" r:id="rId31"/>
+    <hyperlink ref="N44" r:id="rId32"/>
+    <hyperlink ref="N45" r:id="rId33"/>
+    <hyperlink ref="N46" r:id="rId34"/>
+    <hyperlink ref="N47" r:id="rId35"/>
+    <hyperlink ref="N48" r:id="rId36"/>
+    <hyperlink ref="N49" r:id="rId37"/>
+    <hyperlink ref="N50" r:id="rId38"/>
+    <hyperlink ref="N51" r:id="rId39"/>
+    <hyperlink ref="N52" r:id="rId40"/>
+    <hyperlink ref="N53" r:id="rId41"/>
+    <hyperlink ref="N55" r:id="rId42"/>
+    <hyperlink ref="N56" r:id="rId43"/>
+    <hyperlink ref="N57" r:id="rId44"/>
+    <hyperlink ref="N59" r:id="rId45"/>
+    <hyperlink ref="N60" r:id="rId46"/>
+    <hyperlink ref="N61" r:id="rId47"/>
+    <hyperlink ref="N62" r:id="rId48"/>
+    <hyperlink ref="N63" r:id="rId49"/>
+    <hyperlink ref="N64" r:id="rId50"/>
+    <hyperlink ref="N65" r:id="rId51"/>
+    <hyperlink ref="N66" r:id="rId52"/>
+    <hyperlink ref="N67" r:id="rId53"/>
+    <hyperlink ref="N18" r:id="rId54"/>
+    <hyperlink ref="N58" r:id="rId55"/>
+    <hyperlink ref="N43" r:id="rId56"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId57"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S69"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -3995,7 +7492,9 @@
         <f t="shared" ref="Q38" si="30">P38*N38</f>
         <v>0.1</v>
       </c>
-      <c r="R38" s="44"/>
+      <c r="R38" s="91" t="s">
+        <v>357</v>
+      </c>
       <c r="S38" s="49"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
@@ -5672,6 +9171,9 @@
       </c>
       <c r="R69" s="76"/>
       <c r="S69" s="77"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P70" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="346">
   <si>
     <t>Component list</t>
   </si>
@@ -655,9 +655,6 @@
     <t>C106256</t>
   </si>
   <si>
-    <t>C2936601</t>
-  </si>
-  <si>
     <t>C338080</t>
   </si>
   <si>
@@ -1022,6 +1019,45 @@
   </si>
   <si>
     <t>C431873</t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>Terminal Block Cable</t>
+  </si>
+  <si>
+    <t>Dupont Cable/Terminal Block Cable/Electronic Cable ROHS</t>
+  </si>
+  <si>
+    <t>LDR100-157128-150-5P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEALON </t>
+  </si>
+  <si>
+    <t>C2998992</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>This part provide by client.</t>
+  </si>
+  <si>
+    <t>WF12P5R60FTL</t>
+  </si>
+  <si>
+    <t>CL10A106MO8NQNC</t>
+  </si>
+  <si>
+    <t>C92487</t>
+  </si>
+  <si>
+    <t>DNP</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1069,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1209,8 +1245,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1235,8 +1279,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1492,12 +1542,112 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1727,6 +1877,66 @@
     <xf numFmtId="166" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1763,6 +1973,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2160,11 +2382,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S64"/>
+  <dimension ref="A1:S68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.5703125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
@@ -2178,7 +2400,7 @@
     <col min="14" max="14" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2193,14 +2415,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="84"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="104"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2211,7 +2433,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2235,7 +2457,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2248,7 +2470,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
-      <c r="R3" s="85"/>
+      <c r="R3" s="105"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2259,7 +2481,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2272,7 +2494,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="86"/>
+      <c r="R4" s="106"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2296,7 +2518,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
-      <c r="R5" s="86"/>
+      <c r="R5" s="106"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2316,7 +2538,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="86"/>
+      <c r="R6" s="106"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2336,7 +2558,7 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="86"/>
+      <c r="R7" s="106"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2356,7 +2578,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
-      <c r="R8" s="86"/>
+      <c r="R8" s="106"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2382,34 +2604,34 @@
         <v>182</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J9" s="30" t="s">
         <v>205</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="N9" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="P9" s="30" t="s">
-        <v>299</v>
-      </c>
       <c r="Q9" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="R9" s="30" t="s">
         <v>282</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -2422,7 +2644,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>67</v>
@@ -2437,13 +2659,13 @@
         <v>183</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>206</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -2452,7 +2674,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O10" s="38">
         <v>1.89E-2</v>
@@ -2467,7 +2689,7 @@
     <row r="11" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="40">
-        <f t="shared" ref="B11:B63" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B67" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="50" t="s">
@@ -2489,13 +2711,13 @@
         <v>184</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J11" s="44" t="s">
         <v>207</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L11" s="44">
         <v>2</v>
@@ -2504,9 +2726,9 @@
         <v>3</v>
       </c>
       <c r="N11" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="O11" s="45">
+        <v>285</v>
+      </c>
+      <c r="O11" s="117">
         <v>1.4064000000000001</v>
       </c>
       <c r="P11" s="45">
@@ -2541,13 +2763,13 @@
         <v>183</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J12" s="37" t="s">
         <v>208</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L12" s="37">
         <v>14</v>
@@ -2556,7 +2778,7 @@
         <v>100</v>
       </c>
       <c r="N12" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O12" s="38">
         <v>5.0000000000000001E-3</v>
@@ -2593,13 +2815,13 @@
         <v>183</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J13" s="44" t="s">
         <v>209</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L13" s="44">
         <v>1</v>
@@ -2608,7 +2830,7 @@
         <v>100</v>
       </c>
       <c r="N13" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O13" s="45">
         <v>2.8E-3</v>
@@ -2630,7 +2852,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>71</v>
@@ -2645,13 +2867,13 @@
         <v>183</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>210</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L14" s="37">
         <v>22</v>
@@ -2660,7 +2882,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O14" s="38">
         <v>1.8E-3</v>
@@ -2690,36 +2912,36 @@
       <c r="F15" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="56" t="s">
         <v>147</v>
       </c>
       <c r="H15" s="44" t="s">
         <v>183</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>211</v>
+        <v>344</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L15" s="44">
         <v>2</v>
       </c>
       <c r="M15" s="44">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N15" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O15" s="45">
-        <v>0.16370000000000001</v>
+        <v>1.77E-2</v>
       </c>
       <c r="P15" s="45">
         <f t="shared" ref="P15" si="3">O15*M15</f>
-        <v>0.81850000000000001</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="Q15" s="44"/>
       <c r="R15" s="49"/>
@@ -2749,13 +2971,13 @@
         <v>185</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L16" s="37">
         <v>2</v>
@@ -2764,12 +2986,12 @@
         <v>5</v>
       </c>
       <c r="N16" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O16" s="38">
         <v>0.42320000000000002</v>
       </c>
-      <c r="P16" s="38">
+      <c r="P16" s="81">
         <f>O16*M16</f>
         <v>2.1160000000000001</v>
       </c>
@@ -2801,13 +3023,13 @@
         <v>183</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L17" s="44">
         <v>6</v>
@@ -2816,7 +3038,7 @@
         <v>20</v>
       </c>
       <c r="N17" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O17" s="45">
         <v>2.3800000000000002E-2</v>
@@ -2853,13 +3075,13 @@
         <v>186</v>
       </c>
       <c r="I18" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="J18" s="37" t="s">
         <v>290</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>291</v>
-      </c>
       <c r="K18" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -2868,7 +3090,7 @@
         <v>50</v>
       </c>
       <c r="N18" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O18" s="38">
         <v>5.4999999999999997E-3</v>
@@ -2905,13 +3127,13 @@
         <v>183</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L19" s="44">
         <v>1</v>
@@ -2920,7 +3142,7 @@
         <v>20</v>
       </c>
       <c r="N19" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O19" s="45">
         <v>2.0199999999999999E-2</v>
@@ -2957,13 +3179,13 @@
         <v>183</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L20" s="44">
         <v>2</v>
@@ -2972,7 +3194,7 @@
         <v>100</v>
       </c>
       <c r="N20" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O20" s="45">
         <v>3.7000000000000002E-3</v>
@@ -3009,13 +3231,13 @@
         <v>183</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L21" s="37">
         <v>2</v>
@@ -3024,7 +3246,7 @@
         <v>100</v>
       </c>
       <c r="N21" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O21" s="38">
         <v>4.4999999999999997E-3</v>
@@ -3061,13 +3283,13 @@
         <v>183</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L22" s="44">
         <v>1</v>
@@ -3076,7 +3298,7 @@
         <v>100</v>
       </c>
       <c r="N22" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O22" s="45">
         <v>3.2000000000000002E-3</v>
@@ -3113,13 +3335,13 @@
         <v>187</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L23" s="44">
         <v>1</v>
@@ -3128,7 +3350,7 @@
         <v>5</v>
       </c>
       <c r="N23" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O23" s="45">
         <v>8.6400000000000005E-2</v>
@@ -3165,13 +3387,13 @@
         <v>188</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -3180,7 +3402,7 @@
         <v>20</v>
       </c>
       <c r="N24" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O24" s="38">
         <v>2.63E-2</v>
@@ -3202,28 +3424,28 @@
         <v>10</v>
       </c>
       <c r="D25" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="E25" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="F25" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="G25" s="44" t="s">
         <v>304</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>305</v>
       </c>
       <c r="H25" s="44" t="s">
         <v>188</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L25" s="44">
         <v>1</v>
@@ -3232,7 +3454,7 @@
         <v>20</v>
       </c>
       <c r="N25" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O25" s="44">
         <v>3.8100000000000002E-2</v>
@@ -3269,13 +3491,13 @@
         <v>186</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L26" s="37">
         <v>2</v>
@@ -3284,7 +3506,7 @@
         <v>20</v>
       </c>
       <c r="N26" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O26" s="38">
         <v>3.2199999999999999E-2</v>
@@ -3321,13 +3543,13 @@
         <v>186</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L27" s="44">
         <v>1</v>
@@ -3336,7 +3558,7 @@
         <v>50</v>
       </c>
       <c r="N27" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O27" s="45">
         <v>8.8999999999999999E-3</v>
@@ -3355,25 +3577,31 @@
         <v>19</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D28" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E28" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="G28" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>271</v>
+      </c>
       <c r="K28" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3381,11 +3609,14 @@
       <c r="M28" s="37">
         <v>5</v>
       </c>
-      <c r="N28" s="52"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38">
-        <f>O28*M28</f>
-        <v>0</v>
+      <c r="N28" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="O28" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="P28" s="38" t="s">
+        <v>271</v>
       </c>
       <c r="Q28" s="37"/>
       <c r="R28" s="49"/>
@@ -3400,28 +3631,28 @@
         <v>13</v>
       </c>
       <c r="D29" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="E29" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="F29" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="G29" s="44" t="s">
         <v>311</v>
       </c>
-      <c r="F29" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="G29" s="44" t="s">
+      <c r="H29" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="I29" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="J29" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="I29" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>314</v>
-      </c>
       <c r="K29" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L29" s="44">
         <v>3</v>
@@ -3430,7 +3661,7 @@
         <v>20</v>
       </c>
       <c r="N29" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O29" s="45">
         <v>2.52E-2</v>
@@ -3442,7 +3673,7 @@
       <c r="Q29" s="44"/>
       <c r="R29" s="49"/>
     </row>
-    <row r="30" spans="1:18" s="72" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="70"/>
       <c r="B30" s="39">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -3458,7 +3689,7 @@
         <v>84</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>122</v>
@@ -3467,13 +3698,13 @@
         <v>189</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3482,16 +3713,17 @@
         <v>2</v>
       </c>
       <c r="N30" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="O30" s="38">
-        <v>1.4796</v>
-      </c>
-      <c r="P30" s="38">
-        <f>O30*M30</f>
-        <v>2.9592000000000001</v>
-      </c>
-      <c r="Q30" s="37"/>
+        <v>285</v>
+      </c>
+      <c r="O30" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="P30" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q30" s="118" t="s">
+        <v>345</v>
+      </c>
       <c r="R30" s="49"/>
     </row>
     <row r="31" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3501,7 +3733,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D31" s="44" t="s">
         <v>39</v>
@@ -3510,7 +3742,7 @@
         <v>85</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G31" s="44" t="s">
         <v>123</v>
@@ -3519,13 +3751,13 @@
         <v>189</v>
       </c>
       <c r="I31" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J31" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L31" s="44">
         <v>1</v>
@@ -3534,7 +3766,7 @@
         <v>2</v>
       </c>
       <c r="N31" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O31" s="45">
         <v>0.9546</v>
@@ -3553,31 +3785,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="D32" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="E32" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="F32" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="G32" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="F32" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G32" s="37" t="s">
+      <c r="H32" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="H32" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>319</v>
-      </c>
       <c r="K32" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3586,7 +3818,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O32" s="38">
         <v>3.8199999999999998E-2</v>
@@ -3614,7 +3846,7 @@
         <v>86</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G33" s="44" t="s">
         <v>124</v>
@@ -3623,13 +3855,13 @@
         <v>190</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J33" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L33" s="44">
         <v>1</v>
@@ -3638,7 +3870,7 @@
         <v>2</v>
       </c>
       <c r="N33" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O33" s="45">
         <v>0.29110000000000003</v>
@@ -3666,37 +3898,37 @@
         <v>87</v>
       </c>
       <c r="F34" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="G34" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="G34" s="54" t="s">
-        <v>274</v>
-      </c>
       <c r="H34" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I34" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J34" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K34" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L34" s="54">
         <v>13</v>
       </c>
       <c r="M34" s="54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N34" s="54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O34" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P34" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q34" s="54"/>
       <c r="R34" s="58"/>
@@ -3726,13 +3958,13 @@
         <v>191</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J35" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L35" s="44">
         <v>1</v>
@@ -3741,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="N35" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O35" s="45">
         <v>4.6899999999999997E-2</v>
@@ -3778,13 +4010,13 @@
         <v>192</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -3793,19 +4025,19 @@
         <v>20</v>
       </c>
       <c r="N36" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O36" s="38">
         <v>3.49E-2</v>
       </c>
-      <c r="P36" s="38">
+      <c r="P36" s="115">
         <f>O36*M36</f>
         <v>0.69799999999999995</v>
       </c>
       <c r="Q36" s="37"/>
       <c r="R36" s="49"/>
     </row>
-    <row r="37" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="70"/>
       <c r="B37" s="40">
         <f t="shared" si="0"/>
@@ -3815,7 +4047,7 @@
         <v>17</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>90</v>
@@ -3830,13 +4062,13 @@
         <v>183</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L37" s="44">
         <v>11</v>
@@ -3845,7 +4077,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O37" s="45">
         <v>1E-3</v>
@@ -3855,7 +4087,7 @@
         <v>0.1</v>
       </c>
       <c r="Q37" s="73" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R37" s="49"/>
     </row>
@@ -3884,13 +4116,13 @@
         <v>183</v>
       </c>
       <c r="I38" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J38" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L38" s="44">
         <v>3</v>
@@ -3899,7 +4131,7 @@
         <v>100</v>
       </c>
       <c r="N38" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O38" s="45">
         <v>1.1000000000000001E-3</v>
@@ -3924,25 +4156,25 @@
         <v>45</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F39" s="44" t="s">
         <v>126</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H39" s="44" t="s">
         <v>183</v>
       </c>
       <c r="I39" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J39" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="K39" s="44" t="s">
         <v>330</v>
-      </c>
-      <c r="K39" s="44" t="s">
-        <v>331</v>
       </c>
       <c r="L39" s="44">
         <v>1</v>
@@ -3951,7 +4183,7 @@
         <v>100</v>
       </c>
       <c r="N39" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O39" s="38">
         <v>1.2999999999999999E-3</v>
@@ -3988,13 +4220,13 @@
         <v>183</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L40" s="37">
         <v>2</v>
@@ -4003,7 +4235,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O40" s="38">
         <v>1.1000000000000001E-3</v>
@@ -4028,25 +4260,25 @@
         <v>47</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F41" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="G41" s="44" t="s">
         <v>293</v>
-      </c>
-      <c r="G41" s="44" t="s">
-        <v>294</v>
       </c>
       <c r="H41" s="44" t="s">
         <v>183</v>
       </c>
       <c r="I41" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J41" s="44" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K41" s="44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L41" s="44">
         <v>1</v>
@@ -4055,7 +4287,7 @@
         <v>20</v>
       </c>
       <c r="N41" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O41" s="45">
         <v>2.7699999999999999E-2</v>
@@ -4092,13 +4324,13 @@
         <v>183</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L42" s="37">
         <v>5</v>
@@ -4107,7 +4339,7 @@
         <v>100</v>
       </c>
       <c r="N42" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O42" s="38">
         <v>1.1999999999999999E-3</v>
@@ -4144,13 +4376,13 @@
         <v>183</v>
       </c>
       <c r="I43" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J43" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L43" s="44">
         <v>2</v>
@@ -4159,7 +4391,7 @@
         <v>100</v>
       </c>
       <c r="N43" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O43" s="45">
         <v>3.0999999999999999E-3</v>
@@ -4196,13 +4428,13 @@
         <v>183</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L44" s="37">
         <v>3</v>
@@ -4211,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="N44" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O44" s="38">
         <v>1.1000000000000001E-3</v>
@@ -4248,13 +4480,13 @@
         <v>183</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L45" s="44">
         <v>2</v>
@@ -4263,7 +4495,7 @@
         <v>100</v>
       </c>
       <c r="N45" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O45" s="45">
         <v>1.1999999999999999E-3</v>
@@ -4300,13 +4532,13 @@
         <v>183</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L46" s="37">
         <v>2</v>
@@ -4315,7 +4547,7 @@
         <v>100</v>
       </c>
       <c r="N46" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O46" s="38">
         <v>1.8E-3</v>
@@ -4352,13 +4584,13 @@
         <v>183</v>
       </c>
       <c r="I47" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J47" s="44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L47" s="44">
         <v>1</v>
@@ -4367,7 +4599,7 @@
         <v>20</v>
       </c>
       <c r="N47" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O47" s="45">
         <v>2.75E-2</v>
@@ -4404,13 +4636,13 @@
         <v>183</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K48" s="37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L48" s="37">
         <v>1</v>
@@ -4419,7 +4651,7 @@
         <v>50</v>
       </c>
       <c r="N48" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O48" s="38">
         <v>8.8000000000000005E-3</v>
@@ -4441,43 +4673,43 @@
         <v>127</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E49" s="54" t="s">
         <v>100</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G49" s="54" t="s">
         <v>127</v>
       </c>
       <c r="H49" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I49" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J49" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K49" s="54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L49" s="54">
         <v>6</v>
       </c>
       <c r="M49" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N49" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O49" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P49" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q49" s="54"/>
       <c r="R49" s="58"/>
@@ -4492,13 +4724,13 @@
         <v>18</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E50" s="44" t="s">
         <v>101</v>
       </c>
       <c r="F50" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G50" s="44" t="s">
         <v>128</v>
@@ -4507,13 +4739,13 @@
         <v>193</v>
       </c>
       <c r="I50" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J50" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L50" s="44">
         <v>2</v>
@@ -4522,9 +4754,9 @@
         <v>5</v>
       </c>
       <c r="N50" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="O50" s="45">
+        <v>285</v>
+      </c>
+      <c r="O50" s="117">
         <v>0.3135</v>
       </c>
       <c r="P50" s="45">
@@ -4544,28 +4776,28 @@
         <v>18</v>
       </c>
       <c r="D51" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="F51" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="G51" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="F51" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G51" s="37" t="s">
+      <c r="H51" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="I51" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="I51" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>326</v>
-      </c>
       <c r="K51" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L51" s="37">
         <v>1</v>
@@ -4574,9 +4806,9 @@
         <v>2</v>
       </c>
       <c r="N51" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="O51" s="37">
+        <v>285</v>
+      </c>
+      <c r="O51" s="116">
         <v>0.42799999999999999</v>
       </c>
       <c r="P51" s="38">
@@ -4585,7 +4817,7 @@
       </c>
       <c r="Q51" s="38"/>
       <c r="R51" s="37"/>
-      <c r="S51" s="49"/>
+      <c r="S51" s="72"/>
     </row>
     <row r="52" spans="1:19" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A52" s="70"/>
@@ -4597,13 +4829,13 @@
         <v>18</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E52" s="44" t="s">
         <v>107</v>
       </c>
       <c r="F52" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G52" s="44" t="s">
         <v>134</v>
@@ -4612,13 +4844,13 @@
         <v>199</v>
       </c>
       <c r="I52" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J52" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L52" s="44">
         <v>1</v>
@@ -4627,7 +4859,7 @@
         <v>10</v>
       </c>
       <c r="N52" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O52" s="45">
         <v>6.2100000000000002E-2</v>
@@ -4664,13 +4896,13 @@
         <v>194</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K53" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L53" s="37">
         <v>1</v>
@@ -4679,7 +4911,7 @@
         <v>2</v>
       </c>
       <c r="N53" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O53" s="38">
         <v>0.16209999999999999</v>
@@ -4716,13 +4948,13 @@
         <v>195</v>
       </c>
       <c r="I54" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J54" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L54" s="44">
         <v>1</v>
@@ -4731,7 +4963,7 @@
         <v>5</v>
       </c>
       <c r="N54" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O54" s="45">
         <v>0.1341</v>
@@ -4768,13 +5000,13 @@
         <v>196</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K55" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L55" s="37">
         <v>1</v>
@@ -4783,7 +5015,7 @@
         <v>5</v>
       </c>
       <c r="N55" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O55" s="38">
         <v>0.19539999999999999</v>
@@ -4820,13 +5052,13 @@
         <v>197</v>
       </c>
       <c r="I56" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J56" s="44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L56" s="44">
         <v>1</v>
@@ -4835,7 +5067,7 @@
         <v>2</v>
       </c>
       <c r="N56" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O56" s="45">
         <v>0.43909999999999999</v>
@@ -4872,13 +5104,13 @@
         <v>198</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L57" s="37">
         <v>1</v>
@@ -4887,7 +5119,7 @@
         <v>5</v>
       </c>
       <c r="N57" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O57" s="38">
         <v>0.15479999999999999</v>
@@ -4924,13 +5156,13 @@
         <v>200</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L58" s="37">
         <v>1</v>
@@ -4939,9 +5171,9 @@
         <v>2</v>
       </c>
       <c r="N58" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="O58" s="38">
+        <v>285</v>
+      </c>
+      <c r="O58" s="115">
         <v>5.1212</v>
       </c>
       <c r="P58" s="38">
@@ -4976,13 +5208,13 @@
         <v>201</v>
       </c>
       <c r="I59" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L59" s="44">
         <v>1</v>
@@ -4991,7 +5223,7 @@
         <v>5</v>
       </c>
       <c r="N59" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O59" s="45">
         <v>0.15670000000000001</v>
@@ -5028,13 +5260,13 @@
         <v>202</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L60" s="37">
         <v>1</v>
@@ -5043,7 +5275,7 @@
         <v>2</v>
       </c>
       <c r="N60" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O60" s="38">
         <v>0.96889999999999998</v>
@@ -5080,13 +5312,13 @@
         <v>203</v>
       </c>
       <c r="I61" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J61" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L61" s="44">
         <v>1</v>
@@ -5095,7 +5327,7 @@
         <v>2</v>
       </c>
       <c r="N61" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O61" s="45">
         <v>0.28870000000000001</v>
@@ -5132,13 +5364,13 @@
         <v>197</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K62" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -5147,7 +5379,7 @@
         <v>2</v>
       </c>
       <c r="N62" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O62" s="38">
         <v>2.0651000000000002</v>
@@ -5159,7 +5391,7 @@
       <c r="Q62" s="37"/>
       <c r="R62" s="49"/>
     </row>
-    <row r="63" spans="1:19" s="72" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A63" s="70"/>
       <c r="B63" s="59">
         <f t="shared" si="0"/>
@@ -5184,13 +5416,13 @@
         <v>204</v>
       </c>
       <c r="I63" s="49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J63" s="49" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K63" s="61" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L63" s="49">
         <v>1</v>
@@ -5199,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="N63" s="62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O63" s="63">
         <v>1.2919</v>
@@ -5211,37 +5443,240 @@
       <c r="Q63" s="49"/>
       <c r="R63" s="49"/>
     </row>
-    <row r="64" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="75"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="77"/>
-      <c r="E64" s="78"/>
-      <c r="F64" s="79"/>
-      <c r="G64" s="80"/>
-      <c r="H64" s="79"/>
-      <c r="I64" s="80"/>
-      <c r="J64" s="79"/>
-      <c r="K64" s="80"/>
-      <c r="L64" s="80"/>
-      <c r="M64" s="87" t="s">
+    <row r="64" spans="1:19" s="72" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="70"/>
+      <c r="B64" s="59">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C64" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="F64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="H64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="I64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="K64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="L64" s="49">
+        <v>1</v>
+      </c>
+      <c r="M64" s="49"/>
+      <c r="N64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="O64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="P64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q64" s="89" t="s">
+        <v>341</v>
+      </c>
+      <c r="R64" s="49"/>
+    </row>
+    <row r="65" spans="1:18" s="72" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="70"/>
+      <c r="B65" s="59">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C65" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="D65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="F65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="H65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="I65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="K65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="L65" s="49">
+        <v>1</v>
+      </c>
+      <c r="M65" s="49"/>
+      <c r="N65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="O65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="P65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q65" s="89" t="s">
+        <v>341</v>
+      </c>
+      <c r="R65" s="49"/>
+    </row>
+    <row r="66" spans="1:18" s="72" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="70"/>
+      <c r="B66" s="59">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C66" s="60" t="s">
+        <v>340</v>
+      </c>
+      <c r="D66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="F66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="H66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="I66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="K66" s="49"/>
+      <c r="L66" s="49">
+        <v>1</v>
+      </c>
+      <c r="M66" s="49"/>
+      <c r="N66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="O66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="P66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q66" s="89" t="s">
+        <v>341</v>
+      </c>
+      <c r="R66" s="49"/>
+    </row>
+    <row r="67" spans="1:18" s="72" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="70"/>
+      <c r="B67" s="59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C67" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>336</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G67" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="H67" s="49" t="s">
+        <v>338</v>
+      </c>
+      <c r="I67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J67" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="K67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="L67" s="49">
+        <v>1</v>
+      </c>
+      <c r="M67" s="49">
+        <v>2</v>
+      </c>
+      <c r="N67" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="O67" s="63">
+        <v>0.1202</v>
+      </c>
+      <c r="P67" s="88">
+        <f>O67*M67</f>
+        <v>0.2404</v>
+      </c>
+      <c r="Q67" s="49"/>
+      <c r="R67" s="49"/>
+    </row>
+    <row r="68" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="75"/>
+      <c r="C68" s="76"/>
+      <c r="D68" s="77"/>
+      <c r="E68" s="78"/>
+      <c r="F68" s="79"/>
+      <c r="G68" s="80"/>
+      <c r="H68" s="79"/>
+      <c r="I68" s="80"/>
+      <c r="J68" s="79"/>
+      <c r="K68" s="80"/>
+      <c r="L68" s="80"/>
+      <c r="M68" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="N64" s="88"/>
-      <c r="O64" s="88"/>
-      <c r="P64" s="41">
-        <f>SUM(P10:P63)</f>
-        <v>51.423800000000014</v>
-      </c>
-      <c r="Q64" s="89"/>
-      <c r="R64" s="90"/>
+      <c r="N68" s="108"/>
+      <c r="O68" s="108"/>
+      <c r="P68" s="41">
+        <f>SUM(P10:P67)</f>
+        <v>48.240500000000019</v>
+      </c>
+      <c r="Q68" s="109"/>
+      <c r="R68" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="K1:R1"/>
     <mergeCell ref="R3:R8"/>
-    <mergeCell ref="M64:O64"/>
-    <mergeCell ref="Q64:R64"/>
+    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="Q68:R68"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N10" r:id="rId1"/>
@@ -5249,62 +5684,64 @@
     <hyperlink ref="N12" r:id="rId3"/>
     <hyperlink ref="N13" r:id="rId4"/>
     <hyperlink ref="N14" r:id="rId5"/>
-    <hyperlink ref="N15" r:id="rId6"/>
-    <hyperlink ref="N16" r:id="rId7"/>
-    <hyperlink ref="N17" r:id="rId8"/>
-    <hyperlink ref="N19" r:id="rId9"/>
-    <hyperlink ref="N20" r:id="rId10"/>
-    <hyperlink ref="N21" r:id="rId11"/>
-    <hyperlink ref="N22" r:id="rId12"/>
-    <hyperlink ref="N23" r:id="rId13"/>
-    <hyperlink ref="N24" r:id="rId14"/>
-    <hyperlink ref="N26" r:id="rId15"/>
-    <hyperlink ref="N27" r:id="rId16"/>
-    <hyperlink ref="N30" r:id="rId17"/>
-    <hyperlink ref="N31" r:id="rId18"/>
-    <hyperlink ref="N33" r:id="rId19"/>
-    <hyperlink ref="N35" r:id="rId20"/>
-    <hyperlink ref="N36" r:id="rId21"/>
-    <hyperlink ref="N37" r:id="rId22"/>
-    <hyperlink ref="N38" r:id="rId23"/>
-    <hyperlink ref="N40" r:id="rId24"/>
-    <hyperlink ref="N42" r:id="rId25"/>
-    <hyperlink ref="N43" r:id="rId26"/>
-    <hyperlink ref="N44" r:id="rId27"/>
-    <hyperlink ref="N45" r:id="rId28"/>
-    <hyperlink ref="N46" r:id="rId29"/>
-    <hyperlink ref="N47" r:id="rId30"/>
-    <hyperlink ref="N48" r:id="rId31"/>
-    <hyperlink ref="N50" r:id="rId32"/>
-    <hyperlink ref="N52" r:id="rId33"/>
-    <hyperlink ref="N53" r:id="rId34"/>
-    <hyperlink ref="N55" r:id="rId35"/>
-    <hyperlink ref="N56" r:id="rId36"/>
-    <hyperlink ref="N57" r:id="rId37"/>
-    <hyperlink ref="N58" r:id="rId38"/>
-    <hyperlink ref="N59" r:id="rId39"/>
-    <hyperlink ref="N60" r:id="rId40"/>
-    <hyperlink ref="N61" r:id="rId41"/>
-    <hyperlink ref="N62" r:id="rId42"/>
-    <hyperlink ref="N63" r:id="rId43"/>
-    <hyperlink ref="N18" r:id="rId44"/>
-    <hyperlink ref="N54" r:id="rId45"/>
-    <hyperlink ref="N41" r:id="rId46"/>
-    <hyperlink ref="N25" r:id="rId47"/>
-    <hyperlink ref="N29" r:id="rId48"/>
-    <hyperlink ref="N32" r:id="rId49"/>
-    <hyperlink ref="N39" r:id="rId50"/>
-    <hyperlink ref="N51" r:id="rId51"/>
+    <hyperlink ref="N16" r:id="rId6"/>
+    <hyperlink ref="N17" r:id="rId7"/>
+    <hyperlink ref="N19" r:id="rId8"/>
+    <hyperlink ref="N20" r:id="rId9"/>
+    <hyperlink ref="N21" r:id="rId10"/>
+    <hyperlink ref="N22" r:id="rId11"/>
+    <hyperlink ref="N23" r:id="rId12"/>
+    <hyperlink ref="N24" r:id="rId13"/>
+    <hyperlink ref="N26" r:id="rId14"/>
+    <hyperlink ref="N27" r:id="rId15"/>
+    <hyperlink ref="N30" r:id="rId16"/>
+    <hyperlink ref="N31" r:id="rId17"/>
+    <hyperlink ref="N33" r:id="rId18"/>
+    <hyperlink ref="N35" r:id="rId19"/>
+    <hyperlink ref="N36" r:id="rId20"/>
+    <hyperlink ref="N37" r:id="rId21"/>
+    <hyperlink ref="N38" r:id="rId22"/>
+    <hyperlink ref="N40" r:id="rId23"/>
+    <hyperlink ref="N42" r:id="rId24"/>
+    <hyperlink ref="N43" r:id="rId25"/>
+    <hyperlink ref="N44" r:id="rId26"/>
+    <hyperlink ref="N45" r:id="rId27"/>
+    <hyperlink ref="N46" r:id="rId28"/>
+    <hyperlink ref="N47" r:id="rId29"/>
+    <hyperlink ref="N48" r:id="rId30"/>
+    <hyperlink ref="N50" r:id="rId31"/>
+    <hyperlink ref="N52" r:id="rId32"/>
+    <hyperlink ref="N53" r:id="rId33"/>
+    <hyperlink ref="N55" r:id="rId34"/>
+    <hyperlink ref="N56" r:id="rId35"/>
+    <hyperlink ref="N57" r:id="rId36"/>
+    <hyperlink ref="N58" r:id="rId37"/>
+    <hyperlink ref="N59" r:id="rId38"/>
+    <hyperlink ref="N60" r:id="rId39"/>
+    <hyperlink ref="N61" r:id="rId40"/>
+    <hyperlink ref="N62" r:id="rId41"/>
+    <hyperlink ref="N63" r:id="rId42"/>
+    <hyperlink ref="N18" r:id="rId43"/>
+    <hyperlink ref="N54" r:id="rId44"/>
+    <hyperlink ref="N41" r:id="rId45"/>
+    <hyperlink ref="N25" r:id="rId46"/>
+    <hyperlink ref="N29" r:id="rId47"/>
+    <hyperlink ref="N32" r:id="rId48"/>
+    <hyperlink ref="N39" r:id="rId49"/>
+    <hyperlink ref="N51" r:id="rId50"/>
+    <hyperlink ref="N67" r:id="rId51"/>
+    <hyperlink ref="N15" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId52"/>
+  <pageSetup orientation="portrait" r:id="rId53"/>
+  <drawing r:id="rId54"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -5338,15 +5775,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="104"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5357,7 +5794,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -5382,7 +5819,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -5396,7 +5833,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="85"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5407,7 +5844,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -5421,7 +5858,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="86"/>
+      <c r="S4" s="106"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5446,7 +5883,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="86"/>
+      <c r="S5" s="106"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5467,7 +5904,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="86"/>
+      <c r="S6" s="106"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5488,7 +5925,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="86"/>
+      <c r="S7" s="106"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5509,7 +5946,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="86"/>
+      <c r="S8" s="106"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5535,37 +5972,37 @@
         <v>182</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J9" s="30" t="s">
         <v>205</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="N9" s="90" t="s">
         <v>277</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="95" t="s">
         <v>279</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>282</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -5578,7 +6015,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>67</v>
@@ -5593,13 +6030,13 @@
         <v>183</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>206</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -5608,13 +6045,13 @@
         <f>L10*5</f>
         <v>15</v>
       </c>
-      <c r="N10" s="37">
+      <c r="N10" s="91">
         <v>50</v>
       </c>
       <c r="O10" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P10" s="38">
+        <v>285</v>
+      </c>
+      <c r="P10" s="96">
         <v>1.89E-2</v>
       </c>
       <c r="Q10" s="81">
@@ -5627,7 +6064,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="40">
-        <f t="shared" ref="B11:B63" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B67" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="50" t="s">
@@ -5649,13 +6086,13 @@
         <v>184</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J11" s="44" t="s">
         <v>207</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L11" s="44">
         <v>2</v>
@@ -5664,13 +6101,13 @@
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>10</v>
       </c>
-      <c r="N11" s="44">
+      <c r="N11" s="84">
         <v>11</v>
       </c>
       <c r="O11" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P11" s="45">
+        <v>285</v>
+      </c>
+      <c r="P11" s="97">
         <v>1.4064000000000001</v>
       </c>
       <c r="Q11" s="81">
@@ -5705,13 +6142,13 @@
         <v>183</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J12" s="37" t="s">
         <v>208</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L12" s="37">
         <v>14</v>
@@ -5720,13 +6157,13 @@
         <f>L12*5</f>
         <v>70</v>
       </c>
-      <c r="N12" s="37">
+      <c r="N12" s="91">
         <v>100</v>
       </c>
       <c r="O12" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P12" s="38">
+        <v>285</v>
+      </c>
+      <c r="P12" s="96">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q12" s="81">
@@ -5761,13 +6198,13 @@
         <v>183</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J13" s="44" t="s">
         <v>209</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L13" s="44">
         <v>1</v>
@@ -5776,13 +6213,13 @@
         <f t="shared" ref="M13" si="3">L13*5</f>
         <v>5</v>
       </c>
-      <c r="N13" s="44">
+      <c r="N13" s="84">
         <v>100</v>
       </c>
       <c r="O13" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P13" s="45">
+        <v>285</v>
+      </c>
+      <c r="P13" s="97">
         <v>2.8E-3</v>
       </c>
       <c r="Q13" s="81">
@@ -5802,7 +6239,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>71</v>
@@ -5817,13 +6254,13 @@
         <v>183</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>210</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L14" s="37">
         <v>22</v>
@@ -5832,13 +6269,13 @@
         <f>L14*5</f>
         <v>110</v>
       </c>
-      <c r="N14" s="37">
+      <c r="N14" s="91">
         <v>200</v>
       </c>
       <c r="O14" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P14" s="38">
+        <v>285</v>
+      </c>
+      <c r="P14" s="96">
         <v>1.8E-3</v>
       </c>
       <c r="Q14" s="81">
@@ -5866,20 +6303,20 @@
       <c r="F15" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="56" t="s">
         <v>147</v>
       </c>
       <c r="H15" s="44" t="s">
         <v>183</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>211</v>
+        <v>344</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L15" s="44">
         <v>2</v>
@@ -5888,18 +6325,18 @@
         <f t="shared" ref="M15" si="4">L15*5</f>
         <v>10</v>
       </c>
-      <c r="N15" s="44">
-        <v>15</v>
+      <c r="N15" s="84">
+        <v>20</v>
       </c>
       <c r="O15" s="53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P15" s="45">
-        <v>0.16370000000000001</v>
+        <v>1.77E-2</v>
       </c>
       <c r="Q15" s="81">
         <f t="shared" si="2"/>
-        <v>2.4555000000000002</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="R15" s="44"/>
       <c r="S15" s="49"/>
@@ -5929,13 +6366,13 @@
         <v>185</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L16" s="37">
         <v>2</v>
@@ -5944,13 +6381,13 @@
         <f>L16*5</f>
         <v>10</v>
       </c>
-      <c r="N16" s="37">
+      <c r="N16" s="91">
         <v>15</v>
       </c>
       <c r="O16" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P16" s="38">
+        <v>285</v>
+      </c>
+      <c r="P16" s="96">
         <v>0.42320000000000002</v>
       </c>
       <c r="Q16" s="81">
@@ -5985,13 +6422,13 @@
         <v>183</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L17" s="44">
         <v>6</v>
@@ -6000,13 +6437,13 @@
         <f t="shared" ref="M17" si="5">L17*5</f>
         <v>30</v>
       </c>
-      <c r="N17" s="44">
+      <c r="N17" s="84">
         <v>40</v>
       </c>
       <c r="O17" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P17" s="45">
+        <v>285</v>
+      </c>
+      <c r="P17" s="97">
         <v>2.3800000000000002E-2</v>
       </c>
       <c r="Q17" s="81">
@@ -6041,13 +6478,13 @@
         <v>186</v>
       </c>
       <c r="I18" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="J18" s="37" t="s">
         <v>290</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>291</v>
-      </c>
       <c r="K18" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -6056,13 +6493,13 @@
         <f>L18*5</f>
         <v>15</v>
       </c>
-      <c r="N18" s="37">
+      <c r="N18" s="91">
         <v>50</v>
       </c>
       <c r="O18" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P18" s="38">
+        <v>285</v>
+      </c>
+      <c r="P18" s="96">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q18" s="81">
@@ -6097,13 +6534,13 @@
         <v>183</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L19" s="44">
         <v>1</v>
@@ -6112,13 +6549,13 @@
         <f t="shared" ref="M19" si="6">L19*5</f>
         <v>5</v>
       </c>
-      <c r="N19" s="44">
+      <c r="N19" s="84">
         <v>20</v>
       </c>
       <c r="O19" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P19" s="45">
+        <v>285</v>
+      </c>
+      <c r="P19" s="97">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="Q19" s="81">
@@ -6153,13 +6590,13 @@
         <v>183</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L20" s="44">
         <v>2</v>
@@ -6168,13 +6605,13 @@
         <f t="shared" ref="M20" si="7">L20*5</f>
         <v>10</v>
       </c>
-      <c r="N20" s="44">
+      <c r="N20" s="84">
         <v>100</v>
       </c>
       <c r="O20" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P20" s="45">
+        <v>285</v>
+      </c>
+      <c r="P20" s="97">
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="Q20" s="81">
@@ -6209,13 +6646,13 @@
         <v>183</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L21" s="37">
         <v>2</v>
@@ -6224,13 +6661,13 @@
         <f>L21*5</f>
         <v>10</v>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="91">
         <v>100</v>
       </c>
       <c r="O21" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P21" s="38">
+        <v>285</v>
+      </c>
+      <c r="P21" s="96">
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="Q21" s="81">
@@ -6265,13 +6702,13 @@
         <v>183</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L22" s="44">
         <v>1</v>
@@ -6280,13 +6717,13 @@
         <f t="shared" ref="M22" si="8">L22*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="44">
+      <c r="N22" s="84">
         <v>100</v>
       </c>
       <c r="O22" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P22" s="45">
+        <v>285</v>
+      </c>
+      <c r="P22" s="97">
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="Q22" s="81">
@@ -6321,13 +6758,13 @@
         <v>187</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L23" s="44">
         <v>1</v>
@@ -6336,13 +6773,13 @@
         <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="37">
+      <c r="N23" s="91">
         <v>10</v>
       </c>
       <c r="O23" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P23" s="45">
+        <v>285</v>
+      </c>
+      <c r="P23" s="97">
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="Q23" s="81">
@@ -6377,13 +6814,13 @@
         <v>188</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -6392,13 +6829,13 @@
         <f t="shared" ref="M24" si="9">L24*5</f>
         <v>5</v>
       </c>
-      <c r="N24" s="44">
+      <c r="N24" s="84">
         <v>10</v>
       </c>
       <c r="O24" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P24" s="38">
+        <v>285</v>
+      </c>
+      <c r="P24" s="96">
         <v>2.63E-2</v>
       </c>
       <c r="Q24" s="81">
@@ -6418,28 +6855,28 @@
         <v>10</v>
       </c>
       <c r="D25" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="E25" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="F25" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="G25" s="44" t="s">
         <v>304</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>305</v>
       </c>
       <c r="H25" s="44" t="s">
         <v>188</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L25" s="44">
         <v>1</v>
@@ -6448,13 +6885,13 @@
         <f>L25*5</f>
         <v>5</v>
       </c>
-      <c r="N25" s="37">
+      <c r="N25" s="91">
         <v>20</v>
       </c>
       <c r="O25" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P25" s="44">
+        <v>285</v>
+      </c>
+      <c r="P25" s="85">
         <v>3.8100000000000002E-2</v>
       </c>
       <c r="Q25" s="81">
@@ -6489,13 +6926,13 @@
         <v>186</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L26" s="37">
         <v>2</v>
@@ -6504,13 +6941,13 @@
         <f t="shared" ref="M26" si="10">L26*5</f>
         <v>10</v>
       </c>
-      <c r="N26" s="44">
+      <c r="N26" s="84">
         <v>10</v>
       </c>
       <c r="O26" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P26" s="38">
+        <v>285</v>
+      </c>
+      <c r="P26" s="96">
         <v>3.2199999999999999E-2</v>
       </c>
       <c r="Q26" s="81">
@@ -6545,13 +6982,13 @@
         <v>186</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L27" s="44">
         <v>1</v>
@@ -6560,13 +6997,13 @@
         <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N27" s="37">
+      <c r="N27" s="91">
         <v>20</v>
       </c>
       <c r="O27" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P27" s="45">
+        <v>285</v>
+      </c>
+      <c r="P27" s="97">
         <v>8.8999999999999999E-3</v>
       </c>
       <c r="Q27" s="81">
@@ -6583,25 +7020,25 @@
         <v>19</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D28" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E28" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="G28" s="37" t="s">
         <v>308</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>309</v>
       </c>
       <c r="H28" s="37"/>
       <c r="I28" s="37"/>
       <c r="J28" s="37"/>
       <c r="K28" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -6610,11 +7047,11 @@
         <f t="shared" ref="M28" si="11">L28*5</f>
         <v>5</v>
       </c>
-      <c r="N28" s="44">
+      <c r="N28" s="84">
         <v>50</v>
       </c>
       <c r="O28" s="52"/>
-      <c r="P28" s="38"/>
+      <c r="P28" s="96"/>
       <c r="Q28" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -6632,28 +7069,28 @@
         <v>13</v>
       </c>
       <c r="D29" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="E29" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="F29" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="G29" s="44" t="s">
         <v>311</v>
       </c>
-      <c r="F29" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="G29" s="44" t="s">
+      <c r="H29" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="I29" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="J29" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="I29" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>314</v>
-      </c>
       <c r="K29" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L29" s="44">
         <v>3</v>
@@ -6662,13 +7099,13 @@
         <f>L29*5</f>
         <v>15</v>
       </c>
-      <c r="N29" s="37">
+      <c r="N29" s="91">
         <v>20</v>
       </c>
       <c r="O29" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P29" s="45">
+        <v>285</v>
+      </c>
+      <c r="P29" s="97">
         <v>2.52E-2</v>
       </c>
       <c r="Q29" s="81">
@@ -6694,7 +7131,7 @@
         <v>84</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>122</v>
@@ -6703,13 +7140,13 @@
         <v>189</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -6718,13 +7155,13 @@
         <f t="shared" ref="M30" si="12">L30*5</f>
         <v>5</v>
       </c>
-      <c r="N30" s="44">
+      <c r="N30" s="84">
         <v>6</v>
       </c>
       <c r="O30" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P30" s="38">
+        <v>285</v>
+      </c>
+      <c r="P30" s="96">
         <v>1.4796</v>
       </c>
       <c r="Q30" s="81">
@@ -6741,7 +7178,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D31" s="44" t="s">
         <v>39</v>
@@ -6750,7 +7187,7 @@
         <v>85</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G31" s="44" t="s">
         <v>123</v>
@@ -6759,13 +7196,13 @@
         <v>189</v>
       </c>
       <c r="I31" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J31" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L31" s="44">
         <v>1</v>
@@ -6774,13 +7211,13 @@
         <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="91">
         <v>6</v>
       </c>
       <c r="O31" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P31" s="45">
+        <v>285</v>
+      </c>
+      <c r="P31" s="97">
         <v>0.9546</v>
       </c>
       <c r="Q31" s="81">
@@ -6797,31 +7234,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="D32" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="E32" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="F32" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="G32" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="F32" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G32" s="37" t="s">
+      <c r="H32" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="H32" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>319</v>
-      </c>
       <c r="K32" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -6830,13 +7267,13 @@
         <f t="shared" ref="M32" si="13">L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="44">
+      <c r="N32" s="84">
         <v>6</v>
       </c>
       <c r="O32" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P32" s="38">
+        <v>285</v>
+      </c>
+      <c r="P32" s="96">
         <v>3.8199999999999998E-2</v>
       </c>
       <c r="Q32" s="81">
@@ -6862,7 +7299,7 @@
         <v>86</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G33" s="44" t="s">
         <v>124</v>
@@ -6871,13 +7308,13 @@
         <v>190</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J33" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L33" s="44">
         <v>1</v>
@@ -6886,13 +7323,13 @@
         <f>L33*5</f>
         <v>5</v>
       </c>
-      <c r="N33" s="37">
+      <c r="N33" s="91">
         <v>10</v>
       </c>
       <c r="O33" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P33" s="45">
+        <v>285</v>
+      </c>
+      <c r="P33" s="97">
         <v>0.29110000000000003</v>
       </c>
       <c r="Q33" s="81">
@@ -6918,22 +7355,22 @@
         <v>87</v>
       </c>
       <c r="F34" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="G34" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="G34" s="54" t="s">
-        <v>274</v>
-      </c>
       <c r="H34" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I34" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J34" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K34" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L34" s="54">
         <v>13</v>
@@ -6942,17 +7379,17 @@
         <f t="shared" ref="M34" si="14">L34*5</f>
         <v>65</v>
       </c>
-      <c r="N34" s="56">
+      <c r="N34" s="92">
         <v>6</v>
       </c>
       <c r="O34" s="54" t="s">
-        <v>272</v>
-      </c>
-      <c r="P34" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
+      </c>
+      <c r="P34" s="98" t="s">
+        <v>271</v>
       </c>
       <c r="Q34" s="82" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R34" s="44"/>
       <c r="S34" s="49"/>
@@ -6982,13 +7419,13 @@
         <v>191</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J35" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L35" s="44">
         <v>1</v>
@@ -6997,13 +7434,13 @@
         <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N35" s="91">
         <v>10</v>
       </c>
       <c r="O35" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P35" s="45">
+        <v>285</v>
+      </c>
+      <c r="P35" s="97">
         <v>4.6899999999999997E-2</v>
       </c>
       <c r="Q35" s="81">
@@ -7038,13 +7475,13 @@
         <v>192</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -7053,13 +7490,13 @@
         <f t="shared" ref="M36" si="15">L36*5</f>
         <v>5</v>
       </c>
-      <c r="N36" s="44">
+      <c r="N36" s="84">
         <v>20</v>
       </c>
       <c r="O36" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P36" s="38">
+        <v>285</v>
+      </c>
+      <c r="P36" s="96">
         <v>3.49E-2</v>
       </c>
       <c r="Q36" s="81">
@@ -7079,7 +7516,7 @@
         <v>17</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>90</v>
@@ -7094,13 +7531,13 @@
         <v>183</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L37" s="44">
         <v>11</v>
@@ -7109,13 +7546,13 @@
         <f>L37*5</f>
         <v>55</v>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="91">
         <v>100</v>
       </c>
       <c r="O37" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P37" s="45">
+        <v>285</v>
+      </c>
+      <c r="P37" s="97">
         <v>1E-3</v>
       </c>
       <c r="Q37" s="81">
@@ -7123,7 +7560,7 @@
         <v>0.1</v>
       </c>
       <c r="R37" s="73" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S37" s="49"/>
     </row>
@@ -7152,13 +7589,13 @@
         <v>183</v>
       </c>
       <c r="I38" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J38" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L38" s="44">
         <v>3</v>
@@ -7167,13 +7604,13 @@
         <f t="shared" ref="M38" si="16">L38*5</f>
         <v>15</v>
       </c>
-      <c r="N38" s="44">
+      <c r="N38" s="84">
         <v>100</v>
       </c>
       <c r="O38" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P38" s="45">
+        <v>285</v>
+      </c>
+      <c r="P38" s="97">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q38" s="81">
@@ -7196,25 +7633,25 @@
         <v>45</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F39" s="44" t="s">
         <v>126</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H39" s="44" t="s">
         <v>183</v>
       </c>
       <c r="I39" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J39" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="K39" s="44" t="s">
         <v>330</v>
-      </c>
-      <c r="K39" s="44" t="s">
-        <v>331</v>
       </c>
       <c r="L39" s="44">
         <v>1</v>
@@ -7223,13 +7660,13 @@
         <f>L39*5</f>
         <v>5</v>
       </c>
-      <c r="N39" s="37">
+      <c r="N39" s="91">
         <v>100</v>
       </c>
       <c r="O39" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P39" s="38">
+        <v>285</v>
+      </c>
+      <c r="P39" s="96">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q39" s="81">
@@ -7264,13 +7701,13 @@
         <v>183</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L40" s="37">
         <v>2</v>
@@ -7279,13 +7716,13 @@
         <f t="shared" ref="M40" si="17">L40*5</f>
         <v>10</v>
       </c>
-      <c r="N40" s="44">
+      <c r="N40" s="84">
         <v>100</v>
       </c>
       <c r="O40" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P40" s="38">
+        <v>285</v>
+      </c>
+      <c r="P40" s="96">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q40" s="81">
@@ -7308,25 +7745,25 @@
         <v>47</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F41" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="G41" s="56" t="s">
         <v>293</v>
-      </c>
-      <c r="G41" s="56" t="s">
-        <v>294</v>
       </c>
       <c r="H41" s="44" t="s">
         <v>183</v>
       </c>
       <c r="I41" s="44" t="s">
-        <v>272</v>
+        <v>342</v>
       </c>
       <c r="J41" s="44" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K41" s="44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L41" s="44">
         <v>1</v>
@@ -7335,13 +7772,13 @@
         <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="37">
+      <c r="N41" s="91">
         <v>50</v>
       </c>
       <c r="O41" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P41" s="45">
+        <v>285</v>
+      </c>
+      <c r="P41" s="97">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q41" s="81">
@@ -7376,13 +7813,13 @@
         <v>183</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L42" s="37">
         <v>5</v>
@@ -7391,13 +7828,13 @@
         <f>L42*5</f>
         <v>25</v>
       </c>
-      <c r="N42" s="37">
+      <c r="N42" s="91">
         <v>100</v>
       </c>
       <c r="O42" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P42" s="38">
+        <v>285</v>
+      </c>
+      <c r="P42" s="96">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q42" s="81">
@@ -7432,13 +7869,13 @@
         <v>183</v>
       </c>
       <c r="I43" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J43" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L43" s="44">
         <v>2</v>
@@ -7447,13 +7884,13 @@
         <f t="shared" ref="M43" si="18">L43*5</f>
         <v>10</v>
       </c>
-      <c r="N43" s="44">
+      <c r="N43" s="84">
         <v>100</v>
       </c>
       <c r="O43" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P43" s="45">
+        <v>285</v>
+      </c>
+      <c r="P43" s="97">
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="Q43" s="81">
@@ -7488,13 +7925,13 @@
         <v>183</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L44" s="37">
         <v>3</v>
@@ -7503,13 +7940,13 @@
         <f>L44*5</f>
         <v>15</v>
       </c>
-      <c r="N44" s="37">
+      <c r="N44" s="91">
         <v>100</v>
       </c>
       <c r="O44" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P44" s="38">
+        <v>285</v>
+      </c>
+      <c r="P44" s="96">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q44" s="81">
@@ -7544,13 +7981,13 @@
         <v>183</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L45" s="44">
         <v>2</v>
@@ -7559,13 +7996,13 @@
         <f t="shared" ref="M45" si="19">L45*5</f>
         <v>10</v>
       </c>
-      <c r="N45" s="44">
+      <c r="N45" s="84">
         <v>100</v>
       </c>
       <c r="O45" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P45" s="45">
+        <v>285</v>
+      </c>
+      <c r="P45" s="97">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q45" s="81">
@@ -7600,13 +8037,13 @@
         <v>183</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L46" s="37">
         <v>2</v>
@@ -7615,13 +8052,13 @@
         <f>L46*5</f>
         <v>10</v>
       </c>
-      <c r="N46" s="37">
+      <c r="N46" s="91">
         <v>100</v>
       </c>
       <c r="O46" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P46" s="38">
+        <v>285</v>
+      </c>
+      <c r="P46" s="96">
         <v>1.8E-3</v>
       </c>
       <c r="Q46" s="81">
@@ -7656,13 +8093,13 @@
         <v>183</v>
       </c>
       <c r="I47" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J47" s="44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L47" s="44">
         <v>1</v>
@@ -7671,13 +8108,13 @@
         <f t="shared" ref="M47" si="20">L47*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="44">
+      <c r="N47" s="84">
         <v>20</v>
       </c>
       <c r="O47" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P47" s="45">
+        <v>285</v>
+      </c>
+      <c r="P47" s="97">
         <v>2.75E-2</v>
       </c>
       <c r="Q47" s="81">
@@ -7712,13 +8149,13 @@
         <v>183</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K48" s="37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L48" s="37">
         <v>1</v>
@@ -7727,13 +8164,13 @@
         <f>L48*5</f>
         <v>5</v>
       </c>
-      <c r="N48" s="37">
+      <c r="N48" s="91">
         <v>50</v>
       </c>
       <c r="O48" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P48" s="38">
+        <v>285</v>
+      </c>
+      <c r="P48" s="96">
         <v>8.8000000000000005E-3</v>
       </c>
       <c r="Q48" s="81">
@@ -7753,28 +8190,28 @@
         <v>127</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E49" s="54" t="s">
         <v>100</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G49" s="54" t="s">
         <v>127</v>
       </c>
       <c r="H49" s="55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I49" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J49" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K49" s="54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L49" s="54">
         <v>6</v>
@@ -7783,17 +8220,17 @@
         <f t="shared" ref="M49" si="21">L49*5</f>
         <v>30</v>
       </c>
-      <c r="N49" s="44">
+      <c r="N49" s="84">
         <v>20</v>
       </c>
       <c r="O49" s="56" t="s">
-        <v>272</v>
-      </c>
-      <c r="P49" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
+      </c>
+      <c r="P49" s="98" t="s">
+        <v>271</v>
       </c>
       <c r="Q49" s="81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R49" s="44"/>
       <c r="S49" s="49"/>
@@ -7808,13 +8245,13 @@
         <v>18</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E50" s="44" t="s">
         <v>101</v>
       </c>
       <c r="F50" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G50" s="44" t="s">
         <v>128</v>
@@ -7823,13 +8260,13 @@
         <v>193</v>
       </c>
       <c r="I50" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J50" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L50" s="44">
         <v>2</v>
@@ -7838,13 +8275,13 @@
         <f>L50*5</f>
         <v>10</v>
       </c>
-      <c r="N50" s="37">
+      <c r="N50" s="91">
         <v>15</v>
       </c>
       <c r="O50" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P50" s="45">
+        <v>285</v>
+      </c>
+      <c r="P50" s="97">
         <v>0.3135</v>
       </c>
       <c r="Q50" s="81">
@@ -7864,28 +8301,28 @@
         <v>18</v>
       </c>
       <c r="D51" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="F51" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="G51" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="F51" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G51" s="37" t="s">
+      <c r="H51" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="I51" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="I51" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>326</v>
-      </c>
       <c r="K51" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L51" s="37">
         <v>1</v>
@@ -7894,13 +8331,13 @@
         <f t="shared" ref="M51" si="22">L51*5</f>
         <v>5</v>
       </c>
-      <c r="N51" s="44">
+      <c r="N51" s="84">
         <v>6</v>
       </c>
       <c r="O51" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P51" s="37">
+        <v>285</v>
+      </c>
+      <c r="P51" s="99">
         <v>0.42799999999999999</v>
       </c>
       <c r="Q51" s="81">
@@ -7920,13 +8357,13 @@
         <v>18</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E52" s="44" t="s">
         <v>107</v>
       </c>
       <c r="F52" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G52" s="44" t="s">
         <v>134</v>
@@ -7935,13 +8372,13 @@
         <v>199</v>
       </c>
       <c r="I52" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J52" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L52" s="44">
         <v>1</v>
@@ -7950,13 +8387,13 @@
         <f>L52*5</f>
         <v>5</v>
       </c>
-      <c r="N52" s="37">
+      <c r="N52" s="91">
         <v>10</v>
       </c>
       <c r="O52" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P52" s="45">
+        <v>285</v>
+      </c>
+      <c r="P52" s="97">
         <v>6.2100000000000002E-2</v>
       </c>
       <c r="Q52" s="81">
@@ -7991,13 +8428,13 @@
         <v>194</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K53" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L53" s="37">
         <v>1</v>
@@ -8006,13 +8443,13 @@
         <f t="shared" ref="M53" si="23">L53*5</f>
         <v>5</v>
       </c>
-      <c r="N53" s="44">
+      <c r="N53" s="84">
         <v>6</v>
       </c>
       <c r="O53" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P53" s="38">
+        <v>285</v>
+      </c>
+      <c r="P53" s="96">
         <v>0.16209999999999999</v>
       </c>
       <c r="Q53" s="81">
@@ -8047,13 +8484,13 @@
         <v>195</v>
       </c>
       <c r="I54" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J54" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L54" s="44">
         <v>1</v>
@@ -8062,13 +8499,13 @@
         <f>L54*5</f>
         <v>5</v>
       </c>
-      <c r="N54" s="44">
+      <c r="N54" s="84">
         <v>10</v>
       </c>
       <c r="O54" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P54" s="45">
+        <v>285</v>
+      </c>
+      <c r="P54" s="97">
         <v>0.1341</v>
       </c>
       <c r="Q54" s="81">
@@ -8103,13 +8540,13 @@
         <v>196</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K55" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L55" s="37">
         <v>1</v>
@@ -8118,13 +8555,13 @@
         <f t="shared" ref="M55" si="24">L55*5</f>
         <v>5</v>
       </c>
-      <c r="N55" s="44">
+      <c r="N55" s="84">
         <v>10</v>
       </c>
       <c r="O55" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P55" s="38">
+        <v>285</v>
+      </c>
+      <c r="P55" s="96">
         <v>0.19539999999999999</v>
       </c>
       <c r="Q55" s="81">
@@ -8159,13 +8596,13 @@
         <v>197</v>
       </c>
       <c r="I56" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J56" s="44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L56" s="44">
         <v>1</v>
@@ -8174,13 +8611,13 @@
         <f t="shared" ref="M56" si="25">L56*5</f>
         <v>5</v>
       </c>
-      <c r="N56" s="44">
+      <c r="N56" s="84">
         <v>6</v>
       </c>
       <c r="O56" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P56" s="45">
+        <v>285</v>
+      </c>
+      <c r="P56" s="97">
         <v>0.43909999999999999</v>
       </c>
       <c r="Q56" s="81">
@@ -8215,13 +8652,13 @@
         <v>198</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L57" s="37">
         <v>1</v>
@@ -8230,13 +8667,13 @@
         <f>L57*5</f>
         <v>5</v>
       </c>
-      <c r="N57" s="37">
+      <c r="N57" s="91">
         <v>10</v>
       </c>
       <c r="O57" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P57" s="38">
+        <v>285</v>
+      </c>
+      <c r="P57" s="96">
         <v>0.15479999999999999</v>
       </c>
       <c r="Q57" s="81">
@@ -8271,13 +8708,13 @@
         <v>200</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L58" s="37">
         <v>1</v>
@@ -8286,13 +8723,13 @@
         <f t="shared" ref="M58" si="26">L58*5</f>
         <v>5</v>
       </c>
-      <c r="N58" s="44">
+      <c r="N58" s="84">
         <v>6</v>
       </c>
       <c r="O58" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P58" s="38">
+        <v>285</v>
+      </c>
+      <c r="P58" s="96">
         <v>5.1212</v>
       </c>
       <c r="Q58" s="81">
@@ -8327,13 +8764,13 @@
         <v>201</v>
       </c>
       <c r="I59" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L59" s="44">
         <v>1</v>
@@ -8342,13 +8779,13 @@
         <f>L59*5</f>
         <v>5</v>
       </c>
-      <c r="N59" s="37">
+      <c r="N59" s="91">
         <v>10</v>
       </c>
       <c r="O59" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P59" s="45">
+        <v>285</v>
+      </c>
+      <c r="P59" s="97">
         <v>0.15670000000000001</v>
       </c>
       <c r="Q59" s="81">
@@ -8383,13 +8820,13 @@
         <v>202</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L60" s="37">
         <v>1</v>
@@ -8398,13 +8835,13 @@
         <f t="shared" ref="M60" si="27">L60*5</f>
         <v>5</v>
       </c>
-      <c r="N60" s="44">
+      <c r="N60" s="84">
         <v>6</v>
       </c>
       <c r="O60" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P60" s="38">
+        <v>285</v>
+      </c>
+      <c r="P60" s="96">
         <v>0.96889999999999998</v>
       </c>
       <c r="Q60" s="81">
@@ -8439,13 +8876,13 @@
         <v>203</v>
       </c>
       <c r="I61" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J61" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L61" s="44">
         <v>1</v>
@@ -8454,13 +8891,13 @@
         <f>L61*5</f>
         <v>5</v>
       </c>
-      <c r="N61" s="37">
+      <c r="N61" s="91">
         <v>6</v>
       </c>
       <c r="O61" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="P61" s="45">
+        <v>285</v>
+      </c>
+      <c r="P61" s="97">
         <v>0.28870000000000001</v>
       </c>
       <c r="Q61" s="81">
@@ -8495,13 +8932,13 @@
         <v>197</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K62" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -8510,13 +8947,13 @@
         <f>L62*5</f>
         <v>5</v>
       </c>
-      <c r="N62" s="37">
+      <c r="N62" s="91">
         <v>6</v>
       </c>
       <c r="O62" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="P62" s="38">
+        <v>285</v>
+      </c>
+      <c r="P62" s="96">
         <v>2.0651000000000002</v>
       </c>
       <c r="Q62" s="81">
@@ -8526,7 +8963,7 @@
       <c r="R62" s="37"/>
       <c r="S62" s="49"/>
     </row>
-    <row r="63" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="40">
         <f t="shared" si="0"/>
@@ -8551,99 +8988,320 @@
         <v>204</v>
       </c>
       <c r="I63" s="49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J63" s="49" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K63" s="61" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L63" s="49">
         <v>1</v>
       </c>
-      <c r="M63" s="44">
-        <f t="shared" ref="M63" si="28">L63*5</f>
+      <c r="M63" s="49">
+        <f t="shared" ref="M63:M67" si="28">L63*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="44">
+      <c r="N63" s="93">
         <v>6</v>
       </c>
       <c r="O63" s="62" t="s">
-        <v>286</v>
-      </c>
-      <c r="P63" s="63">
+        <v>285</v>
+      </c>
+      <c r="P63" s="100">
         <v>1.2919</v>
       </c>
-      <c r="Q63" s="81">
+      <c r="Q63" s="86">
         <f t="shared" si="2"/>
         <v>7.7514000000000003</v>
       </c>
-      <c r="R63" s="44"/>
+      <c r="R63" s="49"/>
       <c r="S63" s="49"/>
     </row>
-    <row r="64" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="64"/>
-      <c r="C64" s="65"/>
-      <c r="D64" s="66"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="68"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="68"/>
-      <c r="K64" s="69"/>
-      <c r="L64" s="69"/>
-      <c r="M64" s="69"/>
-      <c r="N64" s="87" t="s">
+      <c r="B64" s="40">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C64" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="F64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="H64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="I64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="K64" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="L64" s="49">
+        <v>1</v>
+      </c>
+      <c r="M64" s="49">
+        <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="O64" s="88"/>
-      <c r="P64" s="88"/>
-      <c r="Q64" s="41">
-        <f>SUM(Q10:Q63)</f>
-        <v>129.81380000000001</v>
-      </c>
-      <c r="R64" s="91"/>
-      <c r="S64" s="92"/>
-    </row>
-    <row r="65" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N64" s="94" t="s">
+        <v>271</v>
+      </c>
+      <c r="O64" s="53" t="s">
+        <v>271</v>
+      </c>
+      <c r="P64" s="101" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q64" s="87" t="s">
+        <v>271</v>
+      </c>
+      <c r="R64" s="83"/>
+      <c r="S64" s="83"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="87" t="s">
+      <c r="B65" s="40">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C65" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="D65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="F65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="H65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="I65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="K65" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="L65" s="49">
+        <v>1</v>
+      </c>
+      <c r="M65" s="49">
+        <f t="shared" si="28"/>
+        <v>5</v>
+      </c>
+      <c r="N65" s="91" t="s">
+        <v>271</v>
+      </c>
+      <c r="O65" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="P65" s="96" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q65" s="81" t="s">
+        <v>271</v>
+      </c>
+      <c r="R65" s="37"/>
+      <c r="S65" s="49"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="40">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C66" s="60" t="s">
+        <v>340</v>
+      </c>
+      <c r="D66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="F66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="H66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="I66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="K66" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="L66" s="49">
+        <v>1</v>
+      </c>
+      <c r="M66" s="49">
+        <f t="shared" si="28"/>
+        <v>5</v>
+      </c>
+      <c r="N66" s="91" t="s">
+        <v>271</v>
+      </c>
+      <c r="O66" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="P66" s="96" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q66" s="81" t="s">
+        <v>271</v>
+      </c>
+      <c r="R66" s="37"/>
+      <c r="S66" s="49"/>
+    </row>
+    <row r="67" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="40">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C67" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>336</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G67" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="H67" s="49" t="s">
+        <v>338</v>
+      </c>
+      <c r="I67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J67" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="K67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="L67" s="49">
+        <v>1</v>
+      </c>
+      <c r="M67" s="49">
+        <f t="shared" si="28"/>
+        <v>5</v>
+      </c>
+      <c r="N67" s="91">
         <v>6</v>
       </c>
-      <c r="O65" s="88"/>
-      <c r="P65" s="88"/>
-      <c r="Q65" s="42">
-        <f>Q64/5</f>
-        <v>25.962760000000003</v>
-      </c>
-      <c r="R65" s="93"/>
-      <c r="S65" s="94"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P66" s="74"/>
+      <c r="O67" s="102" t="s">
+        <v>285</v>
+      </c>
+      <c r="P67" s="96">
+        <v>0.1202</v>
+      </c>
+      <c r="Q67" s="81">
+        <f>P67*N67</f>
+        <v>0.72120000000000006</v>
+      </c>
+      <c r="R67" s="37"/>
+      <c r="S67" s="49"/>
+    </row>
+    <row r="68" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="64"/>
+      <c r="C68" s="65"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="69"/>
+      <c r="L68" s="69"/>
+      <c r="M68" s="69"/>
+      <c r="N68" s="107" t="s">
+        <v>5</v>
+      </c>
+      <c r="O68" s="108"/>
+      <c r="P68" s="108"/>
+      <c r="Q68" s="41">
+        <f>SUM(Q10:Q67)</f>
+        <v>128.43350000000001</v>
+      </c>
+      <c r="R68" s="111"/>
+      <c r="S68" s="112"/>
+    </row>
+    <row r="69" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="107" t="s">
+        <v>6</v>
+      </c>
+      <c r="O69" s="108"/>
+      <c r="P69" s="108"/>
+      <c r="Q69" s="42">
+        <f>Q68/5</f>
+        <v>25.686700000000002</v>
+      </c>
+      <c r="R69" s="113"/>
+      <c r="S69" s="114"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P70" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R64:S65"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="N65:P65"/>
+    <mergeCell ref="R68:S69"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="N69:P69"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -8651,55 +9309,56 @@
     <hyperlink ref="O12" r:id="rId3"/>
     <hyperlink ref="O13" r:id="rId4"/>
     <hyperlink ref="O14" r:id="rId5"/>
-    <hyperlink ref="O15" r:id="rId6"/>
-    <hyperlink ref="O16" r:id="rId7"/>
-    <hyperlink ref="O17" r:id="rId8"/>
-    <hyperlink ref="O19" r:id="rId9"/>
-    <hyperlink ref="O20" r:id="rId10"/>
-    <hyperlink ref="O21" r:id="rId11"/>
-    <hyperlink ref="O22" r:id="rId12"/>
-    <hyperlink ref="O23" r:id="rId13"/>
-    <hyperlink ref="O24" r:id="rId14"/>
-    <hyperlink ref="O26" r:id="rId15"/>
-    <hyperlink ref="O27" r:id="rId16"/>
-    <hyperlink ref="O30" r:id="rId17"/>
-    <hyperlink ref="O31" r:id="rId18"/>
-    <hyperlink ref="O33" r:id="rId19"/>
-    <hyperlink ref="O35" r:id="rId20"/>
-    <hyperlink ref="O36" r:id="rId21"/>
-    <hyperlink ref="O37" r:id="rId22"/>
-    <hyperlink ref="O38" r:id="rId23"/>
-    <hyperlink ref="O40" r:id="rId24"/>
-    <hyperlink ref="O42" r:id="rId25"/>
-    <hyperlink ref="O43" r:id="rId26"/>
-    <hyperlink ref="O44" r:id="rId27"/>
-    <hyperlink ref="O45" r:id="rId28"/>
-    <hyperlink ref="O46" r:id="rId29"/>
-    <hyperlink ref="O47" r:id="rId30"/>
-    <hyperlink ref="O48" r:id="rId31"/>
-    <hyperlink ref="O50" r:id="rId32"/>
-    <hyperlink ref="O52" r:id="rId33"/>
-    <hyperlink ref="O53" r:id="rId34"/>
-    <hyperlink ref="O55" r:id="rId35"/>
-    <hyperlink ref="O56" r:id="rId36"/>
-    <hyperlink ref="O57" r:id="rId37"/>
-    <hyperlink ref="O58" r:id="rId38"/>
-    <hyperlink ref="O59" r:id="rId39"/>
-    <hyperlink ref="O60" r:id="rId40"/>
-    <hyperlink ref="O61" r:id="rId41"/>
-    <hyperlink ref="O62" r:id="rId42"/>
-    <hyperlink ref="O63" r:id="rId43"/>
-    <hyperlink ref="O18" r:id="rId44"/>
-    <hyperlink ref="O54" r:id="rId45"/>
-    <hyperlink ref="O25" r:id="rId46"/>
-    <hyperlink ref="O29" r:id="rId47"/>
-    <hyperlink ref="O32" r:id="rId48"/>
-    <hyperlink ref="O39" r:id="rId49"/>
-    <hyperlink ref="O51" r:id="rId50"/>
-    <hyperlink ref="O41" r:id="rId51"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O17" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O22" r:id="rId11"/>
+    <hyperlink ref="O23" r:id="rId12"/>
+    <hyperlink ref="O24" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O27" r:id="rId15"/>
+    <hyperlink ref="O30" r:id="rId16"/>
+    <hyperlink ref="O31" r:id="rId17"/>
+    <hyperlink ref="O33" r:id="rId18"/>
+    <hyperlink ref="O35" r:id="rId19"/>
+    <hyperlink ref="O36" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O40" r:id="rId23"/>
+    <hyperlink ref="O42" r:id="rId24"/>
+    <hyperlink ref="O43" r:id="rId25"/>
+    <hyperlink ref="O44" r:id="rId26"/>
+    <hyperlink ref="O45" r:id="rId27"/>
+    <hyperlink ref="O46" r:id="rId28"/>
+    <hyperlink ref="O47" r:id="rId29"/>
+    <hyperlink ref="O48" r:id="rId30"/>
+    <hyperlink ref="O50" r:id="rId31"/>
+    <hyperlink ref="O52" r:id="rId32"/>
+    <hyperlink ref="O53" r:id="rId33"/>
+    <hyperlink ref="O55" r:id="rId34"/>
+    <hyperlink ref="O56" r:id="rId35"/>
+    <hyperlink ref="O57" r:id="rId36"/>
+    <hyperlink ref="O58" r:id="rId37"/>
+    <hyperlink ref="O59" r:id="rId38"/>
+    <hyperlink ref="O60" r:id="rId39"/>
+    <hyperlink ref="O61" r:id="rId40"/>
+    <hyperlink ref="O62" r:id="rId41"/>
+    <hyperlink ref="O63" r:id="rId42"/>
+    <hyperlink ref="O18" r:id="rId43"/>
+    <hyperlink ref="O54" r:id="rId44"/>
+    <hyperlink ref="O25" r:id="rId45"/>
+    <hyperlink ref="O29" r:id="rId46"/>
+    <hyperlink ref="O32" r:id="rId47"/>
+    <hyperlink ref="O39" r:id="rId48"/>
+    <hyperlink ref="O51" r:id="rId49"/>
+    <hyperlink ref="O41" r:id="rId50"/>
+    <hyperlink ref="O67" r:id="rId51"/>
+    <hyperlink ref="O15" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId52"/>
-  <drawing r:id="rId53"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
+  <drawing r:id="rId54"/>
 </worksheet>
 </file>
--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="350">
   <si>
     <t>Component list</t>
   </si>
@@ -1058,6 +1058,18 @@
   </si>
   <si>
     <t>DNP</t>
+  </si>
+  <si>
+    <t>No NO J pin 50mA 3mm 100MΩ 100000 12V 250gf@±30gf 2.6mm -30℃~+85℃ 0.65mm Black Round Button Brick nogging SPST SMD Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t>GT-TC025D-H0065-L1</t>
+  </si>
+  <si>
+    <t>C778132</t>
+  </si>
+  <si>
+    <t>Ye Part Design me Change krna ha</t>
   </si>
 </sst>
 </file>
@@ -1937,6 +1949,18 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1973,18 +1997,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2415,14 +2427,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="104"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="108"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2470,7 +2482,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
-      <c r="R3" s="105"/>
+      <c r="R3" s="109"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2494,7 +2506,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="106"/>
+      <c r="R4" s="110"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2518,7 +2530,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
-      <c r="R5" s="106"/>
+      <c r="R5" s="110"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2538,7 +2550,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="106"/>
+      <c r="R6" s="110"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2558,7 +2570,7 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="106"/>
+      <c r="R7" s="110"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2578,7 +2590,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
-      <c r="R8" s="106"/>
+      <c r="R8" s="110"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2728,7 +2740,7 @@
       <c r="N11" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="O11" s="117">
+      <c r="O11" s="105">
         <v>1.4064000000000001</v>
       </c>
       <c r="P11" s="45">
@@ -3721,7 +3733,7 @@
       <c r="P30" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="Q30" s="118" t="s">
+      <c r="Q30" s="106" t="s">
         <v>345</v>
       </c>
       <c r="R30" s="49"/>
@@ -4030,7 +4042,7 @@
       <c r="O36" s="38">
         <v>3.49E-2</v>
       </c>
-      <c r="P36" s="115">
+      <c r="P36" s="38">
         <f>O36*M36</f>
         <v>0.69799999999999995</v>
       </c>
@@ -4714,7 +4726,7 @@
       <c r="Q49" s="54"/>
       <c r="R49" s="58"/>
     </row>
-    <row r="50" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="70"/>
       <c r="B50" s="40">
         <f t="shared" si="0"/>
@@ -4727,22 +4739,22 @@
         <v>320</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>101</v>
+        <v>346</v>
       </c>
       <c r="F50" s="44" t="s">
         <v>272</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>128</v>
+        <v>347</v>
       </c>
       <c r="H50" s="44" t="s">
-        <v>193</v>
+        <v>272</v>
       </c>
       <c r="I50" s="44" t="s">
         <v>271</v>
       </c>
       <c r="J50" s="44" t="s">
-        <v>234</v>
+        <v>348</v>
       </c>
       <c r="K50" s="37" t="s">
         <v>271</v>
@@ -4751,19 +4763,21 @@
         <v>2</v>
       </c>
       <c r="M50" s="44">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N50" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="O50" s="117">
-        <v>0.3135</v>
+      <c r="O50" s="45">
+        <v>3.85E-2</v>
       </c>
       <c r="P50" s="45">
         <f t="shared" ref="P50:P52" si="20">O50*M50</f>
-        <v>1.5674999999999999</v>
-      </c>
-      <c r="Q50" s="44"/>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="Q50" s="73" t="s">
+        <v>349</v>
+      </c>
       <c r="R50" s="49"/>
     </row>
     <row r="51" spans="1:19" ht="36" x14ac:dyDescent="0.25">
@@ -4808,7 +4822,7 @@
       <c r="N51" s="52" t="s">
         <v>285</v>
       </c>
-      <c r="O51" s="116">
+      <c r="O51" s="104">
         <v>0.42799999999999999</v>
       </c>
       <c r="P51" s="38">
@@ -5173,7 +5187,7 @@
       <c r="N58" s="52" t="s">
         <v>285</v>
       </c>
-      <c r="O58" s="115">
+      <c r="O58" s="103">
         <v>5.1212</v>
       </c>
       <c r="P58" s="38">
@@ -5659,17 +5673,17 @@
       <c r="J68" s="79"/>
       <c r="K68" s="80"/>
       <c r="L68" s="80"/>
-      <c r="M68" s="107" t="s">
+      <c r="M68" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="N68" s="108"/>
-      <c r="O68" s="108"/>
+      <c r="N68" s="112"/>
+      <c r="O68" s="112"/>
       <c r="P68" s="41">
         <f>SUM(P10:P67)</f>
-        <v>48.240500000000019</v>
-      </c>
-      <c r="Q68" s="109"/>
-      <c r="R68" s="110"/>
+        <v>47.058000000000014</v>
+      </c>
+      <c r="Q68" s="113"/>
+      <c r="R68" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5709,28 +5723,28 @@
     <hyperlink ref="N46" r:id="rId28"/>
     <hyperlink ref="N47" r:id="rId29"/>
     <hyperlink ref="N48" r:id="rId30"/>
-    <hyperlink ref="N50" r:id="rId31"/>
-    <hyperlink ref="N52" r:id="rId32"/>
-    <hyperlink ref="N53" r:id="rId33"/>
-    <hyperlink ref="N55" r:id="rId34"/>
-    <hyperlink ref="N56" r:id="rId35"/>
-    <hyperlink ref="N57" r:id="rId36"/>
-    <hyperlink ref="N58" r:id="rId37"/>
-    <hyperlink ref="N59" r:id="rId38"/>
-    <hyperlink ref="N60" r:id="rId39"/>
-    <hyperlink ref="N61" r:id="rId40"/>
-    <hyperlink ref="N62" r:id="rId41"/>
-    <hyperlink ref="N63" r:id="rId42"/>
-    <hyperlink ref="N18" r:id="rId43"/>
-    <hyperlink ref="N54" r:id="rId44"/>
-    <hyperlink ref="N41" r:id="rId45"/>
-    <hyperlink ref="N25" r:id="rId46"/>
-    <hyperlink ref="N29" r:id="rId47"/>
-    <hyperlink ref="N32" r:id="rId48"/>
-    <hyperlink ref="N39" r:id="rId49"/>
-    <hyperlink ref="N51" r:id="rId50"/>
-    <hyperlink ref="N67" r:id="rId51"/>
-    <hyperlink ref="N15" r:id="rId52"/>
+    <hyperlink ref="N52" r:id="rId31"/>
+    <hyperlink ref="N53" r:id="rId32"/>
+    <hyperlink ref="N55" r:id="rId33"/>
+    <hyperlink ref="N56" r:id="rId34"/>
+    <hyperlink ref="N57" r:id="rId35"/>
+    <hyperlink ref="N58" r:id="rId36"/>
+    <hyperlink ref="N59" r:id="rId37"/>
+    <hyperlink ref="N60" r:id="rId38"/>
+    <hyperlink ref="N61" r:id="rId39"/>
+    <hyperlink ref="N62" r:id="rId40"/>
+    <hyperlink ref="N63" r:id="rId41"/>
+    <hyperlink ref="N18" r:id="rId42"/>
+    <hyperlink ref="N54" r:id="rId43"/>
+    <hyperlink ref="N41" r:id="rId44"/>
+    <hyperlink ref="N25" r:id="rId45"/>
+    <hyperlink ref="N29" r:id="rId46"/>
+    <hyperlink ref="N32" r:id="rId47"/>
+    <hyperlink ref="N39" r:id="rId48"/>
+    <hyperlink ref="N51" r:id="rId49"/>
+    <hyperlink ref="N67" r:id="rId50"/>
+    <hyperlink ref="N15" r:id="rId51"/>
+    <hyperlink ref="N50" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId53"/>
@@ -5775,15 +5789,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="104"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="108"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5833,7 +5847,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="105"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5858,7 +5872,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="106"/>
+      <c r="S4" s="110"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5883,7 +5897,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="106"/>
+      <c r="S5" s="110"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5904,7 +5918,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="106"/>
+      <c r="S6" s="110"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5925,7 +5939,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="106"/>
+      <c r="S7" s="110"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5946,7 +5960,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="106"/>
+      <c r="S8" s="110"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -9254,17 +9268,17 @@
       <c r="K68" s="69"/>
       <c r="L68" s="69"/>
       <c r="M68" s="69"/>
-      <c r="N68" s="107" t="s">
+      <c r="N68" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="O68" s="108"/>
-      <c r="P68" s="108"/>
+      <c r="O68" s="112"/>
+      <c r="P68" s="112"/>
       <c r="Q68" s="41">
         <f>SUM(Q10:Q67)</f>
         <v>128.43350000000001</v>
       </c>
-      <c r="R68" s="111"/>
-      <c r="S68" s="112"/>
+      <c r="R68" s="115"/>
+      <c r="S68" s="116"/>
     </row>
     <row r="69" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -9280,17 +9294,17 @@
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
       <c r="M69" s="10"/>
-      <c r="N69" s="107" t="s">
+      <c r="N69" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="O69" s="108"/>
-      <c r="P69" s="108"/>
+      <c r="O69" s="112"/>
+      <c r="P69" s="112"/>
       <c r="Q69" s="42">
         <f>Q68/5</f>
         <v>25.686700000000002</v>
       </c>
-      <c r="R69" s="113"/>
-      <c r="S69" s="114"/>
+      <c r="R69" s="117"/>
+      <c r="S69" s="118"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P70" s="74"/>

--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="347">
   <si>
     <t>Component list</t>
   </si>
@@ -325,9 +325,6 @@
     <t>Solder Bridge ON</t>
   </si>
   <si>
-    <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
-  </si>
-  <si>
     <t>Power Supply Support Circuit, Fixed, 1 Channel, +3.1V, CMOS, PDSO5</t>
   </si>
   <si>
@@ -406,9 +403,6 @@
     <t>Solder Bridge</t>
   </si>
   <si>
-    <t>B3U-1000P</t>
-  </si>
-  <si>
     <t>SSOP-5-1.6mm</t>
   </si>
   <si>
@@ -601,9 +595,6 @@
     <t>Diodes</t>
   </si>
   <si>
-    <t>Omron</t>
-  </si>
-  <si>
     <t>Rohm</t>
   </si>
   <si>
@@ -724,9 +715,6 @@
     <t>C724006</t>
   </si>
   <si>
-    <t>C231329</t>
-  </si>
-  <si>
     <t>C253184</t>
   </si>
   <si>
@@ -1060,16 +1048,19 @@
     <t>DNP</t>
   </si>
   <si>
-    <t>No NO J pin 50mA 3mm 100MΩ 100000 12V 250gf@±30gf 2.6mm -30℃~+85℃ 0.65mm Black Round Button Brick nogging SPST SMD Tactile Switches ROHS</t>
-  </si>
-  <si>
-    <t>GT-TC025D-H0065-L1</t>
-  </si>
-  <si>
-    <t>C778132</t>
-  </si>
-  <si>
     <t>Ye Part Design me Change krna ha</t>
+  </si>
+  <si>
+    <t>C381037</t>
+  </si>
+  <si>
+    <t>TS-1109S-C-B</t>
+  </si>
+  <si>
+    <t>No NO 50mA 4.5mm 100000 260gf 12V -30℃~+85℃ 4.5mm 4.3mm Black Round Button Brick nogging SPST SMD Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1291,14 +1282,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1654,12 +1639,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1907,9 +1907,6 @@
     <xf numFmtId="166" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1947,18 +1944,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1999,6 +1984,50 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2427,14 +2456,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="108"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="103"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2445,7 +2474,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="46" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2469,7 +2498,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="47" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2482,7 +2511,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
-      <c r="R3" s="109"/>
+      <c r="R3" s="104"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2493,7 +2522,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="47" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2506,7 +2535,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="110"/>
+      <c r="R4" s="105"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2530,7 +2559,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
-      <c r="R5" s="110"/>
+      <c r="R5" s="105"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2550,7 +2579,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="110"/>
+      <c r="R6" s="105"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2570,7 +2599,7 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="110"/>
+      <c r="R7" s="105"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2590,7 +2619,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
-      <c r="R8" s="110"/>
+      <c r="R8" s="105"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2607,43 +2636,43 @@
         <v>66</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K9" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q9" s="89" t="s">
+        <v>277</v>
+      </c>
+      <c r="R9" s="30" t="s">
         <v>278</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -2656,28 +2685,28 @@
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>67</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -2686,7 +2715,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O10" s="38">
         <v>1.89E-2</v>
@@ -2695,7 +2724,7 @@
         <f>O10*M10</f>
         <v>0.94500000000000006</v>
       </c>
-      <c r="Q10" s="37"/>
+      <c r="Q10" s="90"/>
       <c r="R10" s="71"/>
     </row>
     <row r="11" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -2714,22 +2743,22 @@
         <v>68</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L11" s="44">
         <v>2</v>
@@ -2738,16 +2767,16 @@
         <v>3</v>
       </c>
       <c r="N11" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="O11" s="105">
+        <v>281</v>
+      </c>
+      <c r="O11" s="45">
         <v>1.4064000000000001</v>
       </c>
       <c r="P11" s="45">
         <f t="shared" ref="P11" si="1">O11*M11</f>
         <v>4.2192000000000007</v>
       </c>
-      <c r="Q11" s="44"/>
+      <c r="Q11" s="84"/>
       <c r="R11" s="44"/>
     </row>
     <row r="12" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -2766,22 +2795,22 @@
         <v>69</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="L12" s="37">
         <v>14</v>
@@ -2790,7 +2819,7 @@
         <v>100</v>
       </c>
       <c r="N12" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O12" s="38">
         <v>5.0000000000000001E-3</v>
@@ -2799,7 +2828,7 @@
         <f>O12*M12</f>
         <v>0.5</v>
       </c>
-      <c r="Q12" s="37"/>
+      <c r="Q12" s="90"/>
       <c r="R12" s="49"/>
     </row>
     <row r="13" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -2818,22 +2847,22 @@
         <v>70</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L13" s="44">
         <v>1</v>
@@ -2842,7 +2871,7 @@
         <v>100</v>
       </c>
       <c r="N13" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O13" s="45">
         <v>2.8E-3</v>
@@ -2851,7 +2880,7 @@
         <f t="shared" ref="P13" si="2">O13*M13</f>
         <v>0.27999999999999997</v>
       </c>
-      <c r="Q13" s="44"/>
+      <c r="Q13" s="84"/>
       <c r="R13" s="49"/>
     </row>
     <row r="14" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -2864,28 +2893,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>71</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="L14" s="37">
         <v>22</v>
@@ -2894,7 +2923,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O14" s="38">
         <v>1.8E-3</v>
@@ -2903,7 +2932,7 @@
         <f>O14*M14</f>
         <v>0.18</v>
       </c>
-      <c r="Q14" s="37"/>
+      <c r="Q14" s="90"/>
       <c r="R14" s="49"/>
     </row>
     <row r="15" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -2922,22 +2951,22 @@
         <v>72</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G15" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L15" s="44">
         <v>2</v>
@@ -2946,7 +2975,7 @@
         <v>20</v>
       </c>
       <c r="N15" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O15" s="45">
         <v>1.77E-2</v>
@@ -2955,7 +2984,7 @@
         <f t="shared" ref="P15" si="3">O15*M15</f>
         <v>0.35399999999999998</v>
       </c>
-      <c r="Q15" s="44"/>
+      <c r="Q15" s="84"/>
       <c r="R15" s="49"/>
     </row>
     <row r="16" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -2974,22 +3003,22 @@
         <v>73</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L16" s="37">
         <v>2</v>
@@ -2998,7 +3027,7 @@
         <v>5</v>
       </c>
       <c r="N16" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O16" s="38">
         <v>0.42320000000000002</v>
@@ -3007,7 +3036,7 @@
         <f>O16*M16</f>
         <v>2.1160000000000001</v>
       </c>
-      <c r="Q16" s="37"/>
+      <c r="Q16" s="90"/>
       <c r="R16" s="49"/>
     </row>
     <row r="17" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3026,22 +3055,22 @@
         <v>74</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L17" s="44">
         <v>6</v>
@@ -3050,7 +3079,7 @@
         <v>20</v>
       </c>
       <c r="N17" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O17" s="45">
         <v>2.3800000000000002E-2</v>
@@ -3059,7 +3088,7 @@
         <f t="shared" ref="P17" si="4">O17*M17</f>
         <v>0.47600000000000003</v>
       </c>
-      <c r="Q17" s="44"/>
+      <c r="Q17" s="84"/>
       <c r="R17" s="49"/>
     </row>
     <row r="18" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3078,22 +3107,22 @@
         <v>75</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G18" s="54" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -3102,7 +3131,7 @@
         <v>50</v>
       </c>
       <c r="N18" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O18" s="38">
         <v>5.4999999999999997E-3</v>
@@ -3111,7 +3140,7 @@
         <f>O18*M18</f>
         <v>0.27499999999999997</v>
       </c>
-      <c r="Q18" s="37"/>
+      <c r="Q18" s="90"/>
       <c r="R18" s="49"/>
     </row>
     <row r="19" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3130,22 +3159,22 @@
         <v>76</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L19" s="44">
         <v>1</v>
@@ -3154,7 +3183,7 @@
         <v>20</v>
       </c>
       <c r="N19" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O19" s="45">
         <v>2.0199999999999999E-2</v>
@@ -3163,7 +3192,7 @@
         <f t="shared" ref="P19:P20" si="5">O19*M19</f>
         <v>0.40399999999999997</v>
       </c>
-      <c r="Q19" s="44"/>
+      <c r="Q19" s="84"/>
       <c r="R19" s="49"/>
     </row>
     <row r="20" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3182,22 +3211,22 @@
         <v>77</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H20" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L20" s="44">
         <v>2</v>
@@ -3206,7 +3235,7 @@
         <v>100</v>
       </c>
       <c r="N20" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O20" s="45">
         <v>3.7000000000000002E-3</v>
@@ -3215,7 +3244,7 @@
         <f t="shared" si="5"/>
         <v>0.37</v>
       </c>
-      <c r="Q20" s="44"/>
+      <c r="Q20" s="84"/>
       <c r="R20" s="49"/>
     </row>
     <row r="21" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3234,22 +3263,22 @@
         <v>78</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="L21" s="37">
         <v>2</v>
@@ -3258,7 +3287,7 @@
         <v>100</v>
       </c>
       <c r="N21" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O21" s="38">
         <v>4.4999999999999997E-3</v>
@@ -3267,7 +3296,7 @@
         <f>O21*M21</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="Q21" s="37"/>
+      <c r="Q21" s="90"/>
       <c r="R21" s="49"/>
     </row>
     <row r="22" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3286,22 +3315,22 @@
         <v>79</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L22" s="44">
         <v>1</v>
@@ -3310,7 +3339,7 @@
         <v>100</v>
       </c>
       <c r="N22" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O22" s="45">
         <v>3.2000000000000002E-3</v>
@@ -3319,7 +3348,7 @@
         <f t="shared" ref="P22" si="6">O22*M22</f>
         <v>0.32</v>
       </c>
-      <c r="Q22" s="44"/>
+      <c r="Q22" s="84"/>
       <c r="R22" s="49"/>
     </row>
     <row r="23" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3338,22 +3367,22 @@
         <v>80</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H23" s="44" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L23" s="44">
         <v>1</v>
@@ -3362,7 +3391,7 @@
         <v>5</v>
       </c>
       <c r="N23" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O23" s="45">
         <v>8.6400000000000005E-2</v>
@@ -3371,7 +3400,7 @@
         <f t="shared" ref="P23" si="7">O23*M23</f>
         <v>0.43200000000000005</v>
       </c>
-      <c r="Q23" s="44"/>
+      <c r="Q23" s="84"/>
       <c r="R23" s="49"/>
     </row>
     <row r="24" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -3390,22 +3419,22 @@
         <v>81</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -3414,7 +3443,7 @@
         <v>20</v>
       </c>
       <c r="N24" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O24" s="38">
         <v>2.63E-2</v>
@@ -3423,7 +3452,7 @@
         <f>O24*M24</f>
         <v>0.52600000000000002</v>
       </c>
-      <c r="Q24" s="37"/>
+      <c r="Q24" s="90"/>
       <c r="R24" s="49"/>
     </row>
     <row r="25" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -3436,28 +3465,28 @@
         <v>10</v>
       </c>
       <c r="D25" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="F25" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="H25" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="I25" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="J25" s="44" t="s">
-        <v>305</v>
-      </c>
       <c r="K25" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L25" s="44">
         <v>1</v>
@@ -3466,7 +3495,7 @@
         <v>20</v>
       </c>
       <c r="N25" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O25" s="44">
         <v>3.8100000000000002E-2</v>
@@ -3475,7 +3504,7 @@
         <f>O25*M25</f>
         <v>0.76200000000000001</v>
       </c>
-      <c r="Q25" s="45"/>
+      <c r="Q25" s="115"/>
       <c r="R25" s="44"/>
     </row>
     <row r="26" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3494,22 +3523,22 @@
         <v>82</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L26" s="37">
         <v>2</v>
@@ -3518,7 +3547,7 @@
         <v>20</v>
       </c>
       <c r="N26" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O26" s="38">
         <v>3.2199999999999999E-2</v>
@@ -3527,7 +3556,7 @@
         <f>O26*M26</f>
         <v>0.64400000000000002</v>
       </c>
-      <c r="Q26" s="37"/>
+      <c r="Q26" s="90"/>
       <c r="R26" s="49"/>
     </row>
     <row r="27" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3546,22 +3575,22 @@
         <v>83</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H27" s="44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L27" s="44">
         <v>1</v>
@@ -3570,7 +3599,7 @@
         <v>50</v>
       </c>
       <c r="N27" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O27" s="45">
         <v>8.8999999999999999E-3</v>
@@ -3579,7 +3608,7 @@
         <f t="shared" ref="P27" si="9">O27*M27</f>
         <v>0.44500000000000001</v>
       </c>
-      <c r="Q27" s="44"/>
+      <c r="Q27" s="84"/>
       <c r="R27" s="49"/>
     </row>
     <row r="28" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -3589,31 +3618,31 @@
         <v>19</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D28" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3622,15 +3651,15 @@
         <v>5</v>
       </c>
       <c r="N28" s="52" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O28" s="38" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P28" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q28" s="37"/>
+        <v>267</v>
+      </c>
+      <c r="Q28" s="90"/>
       <c r="R28" s="49"/>
     </row>
     <row r="29" spans="1:18" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
@@ -3643,28 +3672,28 @@
         <v>13</v>
       </c>
       <c r="D29" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="I29" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="J29" s="44" t="s">
         <v>309</v>
       </c>
-      <c r="E29" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="G29" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="H29" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="I29" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>313</v>
-      </c>
       <c r="K29" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L29" s="44">
         <v>3</v>
@@ -3673,7 +3702,7 @@
         <v>20</v>
       </c>
       <c r="N29" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O29" s="45">
         <v>2.52E-2</v>
@@ -3682,7 +3711,7 @@
         <f t="shared" ref="P29" si="10">O29*M29</f>
         <v>0.504</v>
       </c>
-      <c r="Q29" s="44"/>
+      <c r="Q29" s="84"/>
       <c r="R29" s="49"/>
     </row>
     <row r="30" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3701,22 +3730,22 @@
         <v>84</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3725,16 +3754,16 @@
         <v>2</v>
       </c>
       <c r="N30" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O30" s="38" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P30" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q30" s="106" t="s">
-        <v>345</v>
+        <v>267</v>
+      </c>
+      <c r="Q30" s="116" t="s">
+        <v>341</v>
       </c>
       <c r="R30" s="49"/>
     </row>
@@ -3745,7 +3774,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D31" s="44" t="s">
         <v>39</v>
@@ -3754,22 +3783,22 @@
         <v>85</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H31" s="44" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I31" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J31" s="44" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L31" s="44">
         <v>1</v>
@@ -3778,7 +3807,7 @@
         <v>2</v>
       </c>
       <c r="N31" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O31" s="45">
         <v>0.9546</v>
@@ -3787,7 +3816,7 @@
         <f t="shared" ref="P31" si="11">O31*M31</f>
         <v>1.9092</v>
       </c>
-      <c r="Q31" s="44"/>
+      <c r="Q31" s="84"/>
       <c r="R31" s="49"/>
     </row>
     <row r="32" spans="1:18" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
@@ -3797,31 +3826,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>318</v>
-      </c>
       <c r="K32" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3830,7 +3859,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O32" s="38">
         <v>3.8199999999999998E-2</v>
@@ -3839,7 +3868,7 @@
         <f>O32*M32</f>
         <v>0.38200000000000001</v>
       </c>
-      <c r="Q32" s="37"/>
+      <c r="Q32" s="90"/>
       <c r="R32" s="49"/>
     </row>
     <row r="33" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3858,22 +3887,22 @@
         <v>86</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H33" s="44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J33" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L33" s="44">
         <v>1</v>
@@ -3882,7 +3911,7 @@
         <v>2</v>
       </c>
       <c r="N33" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O33" s="45">
         <v>0.29110000000000003</v>
@@ -3891,7 +3920,7 @@
         <f t="shared" ref="P33" si="12">O33*M33</f>
         <v>0.58220000000000005</v>
       </c>
-      <c r="Q33" s="44"/>
+      <c r="Q33" s="84"/>
       <c r="R33" s="49"/>
     </row>
     <row r="34" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -3910,39 +3939,39 @@
         <v>87</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G34" s="54" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H34" s="55" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I34" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J34" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K34" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L34" s="54">
         <v>13</v>
       </c>
       <c r="M34" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N34" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O34" s="57" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P34" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q34" s="54"/>
+        <v>267</v>
+      </c>
+      <c r="Q34" s="117"/>
       <c r="R34" s="58"/>
     </row>
     <row r="35" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -3961,22 +3990,22 @@
         <v>88</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H35" s="44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J35" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L35" s="44">
         <v>1</v>
@@ -3985,7 +4014,7 @@
         <v>10</v>
       </c>
       <c r="N35" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O35" s="45">
         <v>4.6899999999999997E-2</v>
@@ -3994,7 +4023,7 @@
         <f t="shared" ref="P35" si="13">O35*M35</f>
         <v>0.46899999999999997</v>
       </c>
-      <c r="Q35" s="44"/>
+      <c r="Q35" s="84"/>
       <c r="R35" s="49"/>
     </row>
     <row r="36" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4013,22 +4042,22 @@
         <v>89</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -4037,7 +4066,7 @@
         <v>20</v>
       </c>
       <c r="N36" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O36" s="38">
         <v>3.49E-2</v>
@@ -4046,7 +4075,7 @@
         <f>O36*M36</f>
         <v>0.69799999999999995</v>
       </c>
-      <c r="Q36" s="37"/>
+      <c r="Q36" s="90"/>
       <c r="R36" s="49"/>
     </row>
     <row r="37" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4059,28 +4088,28 @@
         <v>17</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>90</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H37" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="L37" s="44">
         <v>11</v>
@@ -4089,7 +4118,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O37" s="45">
         <v>1E-3</v>
@@ -4098,8 +4127,8 @@
         <f t="shared" ref="P37" si="14">O37*M37</f>
         <v>0.1</v>
       </c>
-      <c r="Q37" s="73" t="s">
-        <v>299</v>
+      <c r="Q37" s="114" t="s">
+        <v>295</v>
       </c>
       <c r="R37" s="49"/>
     </row>
@@ -4119,22 +4148,22 @@
         <v>91</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H38" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I38" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J38" s="44" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="L38" s="44">
         <v>3</v>
@@ -4143,7 +4172,7 @@
         <v>100</v>
       </c>
       <c r="N38" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O38" s="45">
         <v>1.1000000000000001E-3</v>
@@ -4152,7 +4181,7 @@
         <f t="shared" ref="P38" si="15">O38*M38</f>
         <v>0.11</v>
       </c>
-      <c r="Q38" s="44"/>
+      <c r="Q38" s="84"/>
       <c r="R38" s="49"/>
     </row>
     <row r="39" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4168,25 +4197,25 @@
         <v>45</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H39" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I39" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J39" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K39" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L39" s="44">
         <v>1</v>
@@ -4195,7 +4224,7 @@
         <v>100</v>
       </c>
       <c r="N39" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O39" s="38">
         <v>1.2999999999999999E-3</v>
@@ -4204,7 +4233,7 @@
         <f>O39*M39</f>
         <v>0.13</v>
       </c>
-      <c r="Q39" s="37"/>
+      <c r="Q39" s="90"/>
       <c r="R39" s="49"/>
     </row>
     <row r="40" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4223,22 +4252,22 @@
         <v>92</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L40" s="37">
         <v>2</v>
@@ -4247,7 +4276,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O40" s="38">
         <v>1.1000000000000001E-3</v>
@@ -4256,7 +4285,7 @@
         <f>O40*M40</f>
         <v>0.11</v>
       </c>
-      <c r="Q40" s="37"/>
+      <c r="Q40" s="90"/>
       <c r="R40" s="49"/>
     </row>
     <row r="41" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4272,25 +4301,25 @@
         <v>47</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F41" s="44" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G41" s="44" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H41" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I41" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J41" s="44" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="K41" s="44" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="L41" s="44">
         <v>1</v>
@@ -4299,7 +4328,7 @@
         <v>20</v>
       </c>
       <c r="N41" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O41" s="45">
         <v>2.7699999999999999E-2</v>
@@ -4308,7 +4337,7 @@
         <f t="shared" ref="P41" si="16">O41*M41</f>
         <v>0.55399999999999994</v>
       </c>
-      <c r="Q41" s="44"/>
+      <c r="Q41" s="84"/>
       <c r="R41" s="49"/>
     </row>
     <row r="42" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4327,22 +4356,22 @@
         <v>93</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L42" s="37">
         <v>5</v>
@@ -4351,7 +4380,7 @@
         <v>100</v>
       </c>
       <c r="N42" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O42" s="38">
         <v>1.1999999999999999E-3</v>
@@ -4360,7 +4389,7 @@
         <f>O42*M42</f>
         <v>0.12</v>
       </c>
-      <c r="Q42" s="37"/>
+      <c r="Q42" s="90"/>
       <c r="R42" s="49"/>
     </row>
     <row r="43" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4379,22 +4408,22 @@
         <v>94</v>
       </c>
       <c r="F43" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G43" s="44" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H43" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I43" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J43" s="44" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="L43" s="44">
         <v>2</v>
@@ -4403,7 +4432,7 @@
         <v>100</v>
       </c>
       <c r="N43" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O43" s="45">
         <v>3.0999999999999999E-3</v>
@@ -4412,7 +4441,7 @@
         <f t="shared" ref="P43" si="17">O43*M43</f>
         <v>0.31</v>
       </c>
-      <c r="Q43" s="44"/>
+      <c r="Q43" s="84"/>
       <c r="R43" s="49"/>
     </row>
     <row r="44" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4431,22 +4460,22 @@
         <v>95</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="L44" s="37">
         <v>3</v>
@@ -4455,7 +4484,7 @@
         <v>100</v>
       </c>
       <c r="N44" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O44" s="38">
         <v>1.1000000000000001E-3</v>
@@ -4464,7 +4493,7 @@
         <f>O44*M44</f>
         <v>0.11</v>
       </c>
-      <c r="Q44" s="37"/>
+      <c r="Q44" s="90"/>
       <c r="R44" s="49"/>
     </row>
     <row r="45" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4483,22 +4512,22 @@
         <v>96</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H45" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="L45" s="44">
         <v>2</v>
@@ -4507,7 +4536,7 @@
         <v>100</v>
       </c>
       <c r="N45" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O45" s="45">
         <v>1.1999999999999999E-3</v>
@@ -4516,7 +4545,7 @@
         <f t="shared" ref="P45" si="18">O45*M45</f>
         <v>0.12</v>
       </c>
-      <c r="Q45" s="44"/>
+      <c r="Q45" s="84"/>
       <c r="R45" s="49"/>
     </row>
     <row r="46" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4535,22 +4564,22 @@
         <v>97</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L46" s="37">
         <v>2</v>
@@ -4559,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="N46" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O46" s="38">
         <v>1.8E-3</v>
@@ -4568,60 +4597,60 @@
         <f>O46*M46</f>
         <v>0.18</v>
       </c>
-      <c r="Q46" s="37"/>
+      <c r="Q46" s="90"/>
       <c r="R46" s="49"/>
     </row>
-    <row r="47" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="70"/>
-      <c r="B47" s="40">
+    <row r="47" spans="1:18" s="129" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="121"/>
+      <c r="B47" s="122">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="44" t="s">
+      <c r="E47" s="124" t="s">
         <v>98</v>
       </c>
-      <c r="F47" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="G47" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="H47" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="I47" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="J47" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="K47" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L47" s="44">
+      <c r="F47" s="124" t="s">
+        <v>125</v>
+      </c>
+      <c r="G47" s="124" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" s="124" t="s">
+        <v>181</v>
+      </c>
+      <c r="I47" s="124" t="s">
+        <v>267</v>
+      </c>
+      <c r="J47" s="124" t="s">
+        <v>229</v>
+      </c>
+      <c r="K47" s="124" t="s">
+        <v>263</v>
+      </c>
+      <c r="L47" s="124">
         <v>1</v>
       </c>
-      <c r="M47" s="44">
+      <c r="M47" s="124">
         <v>20</v>
       </c>
-      <c r="N47" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="O47" s="45">
+      <c r="N47" s="125" t="s">
+        <v>281</v>
+      </c>
+      <c r="O47" s="126">
         <v>2.75E-2</v>
       </c>
-      <c r="P47" s="45">
+      <c r="P47" s="126">
         <f t="shared" ref="P47" si="19">O47*M47</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="49"/>
+      <c r="Q47" s="127"/>
+      <c r="R47" s="128"/>
     </row>
     <row r="48" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="70"/>
@@ -4639,22 +4668,22 @@
         <v>99</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K48" s="37" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="L48" s="37">
         <v>1</v>
@@ -4663,7 +4692,7 @@
         <v>50</v>
       </c>
       <c r="N48" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O48" s="38">
         <v>8.8000000000000005E-3</v>
@@ -4672,7 +4701,7 @@
         <f>O48*M48</f>
         <v>0.44</v>
       </c>
-      <c r="Q48" s="37"/>
+      <c r="Q48" s="90"/>
       <c r="R48" s="49"/>
     </row>
     <row r="49" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4682,51 +4711,51 @@
         <v>40</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E49" s="54" t="s">
         <v>100</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G49" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H49" s="55" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I49" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J49" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K49" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L49" s="54">
         <v>6</v>
       </c>
       <c r="M49" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N49" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O49" s="57" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P49" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q49" s="54"/>
+        <v>267</v>
+      </c>
+      <c r="Q49" s="117"/>
       <c r="R49" s="58"/>
     </row>
-    <row r="50" spans="1:19" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="70"/>
       <c r="B50" s="40">
         <f t="shared" si="0"/>
@@ -4736,49 +4765,49 @@
         <v>18</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F50" s="44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H50" s="44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I50" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J50" s="44" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L50" s="44">
         <v>2</v>
       </c>
       <c r="M50" s="44">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N50" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O50" s="45">
-        <v>3.85E-2</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="P50" s="45">
         <f t="shared" ref="P50:P52" si="20">O50*M50</f>
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="Q50" s="73" t="s">
-        <v>349</v>
-      </c>
-      <c r="R50" s="49"/>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="Q50" s="114" t="s">
+        <v>342</v>
+      </c>
+      <c r="R50" s="44"/>
     </row>
     <row r="51" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
@@ -4790,28 +4819,28 @@
         <v>18</v>
       </c>
       <c r="D51" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="G51" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="I51" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="E51" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>325</v>
-      </c>
       <c r="K51" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L51" s="37">
         <v>1</v>
@@ -4820,16 +4849,16 @@
         <v>2</v>
       </c>
       <c r="N51" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="O51" s="104">
+        <v>281</v>
+      </c>
+      <c r="O51" s="45">
         <v>0.42799999999999999</v>
       </c>
       <c r="P51" s="38">
         <f>O51*M51</f>
         <v>0.85599999999999998</v>
       </c>
-      <c r="Q51" s="38"/>
+      <c r="Q51" s="118"/>
       <c r="R51" s="37"/>
       <c r="S51" s="72"/>
     </row>
@@ -4843,28 +4872,28 @@
         <v>18</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F52" s="44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G52" s="44" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H52" s="44" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I52" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J52" s="44" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L52" s="44">
         <v>1</v>
@@ -4873,7 +4902,7 @@
         <v>10</v>
       </c>
       <c r="N52" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O52" s="45">
         <v>6.2100000000000002E-2</v>
@@ -4882,7 +4911,7 @@
         <f t="shared" si="20"/>
         <v>0.621</v>
       </c>
-      <c r="Q52" s="44"/>
+      <c r="Q52" s="84"/>
       <c r="R52" s="49"/>
     </row>
     <row r="53" spans="1:19" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
@@ -4898,25 +4927,25 @@
         <v>55</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K53" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L53" s="37">
         <v>1</v>
@@ -4925,7 +4954,7 @@
         <v>2</v>
       </c>
       <c r="N53" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O53" s="38">
         <v>0.16209999999999999</v>
@@ -4934,7 +4963,7 @@
         <f>O53*M53</f>
         <v>0.32419999999999999</v>
       </c>
-      <c r="Q53" s="37"/>
+      <c r="Q53" s="90"/>
       <c r="R53" s="49"/>
     </row>
     <row r="54" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -4950,25 +4979,25 @@
         <v>56</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F54" s="44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G54" s="44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H54" s="44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I54" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J54" s="44" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L54" s="44">
         <v>1</v>
@@ -4977,7 +5006,7 @@
         <v>5</v>
       </c>
       <c r="N54" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O54" s="45">
         <v>0.1341</v>
@@ -4986,7 +5015,7 @@
         <f t="shared" ref="P54" si="21">O54*M54</f>
         <v>0.67049999999999998</v>
       </c>
-      <c r="Q54" s="44"/>
+      <c r="Q54" s="84"/>
       <c r="R54" s="49"/>
     </row>
     <row r="55" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5002,25 +5031,25 @@
         <v>57</v>
       </c>
       <c r="E55" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K55" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L55" s="37">
         <v>1</v>
@@ -5029,7 +5058,7 @@
         <v>5</v>
       </c>
       <c r="N55" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O55" s="38">
         <v>0.19539999999999999</v>
@@ -5038,7 +5067,7 @@
         <f>O55*M55</f>
         <v>0.97699999999999998</v>
       </c>
-      <c r="Q55" s="37"/>
+      <c r="Q55" s="90"/>
       <c r="R55" s="49"/>
     </row>
     <row r="56" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5054,25 +5083,25 @@
         <v>58</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F56" s="44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H56" s="44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I56" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J56" s="44" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L56" s="44">
         <v>1</v>
@@ -5081,7 +5110,7 @@
         <v>2</v>
       </c>
       <c r="N56" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O56" s="45">
         <v>0.43909999999999999</v>
@@ -5090,7 +5119,7 @@
         <f t="shared" ref="P56" si="22">O56*M56</f>
         <v>0.87819999999999998</v>
       </c>
-      <c r="Q56" s="44"/>
+      <c r="Q56" s="84"/>
       <c r="R56" s="49"/>
     </row>
     <row r="57" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5106,25 +5135,25 @@
         <v>59</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L57" s="37">
         <v>1</v>
@@ -5133,7 +5162,7 @@
         <v>5</v>
       </c>
       <c r="N57" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O57" s="38">
         <v>0.15479999999999999</v>
@@ -5142,7 +5171,7 @@
         <f>O57*M57</f>
         <v>0.77400000000000002</v>
       </c>
-      <c r="Q57" s="37"/>
+      <c r="Q57" s="90"/>
       <c r="R57" s="49"/>
     </row>
     <row r="58" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5158,25 +5187,25 @@
         <v>60</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L58" s="37">
         <v>1</v>
@@ -5185,16 +5214,16 @@
         <v>2</v>
       </c>
       <c r="N58" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="O58" s="103">
+        <v>281</v>
+      </c>
+      <c r="O58" s="38">
         <v>5.1212</v>
       </c>
       <c r="P58" s="38">
         <f>O58*M58</f>
         <v>10.2424</v>
       </c>
-      <c r="Q58" s="37"/>
+      <c r="Q58" s="90"/>
       <c r="R58" s="49"/>
     </row>
     <row r="59" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5210,25 +5239,25 @@
         <v>61</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F59" s="44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H59" s="44" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I59" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L59" s="44">
         <v>1</v>
@@ -5237,7 +5266,7 @@
         <v>5</v>
       </c>
       <c r="N59" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O59" s="45">
         <v>0.15670000000000001</v>
@@ -5246,7 +5275,7 @@
         <f t="shared" ref="P59" si="23">O59*M59</f>
         <v>0.78350000000000009</v>
       </c>
-      <c r="Q59" s="44"/>
+      <c r="Q59" s="84"/>
       <c r="R59" s="49"/>
     </row>
     <row r="60" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5262,25 +5291,25 @@
         <v>62</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L60" s="37">
         <v>1</v>
@@ -5289,7 +5318,7 @@
         <v>2</v>
       </c>
       <c r="N60" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O60" s="38">
         <v>0.96889999999999998</v>
@@ -5298,7 +5327,7 @@
         <f>O60*M60</f>
         <v>1.9378</v>
       </c>
-      <c r="Q60" s="37"/>
+      <c r="Q60" s="90"/>
       <c r="R60" s="49"/>
     </row>
     <row r="61" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
@@ -5314,25 +5343,25 @@
         <v>63</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F61" s="44" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G61" s="44" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H61" s="44" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I61" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J61" s="44" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L61" s="44">
         <v>1</v>
@@ -5341,7 +5370,7 @@
         <v>2</v>
       </c>
       <c r="N61" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O61" s="45">
         <v>0.28870000000000001</v>
@@ -5350,7 +5379,7 @@
         <f t="shared" ref="P61" si="24">O61*M61</f>
         <v>0.57740000000000002</v>
       </c>
-      <c r="Q61" s="44"/>
+      <c r="Q61" s="84"/>
       <c r="R61" s="49"/>
     </row>
     <row r="62" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5366,25 +5395,25 @@
         <v>64</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K62" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -5393,7 +5422,7 @@
         <v>2</v>
       </c>
       <c r="N62" s="52" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O62" s="38">
         <v>2.0651000000000002</v>
@@ -5402,7 +5431,7 @@
         <f>O62*M62</f>
         <v>4.1302000000000003</v>
       </c>
-      <c r="Q62" s="37"/>
+      <c r="Q62" s="90"/>
       <c r="R62" s="49"/>
     </row>
     <row r="63" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -5418,25 +5447,25 @@
         <v>65</v>
       </c>
       <c r="E63" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F63" s="49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G63" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H63" s="49" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I63" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J63" s="49" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K63" s="61" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L63" s="49">
         <v>1</v>
@@ -5445,7 +5474,7 @@
         <v>2</v>
       </c>
       <c r="N63" s="62" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O63" s="63">
         <v>1.2919</v>
@@ -5454,7 +5483,7 @@
         <f t="shared" ref="P63" si="25">O63*M63</f>
         <v>2.5838000000000001</v>
       </c>
-      <c r="Q63" s="49"/>
+      <c r="Q63" s="92"/>
       <c r="R63" s="49"/>
     </row>
     <row r="64" spans="1:19" s="72" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
@@ -5464,47 +5493,47 @@
         <v>55</v>
       </c>
       <c r="C64" s="60" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L64" s="49">
         <v>1</v>
       </c>
       <c r="M64" s="49"/>
       <c r="N64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P64" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q64" s="89" t="s">
-        <v>341</v>
+        <v>267</v>
+      </c>
+      <c r="Q64" s="119" t="s">
+        <v>337</v>
       </c>
       <c r="R64" s="49"/>
     </row>
@@ -5515,47 +5544,47 @@
         <v>56</v>
       </c>
       <c r="C65" s="60" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L65" s="49">
         <v>1</v>
       </c>
       <c r="M65" s="49"/>
       <c r="N65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P65" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q65" s="89" t="s">
-        <v>341</v>
+        <v>267</v>
+      </c>
+      <c r="Q65" s="119" t="s">
+        <v>337</v>
       </c>
       <c r="R65" s="49"/>
     </row>
@@ -5566,28 +5595,28 @@
         <v>57</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K66" s="49"/>
       <c r="L66" s="49">
@@ -5595,16 +5624,16 @@
       </c>
       <c r="M66" s="49"/>
       <c r="N66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P66" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q66" s="89" t="s">
-        <v>341</v>
+        <v>267</v>
+      </c>
+      <c r="Q66" s="119" t="s">
+        <v>337</v>
       </c>
       <c r="R66" s="49"/>
     </row>
@@ -5615,31 +5644,31 @@
         <v>58</v>
       </c>
       <c r="C67" s="60" t="s">
+        <v>331</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="G67" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="H67" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="I67" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="J67" s="49" t="s">
         <v>335</v>
       </c>
-      <c r="D67" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="E67" s="49" t="s">
-        <v>336</v>
-      </c>
-      <c r="F67" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="G67" s="49" t="s">
-        <v>337</v>
-      </c>
-      <c r="H67" s="49" t="s">
-        <v>338</v>
-      </c>
-      <c r="I67" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="J67" s="49" t="s">
-        <v>339</v>
-      </c>
       <c r="K67" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L67" s="49">
         <v>1</v>
@@ -5648,7 +5677,7 @@
         <v>2</v>
       </c>
       <c r="N67" s="62" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O67" s="63">
         <v>0.1202</v>
@@ -5657,8 +5686,8 @@
         <f>O67*M67</f>
         <v>0.2404</v>
       </c>
-      <c r="Q67" s="49"/>
-      <c r="R67" s="49"/>
+      <c r="Q67" s="92"/>
+      <c r="R67" s="120"/>
     </row>
     <row r="68" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -5673,17 +5702,17 @@
       <c r="J68" s="79"/>
       <c r="K68" s="80"/>
       <c r="L68" s="80"/>
-      <c r="M68" s="111" t="s">
+      <c r="M68" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="N68" s="112"/>
-      <c r="O68" s="112"/>
+      <c r="N68" s="107"/>
+      <c r="O68" s="107"/>
       <c r="P68" s="41">
         <f>SUM(P10:P67)</f>
-        <v>47.058000000000014</v>
-      </c>
-      <c r="Q68" s="113"/>
-      <c r="R68" s="114"/>
+        <v>47.065000000000019</v>
+      </c>
+      <c r="Q68" s="108"/>
+      <c r="R68" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5789,15 +5818,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="108"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="103"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5808,7 +5837,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="46" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -5833,7 +5862,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="47" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -5847,7 +5876,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="109"/>
+      <c r="S3" s="104"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5858,7 +5887,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="47" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -5872,7 +5901,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="110"/>
+      <c r="S4" s="105"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5897,7 +5926,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="110"/>
+      <c r="S5" s="105"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5918,7 +5947,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="110"/>
+      <c r="S6" s="105"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5939,7 +5968,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="110"/>
+      <c r="S7" s="105"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5960,7 +5989,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="110"/>
+      <c r="S8" s="105"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5977,46 +6006,46 @@
         <v>66</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="N9" s="89" t="s">
+        <v>273</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="P9" s="94" t="s">
         <v>275</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>274</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="N9" s="90" t="s">
+      <c r="R9" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>278</v>
-      </c>
-      <c r="P9" s="95" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -6029,28 +6058,28 @@
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>67</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="L10" s="37">
         <v>3</v>
@@ -6059,13 +6088,13 @@
         <f>L10*5</f>
         <v>15</v>
       </c>
-      <c r="N10" s="91">
+      <c r="N10" s="90">
         <v>50</v>
       </c>
       <c r="O10" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P10" s="96">
+        <v>281</v>
+      </c>
+      <c r="P10" s="95">
         <v>1.89E-2</v>
       </c>
       <c r="Q10" s="81">
@@ -6091,22 +6120,22 @@
         <v>68</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L11" s="44">
         <v>2</v>
@@ -6119,9 +6148,9 @@
         <v>11</v>
       </c>
       <c r="O11" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P11" s="97">
+        <v>281</v>
+      </c>
+      <c r="P11" s="96">
         <v>1.4064000000000001</v>
       </c>
       <c r="Q11" s="81">
@@ -6147,22 +6176,22 @@
         <v>69</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="L12" s="37">
         <v>14</v>
@@ -6171,13 +6200,13 @@
         <f>L12*5</f>
         <v>70</v>
       </c>
-      <c r="N12" s="91">
+      <c r="N12" s="90">
         <v>100</v>
       </c>
       <c r="O12" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P12" s="96">
+        <v>281</v>
+      </c>
+      <c r="P12" s="95">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q12" s="81">
@@ -6203,22 +6232,22 @@
         <v>70</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L13" s="44">
         <v>1</v>
@@ -6231,9 +6260,9 @@
         <v>100</v>
       </c>
       <c r="O13" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P13" s="97">
+        <v>281</v>
+      </c>
+      <c r="P13" s="96">
         <v>2.8E-3</v>
       </c>
       <c r="Q13" s="81">
@@ -6253,28 +6282,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>71</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="L14" s="37">
         <v>22</v>
@@ -6283,13 +6312,13 @@
         <f>L14*5</f>
         <v>110</v>
       </c>
-      <c r="N14" s="91">
+      <c r="N14" s="90">
         <v>200</v>
       </c>
       <c r="O14" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P14" s="96">
+        <v>281</v>
+      </c>
+      <c r="P14" s="95">
         <v>1.8E-3</v>
       </c>
       <c r="Q14" s="81">
@@ -6315,22 +6344,22 @@
         <v>72</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G15" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L15" s="44">
         <v>2</v>
@@ -6343,7 +6372,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="P15" s="45">
         <v>1.77E-2</v>
@@ -6371,22 +6400,22 @@
         <v>73</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L16" s="37">
         <v>2</v>
@@ -6395,13 +6424,13 @@
         <f>L16*5</f>
         <v>10</v>
       </c>
-      <c r="N16" s="91">
+      <c r="N16" s="90">
         <v>15</v>
       </c>
       <c r="O16" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P16" s="96">
+        <v>281</v>
+      </c>
+      <c r="P16" s="95">
         <v>0.42320000000000002</v>
       </c>
       <c r="Q16" s="81">
@@ -6427,22 +6456,22 @@
         <v>74</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L17" s="44">
         <v>6</v>
@@ -6455,9 +6484,9 @@
         <v>40</v>
       </c>
       <c r="O17" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P17" s="97">
+        <v>281</v>
+      </c>
+      <c r="P17" s="96">
         <v>2.3800000000000002E-2</v>
       </c>
       <c r="Q17" s="81">
@@ -6483,22 +6512,22 @@
         <v>75</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G18" s="54" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -6507,13 +6536,13 @@
         <f>L18*5</f>
         <v>15</v>
       </c>
-      <c r="N18" s="91">
+      <c r="N18" s="90">
         <v>50</v>
       </c>
       <c r="O18" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P18" s="96">
+        <v>281</v>
+      </c>
+      <c r="P18" s="95">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q18" s="81">
@@ -6539,22 +6568,22 @@
         <v>76</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L19" s="44">
         <v>1</v>
@@ -6567,9 +6596,9 @@
         <v>20</v>
       </c>
       <c r="O19" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P19" s="97">
+        <v>281</v>
+      </c>
+      <c r="P19" s="96">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="Q19" s="81">
@@ -6595,22 +6624,22 @@
         <v>77</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H20" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L20" s="44">
         <v>2</v>
@@ -6623,9 +6652,9 @@
         <v>100</v>
       </c>
       <c r="O20" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P20" s="97">
+        <v>281</v>
+      </c>
+      <c r="P20" s="96">
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="Q20" s="81">
@@ -6651,22 +6680,22 @@
         <v>78</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="L21" s="37">
         <v>2</v>
@@ -6675,13 +6704,13 @@
         <f>L21*5</f>
         <v>10</v>
       </c>
-      <c r="N21" s="91">
+      <c r="N21" s="90">
         <v>100</v>
       </c>
       <c r="O21" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P21" s="96">
+        <v>281</v>
+      </c>
+      <c r="P21" s="95">
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="Q21" s="81">
@@ -6707,22 +6736,22 @@
         <v>79</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L22" s="44">
         <v>1</v>
@@ -6735,9 +6764,9 @@
         <v>100</v>
       </c>
       <c r="O22" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P22" s="97">
+        <v>281</v>
+      </c>
+      <c r="P22" s="96">
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="Q22" s="81">
@@ -6763,22 +6792,22 @@
         <v>80</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H23" s="44" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L23" s="44">
         <v>1</v>
@@ -6787,13 +6816,13 @@
         <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="91">
+      <c r="N23" s="90">
         <v>10</v>
       </c>
       <c r="O23" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P23" s="97">
+        <v>281</v>
+      </c>
+      <c r="P23" s="96">
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="Q23" s="81">
@@ -6819,22 +6848,22 @@
         <v>81</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -6847,9 +6876,9 @@
         <v>10</v>
       </c>
       <c r="O24" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P24" s="96">
+        <v>281</v>
+      </c>
+      <c r="P24" s="95">
         <v>2.63E-2</v>
       </c>
       <c r="Q24" s="81">
@@ -6869,28 +6898,28 @@
         <v>10</v>
       </c>
       <c r="D25" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="F25" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="H25" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="I25" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="J25" s="44" t="s">
-        <v>305</v>
-      </c>
       <c r="K25" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L25" s="44">
         <v>1</v>
@@ -6899,11 +6928,11 @@
         <f>L25*5</f>
         <v>5</v>
       </c>
-      <c r="N25" s="91">
+      <c r="N25" s="90">
         <v>20</v>
       </c>
       <c r="O25" s="53" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="P25" s="85">
         <v>3.8100000000000002E-2</v>
@@ -6931,22 +6960,22 @@
         <v>82</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L26" s="37">
         <v>2</v>
@@ -6959,9 +6988,9 @@
         <v>10</v>
       </c>
       <c r="O26" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P26" s="96">
+        <v>281</v>
+      </c>
+      <c r="P26" s="95">
         <v>3.2199999999999999E-2</v>
       </c>
       <c r="Q26" s="81">
@@ -6987,22 +7016,22 @@
         <v>83</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H27" s="44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L27" s="44">
         <v>1</v>
@@ -7011,13 +7040,13 @@
         <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N27" s="91">
+      <c r="N27" s="90">
         <v>20</v>
       </c>
       <c r="O27" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P27" s="97">
+        <v>281</v>
+      </c>
+      <c r="P27" s="96">
         <v>8.8999999999999999E-3</v>
       </c>
       <c r="Q27" s="81">
@@ -7034,25 +7063,25 @@
         <v>19</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D28" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="H28" s="37"/>
       <c r="I28" s="37"/>
       <c r="J28" s="37"/>
       <c r="K28" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -7065,7 +7094,7 @@
         <v>50</v>
       </c>
       <c r="O28" s="52"/>
-      <c r="P28" s="96"/>
+      <c r="P28" s="95"/>
       <c r="Q28" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -7083,28 +7112,28 @@
         <v>13</v>
       </c>
       <c r="D29" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="I29" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="J29" s="44" t="s">
         <v>309</v>
       </c>
-      <c r="E29" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="G29" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="H29" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="I29" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>313</v>
-      </c>
       <c r="K29" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L29" s="44">
         <v>3</v>
@@ -7113,13 +7142,13 @@
         <f>L29*5</f>
         <v>15</v>
       </c>
-      <c r="N29" s="91">
+      <c r="N29" s="90">
         <v>20</v>
       </c>
       <c r="O29" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P29" s="97">
+        <v>281</v>
+      </c>
+      <c r="P29" s="96">
         <v>2.52E-2</v>
       </c>
       <c r="Q29" s="81">
@@ -7145,22 +7174,22 @@
         <v>84</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -7173,9 +7202,9 @@
         <v>6</v>
       </c>
       <c r="O30" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P30" s="96">
+        <v>281</v>
+      </c>
+      <c r="P30" s="95">
         <v>1.4796</v>
       </c>
       <c r="Q30" s="81">
@@ -7192,7 +7221,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D31" s="44" t="s">
         <v>39</v>
@@ -7201,22 +7230,22 @@
         <v>85</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H31" s="44" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I31" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J31" s="44" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L31" s="44">
         <v>1</v>
@@ -7225,13 +7254,13 @@
         <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="91">
+      <c r="N31" s="90">
         <v>6</v>
       </c>
       <c r="O31" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P31" s="97">
+        <v>281</v>
+      </c>
+      <c r="P31" s="96">
         <v>0.9546</v>
       </c>
       <c r="Q31" s="81">
@@ -7248,31 +7277,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>318</v>
-      </c>
       <c r="K32" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -7285,9 +7314,9 @@
         <v>6</v>
       </c>
       <c r="O32" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P32" s="96">
+        <v>281</v>
+      </c>
+      <c r="P32" s="95">
         <v>3.8199999999999998E-2</v>
       </c>
       <c r="Q32" s="81">
@@ -7313,22 +7342,22 @@
         <v>86</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H33" s="44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J33" s="44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L33" s="44">
         <v>1</v>
@@ -7337,13 +7366,13 @@
         <f>L33*5</f>
         <v>5</v>
       </c>
-      <c r="N33" s="91">
+      <c r="N33" s="90">
         <v>10</v>
       </c>
       <c r="O33" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P33" s="97">
+        <v>281</v>
+      </c>
+      <c r="P33" s="96">
         <v>0.29110000000000003</v>
       </c>
       <c r="Q33" s="81">
@@ -7369,22 +7398,22 @@
         <v>87</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G34" s="54" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H34" s="55" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I34" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J34" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K34" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L34" s="54">
         <v>13</v>
@@ -7393,17 +7422,17 @@
         <f t="shared" ref="M34" si="14">L34*5</f>
         <v>65</v>
       </c>
-      <c r="N34" s="92">
+      <c r="N34" s="91">
         <v>6</v>
       </c>
       <c r="O34" s="54" t="s">
-        <v>271</v>
-      </c>
-      <c r="P34" s="98" t="s">
-        <v>271</v>
+        <v>267</v>
+      </c>
+      <c r="P34" s="97" t="s">
+        <v>267</v>
       </c>
       <c r="Q34" s="82" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R34" s="44"/>
       <c r="S34" s="49"/>
@@ -7424,22 +7453,22 @@
         <v>88</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H35" s="44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J35" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L35" s="44">
         <v>1</v>
@@ -7448,13 +7477,13 @@
         <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="91">
+      <c r="N35" s="90">
         <v>10</v>
       </c>
       <c r="O35" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P35" s="97">
+        <v>281</v>
+      </c>
+      <c r="P35" s="96">
         <v>4.6899999999999997E-2</v>
       </c>
       <c r="Q35" s="81">
@@ -7480,22 +7509,22 @@
         <v>89</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -7508,9 +7537,9 @@
         <v>20</v>
       </c>
       <c r="O36" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P36" s="96">
+        <v>281</v>
+      </c>
+      <c r="P36" s="95">
         <v>3.49E-2</v>
       </c>
       <c r="Q36" s="81">
@@ -7530,28 +7559,28 @@
         <v>17</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>90</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H37" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="L37" s="44">
         <v>11</v>
@@ -7560,13 +7589,13 @@
         <f>L37*5</f>
         <v>55</v>
       </c>
-      <c r="N37" s="91">
+      <c r="N37" s="90">
         <v>100</v>
       </c>
       <c r="O37" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P37" s="97">
+        <v>281</v>
+      </c>
+      <c r="P37" s="96">
         <v>1E-3</v>
       </c>
       <c r="Q37" s="81">
@@ -7574,7 +7603,7 @@
         <v>0.1</v>
       </c>
       <c r="R37" s="73" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="S37" s="49"/>
     </row>
@@ -7594,22 +7623,22 @@
         <v>91</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H38" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I38" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J38" s="44" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="L38" s="44">
         <v>3</v>
@@ -7622,9 +7651,9 @@
         <v>100</v>
       </c>
       <c r="O38" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P38" s="97">
+        <v>281</v>
+      </c>
+      <c r="P38" s="96">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q38" s="81">
@@ -7647,25 +7676,25 @@
         <v>45</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H39" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I39" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J39" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K39" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L39" s="44">
         <v>1</v>
@@ -7674,13 +7703,13 @@
         <f>L39*5</f>
         <v>5</v>
       </c>
-      <c r="N39" s="91">
+      <c r="N39" s="90">
         <v>100</v>
       </c>
       <c r="O39" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P39" s="96">
+        <v>281</v>
+      </c>
+      <c r="P39" s="95">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q39" s="81">
@@ -7706,22 +7735,22 @@
         <v>92</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L40" s="37">
         <v>2</v>
@@ -7734,9 +7763,9 @@
         <v>100</v>
       </c>
       <c r="O40" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P40" s="96">
+        <v>281</v>
+      </c>
+      <c r="P40" s="95">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q40" s="81">
@@ -7759,25 +7788,25 @@
         <v>47</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F41" s="44" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G41" s="56" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H41" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I41" s="44" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J41" s="44" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K41" s="44" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="L41" s="44">
         <v>1</v>
@@ -7786,13 +7815,13 @@
         <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="91">
+      <c r="N41" s="90">
         <v>50</v>
       </c>
       <c r="O41" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P41" s="97">
+        <v>281</v>
+      </c>
+      <c r="P41" s="96">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q41" s="81">
@@ -7818,22 +7847,22 @@
         <v>93</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L42" s="37">
         <v>5</v>
@@ -7842,13 +7871,13 @@
         <f>L42*5</f>
         <v>25</v>
       </c>
-      <c r="N42" s="91">
+      <c r="N42" s="90">
         <v>100</v>
       </c>
       <c r="O42" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P42" s="96">
+        <v>281</v>
+      </c>
+      <c r="P42" s="95">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q42" s="81">
@@ -7874,22 +7903,22 @@
         <v>94</v>
       </c>
       <c r="F43" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G43" s="44" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H43" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I43" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J43" s="44" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="L43" s="44">
         <v>2</v>
@@ -7902,9 +7931,9 @@
         <v>100</v>
       </c>
       <c r="O43" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P43" s="97">
+        <v>281</v>
+      </c>
+      <c r="P43" s="96">
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="Q43" s="81">
@@ -7930,22 +7959,22 @@
         <v>95</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="L44" s="37">
         <v>3</v>
@@ -7954,13 +7983,13 @@
         <f>L44*5</f>
         <v>15</v>
       </c>
-      <c r="N44" s="91">
+      <c r="N44" s="90">
         <v>100</v>
       </c>
       <c r="O44" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P44" s="96">
+        <v>281</v>
+      </c>
+      <c r="P44" s="95">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q44" s="81">
@@ -7986,22 +8015,22 @@
         <v>96</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H45" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="L45" s="44">
         <v>2</v>
@@ -8014,9 +8043,9 @@
         <v>100</v>
       </c>
       <c r="O45" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P45" s="97">
+        <v>281</v>
+      </c>
+      <c r="P45" s="96">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q45" s="81">
@@ -8042,22 +8071,22 @@
         <v>97</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L46" s="37">
         <v>2</v>
@@ -8066,13 +8095,13 @@
         <f>L46*5</f>
         <v>10</v>
       </c>
-      <c r="N46" s="91">
+      <c r="N46" s="90">
         <v>100</v>
       </c>
       <c r="O46" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P46" s="96">
+        <v>281</v>
+      </c>
+      <c r="P46" s="95">
         <v>1.8E-3</v>
       </c>
       <c r="Q46" s="81">
@@ -8098,22 +8127,22 @@
         <v>98</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H47" s="44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I47" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J47" s="44" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L47" s="44">
         <v>1</v>
@@ -8126,9 +8155,9 @@
         <v>20</v>
       </c>
       <c r="O47" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P47" s="97">
+        <v>281</v>
+      </c>
+      <c r="P47" s="96">
         <v>2.75E-2</v>
       </c>
       <c r="Q47" s="81">
@@ -8154,22 +8183,22 @@
         <v>99</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K48" s="37" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="L48" s="37">
         <v>1</v>
@@ -8178,13 +8207,13 @@
         <f>L48*5</f>
         <v>5</v>
       </c>
-      <c r="N48" s="91">
+      <c r="N48" s="90">
         <v>50</v>
       </c>
       <c r="O48" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P48" s="96">
+        <v>281</v>
+      </c>
+      <c r="P48" s="95">
         <v>8.8000000000000005E-3</v>
       </c>
       <c r="Q48" s="81">
@@ -8201,31 +8230,31 @@
         <v>40</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E49" s="54" t="s">
         <v>100</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G49" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H49" s="55" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I49" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J49" s="56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K49" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L49" s="54">
         <v>6</v>
@@ -8238,18 +8267,18 @@
         <v>20</v>
       </c>
       <c r="O49" s="56" t="s">
-        <v>271</v>
-      </c>
-      <c r="P49" s="98" t="s">
-        <v>271</v>
+        <v>267</v>
+      </c>
+      <c r="P49" s="97" t="s">
+        <v>267</v>
       </c>
       <c r="Q49" s="81" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R49" s="44"/>
       <c r="S49" s="49"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="39">
         <f>ROW(B50) - ROW($B$9)</f>
@@ -8259,28 +8288,28 @@
         <v>18</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>101</v>
+        <v>345</v>
       </c>
       <c r="F50" s="44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="H50" s="44" t="s">
-        <v>193</v>
+        <v>268</v>
       </c>
       <c r="I50" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J50" s="44" t="s">
-        <v>234</v>
+        <v>343</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L50" s="44">
         <v>2</v>
@@ -8289,18 +8318,18 @@
         <f>L50*5</f>
         <v>10</v>
       </c>
-      <c r="N50" s="91">
-        <v>15</v>
+      <c r="N50" s="90">
+        <v>20</v>
       </c>
       <c r="O50" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P50" s="97">
-        <v>0.3135</v>
+        <v>281</v>
+      </c>
+      <c r="P50" s="45">
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="Q50" s="81">
         <f t="shared" si="2"/>
-        <v>4.7024999999999997</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="R50" s="37"/>
       <c r="S50" s="49"/>
@@ -8315,28 +8344,28 @@
         <v>18</v>
       </c>
       <c r="D51" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="G51" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="I51" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="E51" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>325</v>
-      </c>
       <c r="K51" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L51" s="37">
         <v>1</v>
@@ -8349,9 +8378,9 @@
         <v>6</v>
       </c>
       <c r="O51" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P51" s="99">
+        <v>281</v>
+      </c>
+      <c r="P51" s="98">
         <v>0.42799999999999999</v>
       </c>
       <c r="Q51" s="81">
@@ -8371,28 +8400,28 @@
         <v>18</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F52" s="44" t="s">
-        <v>272</v>
+        <v>346</v>
       </c>
       <c r="G52" s="44" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H52" s="44" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I52" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J52" s="44" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L52" s="44">
         <v>1</v>
@@ -8401,13 +8430,13 @@
         <f>L52*5</f>
         <v>5</v>
       </c>
-      <c r="N52" s="91">
+      <c r="N52" s="90">
         <v>10</v>
       </c>
       <c r="O52" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P52" s="97">
+        <v>281</v>
+      </c>
+      <c r="P52" s="96">
         <v>6.2100000000000002E-2</v>
       </c>
       <c r="Q52" s="81">
@@ -8430,25 +8459,25 @@
         <v>55</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K53" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L53" s="37">
         <v>1</v>
@@ -8461,9 +8490,9 @@
         <v>6</v>
       </c>
       <c r="O53" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P53" s="96">
+        <v>281</v>
+      </c>
+      <c r="P53" s="95">
         <v>0.16209999999999999</v>
       </c>
       <c r="Q53" s="81">
@@ -8486,25 +8515,25 @@
         <v>56</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F54" s="44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G54" s="44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H54" s="44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I54" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J54" s="44" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L54" s="44">
         <v>1</v>
@@ -8517,9 +8546,9 @@
         <v>10</v>
       </c>
       <c r="O54" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P54" s="97">
+        <v>281</v>
+      </c>
+      <c r="P54" s="96">
         <v>0.1341</v>
       </c>
       <c r="Q54" s="81">
@@ -8542,25 +8571,25 @@
         <v>57</v>
       </c>
       <c r="E55" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K55" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L55" s="37">
         <v>1</v>
@@ -8573,9 +8602,9 @@
         <v>10</v>
       </c>
       <c r="O55" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P55" s="96">
+        <v>281</v>
+      </c>
+      <c r="P55" s="95">
         <v>0.19539999999999999</v>
       </c>
       <c r="Q55" s="81">
@@ -8598,25 +8627,25 @@
         <v>58</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F56" s="44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H56" s="44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I56" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J56" s="44" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L56" s="44">
         <v>1</v>
@@ -8629,9 +8658,9 @@
         <v>6</v>
       </c>
       <c r="O56" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P56" s="97">
+        <v>281</v>
+      </c>
+      <c r="P56" s="96">
         <v>0.43909999999999999</v>
       </c>
       <c r="Q56" s="81">
@@ -8654,25 +8683,25 @@
         <v>59</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L57" s="37">
         <v>1</v>
@@ -8681,13 +8710,13 @@
         <f>L57*5</f>
         <v>5</v>
       </c>
-      <c r="N57" s="91">
+      <c r="N57" s="90">
         <v>10</v>
       </c>
       <c r="O57" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P57" s="96">
+        <v>281</v>
+      </c>
+      <c r="P57" s="95">
         <v>0.15479999999999999</v>
       </c>
       <c r="Q57" s="81">
@@ -8710,25 +8739,25 @@
         <v>60</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L58" s="37">
         <v>1</v>
@@ -8741,9 +8770,9 @@
         <v>6</v>
       </c>
       <c r="O58" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P58" s="96">
+        <v>281</v>
+      </c>
+      <c r="P58" s="95">
         <v>5.1212</v>
       </c>
       <c r="Q58" s="81">
@@ -8766,25 +8795,25 @@
         <v>61</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F59" s="44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H59" s="44" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I59" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L59" s="44">
         <v>1</v>
@@ -8793,13 +8822,13 @@
         <f>L59*5</f>
         <v>5</v>
       </c>
-      <c r="N59" s="91">
+      <c r="N59" s="90">
         <v>10</v>
       </c>
       <c r="O59" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P59" s="97">
+        <v>281</v>
+      </c>
+      <c r="P59" s="96">
         <v>0.15670000000000001</v>
       </c>
       <c r="Q59" s="81">
@@ -8822,25 +8851,25 @@
         <v>62</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L60" s="37">
         <v>1</v>
@@ -8853,9 +8882,9 @@
         <v>6</v>
       </c>
       <c r="O60" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P60" s="96">
+        <v>281</v>
+      </c>
+      <c r="P60" s="95">
         <v>0.96889999999999998</v>
       </c>
       <c r="Q60" s="81">
@@ -8878,25 +8907,25 @@
         <v>63</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F61" s="44" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G61" s="44" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H61" s="44" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I61" s="44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J61" s="44" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L61" s="44">
         <v>1</v>
@@ -8905,13 +8934,13 @@
         <f>L61*5</f>
         <v>5</v>
       </c>
-      <c r="N61" s="91">
+      <c r="N61" s="90">
         <v>6</v>
       </c>
       <c r="O61" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="P61" s="97">
+        <v>281</v>
+      </c>
+      <c r="P61" s="96">
         <v>0.28870000000000001</v>
       </c>
       <c r="Q61" s="81">
@@ -8934,25 +8963,25 @@
         <v>64</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K62" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -8961,13 +8990,13 @@
         <f>L62*5</f>
         <v>5</v>
       </c>
-      <c r="N62" s="91">
+      <c r="N62" s="90">
         <v>6</v>
       </c>
       <c r="O62" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="P62" s="96">
+        <v>281</v>
+      </c>
+      <c r="P62" s="95">
         <v>2.0651000000000002</v>
       </c>
       <c r="Q62" s="81">
@@ -8990,25 +9019,25 @@
         <v>65</v>
       </c>
       <c r="E63" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F63" s="49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G63" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H63" s="49" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I63" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J63" s="49" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K63" s="61" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L63" s="49">
         <v>1</v>
@@ -9017,13 +9046,13 @@
         <f t="shared" ref="M63:M67" si="28">L63*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="93">
+      <c r="N63" s="92">
         <v>6</v>
       </c>
       <c r="O63" s="62" t="s">
-        <v>285</v>
-      </c>
-      <c r="P63" s="100">
+        <v>281</v>
+      </c>
+      <c r="P63" s="99">
         <v>1.2919</v>
       </c>
       <c r="Q63" s="86">
@@ -9040,31 +9069,31 @@
         <v>55</v>
       </c>
       <c r="C64" s="60" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K64" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L64" s="49">
         <v>1</v>
@@ -9073,17 +9102,17 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N64" s="94" t="s">
-        <v>271</v>
+      <c r="N64" s="93" t="s">
+        <v>267</v>
       </c>
       <c r="O64" s="53" t="s">
-        <v>271</v>
-      </c>
-      <c r="P64" s="101" t="s">
-        <v>271</v>
+        <v>267</v>
+      </c>
+      <c r="P64" s="100" t="s">
+        <v>267</v>
       </c>
       <c r="Q64" s="87" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R64" s="83"/>
       <c r="S64" s="83"/>
@@ -9095,31 +9124,31 @@
         <v>56</v>
       </c>
       <c r="C65" s="60" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K65" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L65" s="49">
         <v>1</v>
@@ -9128,17 +9157,17 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N65" s="91" t="s">
-        <v>271</v>
+      <c r="N65" s="90" t="s">
+        <v>267</v>
       </c>
       <c r="O65" s="52" t="s">
-        <v>271</v>
-      </c>
-      <c r="P65" s="96" t="s">
-        <v>271</v>
+        <v>267</v>
+      </c>
+      <c r="P65" s="95" t="s">
+        <v>267</v>
       </c>
       <c r="Q65" s="81" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R65" s="37"/>
       <c r="S65" s="49"/>
@@ -9150,31 +9179,31 @@
         <v>57</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K66" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L66" s="49">
         <v>1</v>
@@ -9183,17 +9212,17 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N66" s="91" t="s">
-        <v>271</v>
+      <c r="N66" s="90" t="s">
+        <v>267</v>
       </c>
       <c r="O66" s="52" t="s">
-        <v>271</v>
-      </c>
-      <c r="P66" s="96" t="s">
-        <v>271</v>
+        <v>267</v>
+      </c>
+      <c r="P66" s="95" t="s">
+        <v>267</v>
       </c>
       <c r="Q66" s="81" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R66" s="37"/>
       <c r="S66" s="49"/>
@@ -9205,31 +9234,31 @@
         <v>58</v>
       </c>
       <c r="C67" s="60" t="s">
+        <v>331</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="F67" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="G67" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="H67" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="I67" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="J67" s="49" t="s">
         <v>335</v>
       </c>
-      <c r="D67" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="E67" s="49" t="s">
-        <v>336</v>
-      </c>
-      <c r="F67" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="G67" s="49" t="s">
-        <v>337</v>
-      </c>
-      <c r="H67" s="49" t="s">
-        <v>338</v>
-      </c>
-      <c r="I67" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="J67" s="49" t="s">
-        <v>339</v>
-      </c>
       <c r="K67" s="49" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L67" s="49">
         <v>1</v>
@@ -9238,13 +9267,13 @@
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N67" s="91">
+      <c r="N67" s="90">
         <v>6</v>
       </c>
-      <c r="O67" s="102" t="s">
-        <v>285</v>
-      </c>
-      <c r="P67" s="96">
+      <c r="O67" s="101" t="s">
+        <v>281</v>
+      </c>
+      <c r="P67" s="95">
         <v>0.1202</v>
       </c>
       <c r="Q67" s="81">
@@ -9268,17 +9297,17 @@
       <c r="K68" s="69"/>
       <c r="L68" s="69"/>
       <c r="M68" s="69"/>
-      <c r="N68" s="111" t="s">
+      <c r="N68" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="O68" s="112"/>
-      <c r="P68" s="112"/>
+      <c r="O68" s="107"/>
+      <c r="P68" s="107"/>
       <c r="Q68" s="41">
         <f>SUM(Q10:Q67)</f>
-        <v>128.43350000000001</v>
-      </c>
-      <c r="R68" s="115"/>
-      <c r="S68" s="116"/>
+        <v>124.12300000000002</v>
+      </c>
+      <c r="R68" s="110"/>
+      <c r="S68" s="111"/>
     </row>
     <row r="69" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -9294,17 +9323,17 @@
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
       <c r="M69" s="10"/>
-      <c r="N69" s="111" t="s">
+      <c r="N69" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="O69" s="112"/>
-      <c r="P69" s="112"/>
+      <c r="O69" s="107"/>
+      <c r="P69" s="107"/>
       <c r="Q69" s="42">
         <f>Q68/5</f>
-        <v>25.686700000000002</v>
-      </c>
-      <c r="R69" s="117"/>
-      <c r="S69" s="118"/>
+        <v>24.824600000000004</v>
+      </c>
+      <c r="R69" s="112"/>
+      <c r="S69" s="113"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="P70" s="74"/>
@@ -9348,28 +9377,28 @@
     <hyperlink ref="O46" r:id="rId28"/>
     <hyperlink ref="O47" r:id="rId29"/>
     <hyperlink ref="O48" r:id="rId30"/>
-    <hyperlink ref="O50" r:id="rId31"/>
-    <hyperlink ref="O52" r:id="rId32"/>
-    <hyperlink ref="O53" r:id="rId33"/>
-    <hyperlink ref="O55" r:id="rId34"/>
-    <hyperlink ref="O56" r:id="rId35"/>
-    <hyperlink ref="O57" r:id="rId36"/>
-    <hyperlink ref="O58" r:id="rId37"/>
-    <hyperlink ref="O59" r:id="rId38"/>
-    <hyperlink ref="O60" r:id="rId39"/>
-    <hyperlink ref="O61" r:id="rId40"/>
-    <hyperlink ref="O62" r:id="rId41"/>
-    <hyperlink ref="O63" r:id="rId42"/>
-    <hyperlink ref="O18" r:id="rId43"/>
-    <hyperlink ref="O54" r:id="rId44"/>
-    <hyperlink ref="O25" r:id="rId45"/>
-    <hyperlink ref="O29" r:id="rId46"/>
-    <hyperlink ref="O32" r:id="rId47"/>
-    <hyperlink ref="O39" r:id="rId48"/>
-    <hyperlink ref="O51" r:id="rId49"/>
-    <hyperlink ref="O41" r:id="rId50"/>
-    <hyperlink ref="O67" r:id="rId51"/>
-    <hyperlink ref="O15" r:id="rId52"/>
+    <hyperlink ref="O52" r:id="rId31"/>
+    <hyperlink ref="O53" r:id="rId32"/>
+    <hyperlink ref="O55" r:id="rId33"/>
+    <hyperlink ref="O56" r:id="rId34"/>
+    <hyperlink ref="O57" r:id="rId35"/>
+    <hyperlink ref="O58" r:id="rId36"/>
+    <hyperlink ref="O59" r:id="rId37"/>
+    <hyperlink ref="O60" r:id="rId38"/>
+    <hyperlink ref="O61" r:id="rId39"/>
+    <hyperlink ref="O62" r:id="rId40"/>
+    <hyperlink ref="O63" r:id="rId41"/>
+    <hyperlink ref="O18" r:id="rId42"/>
+    <hyperlink ref="O54" r:id="rId43"/>
+    <hyperlink ref="O25" r:id="rId44"/>
+    <hyperlink ref="O29" r:id="rId45"/>
+    <hyperlink ref="O32" r:id="rId46"/>
+    <hyperlink ref="O39" r:id="rId47"/>
+    <hyperlink ref="O51" r:id="rId48"/>
+    <hyperlink ref="O41" r:id="rId49"/>
+    <hyperlink ref="O67" r:id="rId50"/>
+    <hyperlink ref="O15" r:id="rId51"/>
+    <hyperlink ref="O50" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>

--- a/BOM/eSpark-BOM.xlsx
+++ b/BOM/eSpark-BOM.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 Board" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="348">
   <si>
     <t>Component list</t>
   </si>
@@ -892,9 +892,6 @@
     <t>RC1206FR-7W5R6L</t>
   </si>
   <si>
-    <t>C137211</t>
-  </si>
-  <si>
     <t>General Purpose Chip Resistor Thick Film 1206 5.6Ohm 1% Paper T/R</t>
   </si>
   <si>
@@ -1061,6 +1058,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Solder Bridge 0402</t>
+  </si>
+  <si>
+    <t>Solder Bridge_0402</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1075,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1256,6 +1259,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1283,7 +1295,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1540,21 +1552,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -1659,7 +1656,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1767,9 +1764,6 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1889,63 +1883,83 @@
     <xf numFmtId="166" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1984,50 +1998,51 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2456,14 +2471,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="103"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="110"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2473,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="45" t="s">
         <v>279</v>
       </c>
       <c r="G2" s="12"/>
@@ -2497,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="46" t="s">
         <v>280</v>
       </c>
       <c r="G3" s="13"/>
@@ -2511,7 +2526,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
-      <c r="R3" s="104"/>
+      <c r="R3" s="111"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2521,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="46" t="s">
         <v>280</v>
       </c>
       <c r="G4" s="14"/>
@@ -2535,7 +2550,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="105"/>
+      <c r="R4" s="112"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2545,7 +2560,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="47" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="15"/>
@@ -2559,7 +2574,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
-      <c r="R5" s="105"/>
+      <c r="R5" s="112"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2579,7 +2594,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="105"/>
+      <c r="R6" s="112"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2599,7 +2614,7 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="105"/>
+      <c r="R7" s="112"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2619,7 +2634,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
-      <c r="R8" s="105"/>
+      <c r="R8" s="112"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2657,31 +2672,31 @@
         <v>265</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N9" s="30" t="s">
         <v>274</v>
       </c>
       <c r="O9" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="P9" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="P9" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q9" s="89" t="s">
+      <c r="Q9" s="86" t="s">
         <v>277</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
+    <row r="10" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="69"/>
       <c r="B10" s="39">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
@@ -2714,7 +2729,7 @@
       <c r="M10" s="37">
         <v>50</v>
       </c>
-      <c r="N10" s="52" t="s">
+      <c r="N10" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O10" s="38">
@@ -2724,68 +2739,68 @@
         <f>O10*M10</f>
         <v>0.94500000000000006</v>
       </c>
-      <c r="Q10" s="90"/>
-      <c r="R10" s="71"/>
-    </row>
-    <row r="11" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="70"/>
+      <c r="Q10" s="87"/>
+      <c r="R10" s="70"/>
+    </row>
+    <row r="11" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="69"/>
       <c r="B11" s="40">
         <f t="shared" ref="B11:B67" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G11" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="I11" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J11" s="44" t="s">
+      <c r="I11" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J11" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="K11" s="44" t="s">
+      <c r="K11" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="L11" s="44">
+      <c r="L11" s="43">
         <v>2</v>
       </c>
-      <c r="M11" s="44">
+      <c r="M11" s="43">
         <v>3</v>
       </c>
-      <c r="N11" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O11" s="45">
+      <c r="N11" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O11" s="44">
         <v>1.4064000000000001</v>
       </c>
-      <c r="P11" s="45">
+      <c r="P11" s="44">
         <f t="shared" ref="P11" si="1">O11*M11</f>
         <v>4.2192000000000007</v>
       </c>
-      <c r="Q11" s="84"/>
-      <c r="R11" s="44"/>
-    </row>
-    <row r="12" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="43"/>
+    </row>
+    <row r="12" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="69"/>
       <c r="B12" s="39">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
@@ -2818,7 +2833,7 @@
       <c r="M12" s="37">
         <v>100</v>
       </c>
-      <c r="N12" s="52" t="s">
+      <c r="N12" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O12" s="38">
@@ -2828,72 +2843,72 @@
         <f>O12*M12</f>
         <v>0.5</v>
       </c>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="49"/>
-    </row>
-    <row r="13" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="48"/>
+    </row>
+    <row r="13" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="69"/>
       <c r="B13" s="40">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I13" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J13" s="44" t="s">
+      <c r="I13" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J13" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="K13" s="44" t="s">
+      <c r="K13" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="L13" s="44">
+      <c r="L13" s="43">
         <v>1</v>
       </c>
-      <c r="M13" s="44">
+      <c r="M13" s="43">
         <v>100</v>
       </c>
-      <c r="N13" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O13" s="45">
+      <c r="N13" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O13" s="44">
         <v>2.8E-3</v>
       </c>
-      <c r="P13" s="45">
+      <c r="P13" s="44">
         <f t="shared" ref="P13" si="2">O13*M13</f>
         <v>0.27999999999999997</v>
       </c>
-      <c r="Q13" s="84"/>
-      <c r="R13" s="49"/>
-    </row>
-    <row r="14" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="48"/>
+    </row>
+    <row r="14" spans="1:18" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A14" s="69"/>
       <c r="B14" s="39">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>71</v>
@@ -2922,7 +2937,7 @@
       <c r="M14" s="37">
         <v>100</v>
       </c>
-      <c r="N14" s="52" t="s">
+      <c r="N14" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O14" s="38">
@@ -2932,68 +2947,68 @@
         <f>O14*M14</f>
         <v>0.18</v>
       </c>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="49"/>
-    </row>
-    <row r="15" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="70"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="48"/>
+    </row>
+    <row r="15" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="69"/>
       <c r="B15" s="40">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="56" t="s">
+      <c r="G15" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I15" s="44" t="s">
+      <c r="I15" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="J15" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="J15" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="K15" s="44" t="s">
+      <c r="K15" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="43">
         <v>2</v>
       </c>
-      <c r="M15" s="44">
+      <c r="M15" s="43">
         <v>20</v>
       </c>
-      <c r="N15" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O15" s="45">
+      <c r="N15" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O15" s="44">
         <v>1.77E-2</v>
       </c>
-      <c r="P15" s="45">
+      <c r="P15" s="44">
         <f t="shared" ref="P15" si="3">O15*M15</f>
         <v>0.35399999999999998</v>
       </c>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="49"/>
-    </row>
-    <row r="16" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="70"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="48"/>
+    </row>
+    <row r="16" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="69"/>
       <c r="B16" s="39">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
@@ -3026,78 +3041,78 @@
       <c r="M16" s="37">
         <v>5</v>
       </c>
-      <c r="N16" s="52" t="s">
+      <c r="N16" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O16" s="38">
         <v>0.42320000000000002</v>
       </c>
-      <c r="P16" s="81">
+      <c r="P16" s="80">
         <f>O16*M16</f>
         <v>2.1160000000000001</v>
       </c>
-      <c r="Q16" s="90"/>
-      <c r="R16" s="49"/>
-    </row>
-    <row r="17" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="70"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="48"/>
+    </row>
+    <row r="17" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="69"/>
       <c r="B17" s="40">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="F17" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J17" s="44" t="s">
+      <c r="I17" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J17" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K17" s="43" t="s">
         <v>249</v>
       </c>
-      <c r="L17" s="44">
+      <c r="L17" s="43">
         <v>6</v>
       </c>
-      <c r="M17" s="44">
+      <c r="M17" s="43">
         <v>20</v>
       </c>
-      <c r="N17" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O17" s="45">
+      <c r="N17" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O17" s="44">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="P17" s="45">
+      <c r="P17" s="44">
         <f t="shared" ref="P17" si="4">O17*M17</f>
         <v>0.47600000000000003</v>
       </c>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="49"/>
-    </row>
-    <row r="18" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="70"/>
+      <c r="Q17" s="82"/>
+      <c r="R17" s="48"/>
+    </row>
+    <row r="18" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="69"/>
       <c r="B18" s="39">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="37" t="s">
@@ -3109,7 +3124,7 @@
       <c r="F18" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="54" t="s">
+      <c r="G18" s="53" t="s">
         <v>148</v>
       </c>
       <c r="H18" s="37" t="s">
@@ -3130,7 +3145,7 @@
       <c r="M18" s="37">
         <v>50</v>
       </c>
-      <c r="N18" s="52" t="s">
+      <c r="N18" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O18" s="38">
@@ -3140,120 +3155,120 @@
         <f>O18*M18</f>
         <v>0.27499999999999997</v>
       </c>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="49"/>
-    </row>
-    <row r="19" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="70"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="48"/>
+    </row>
+    <row r="19" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="69"/>
       <c r="B19" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="G19" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I19" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J19" s="44" t="s">
+      <c r="I19" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J19" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="K19" s="44" t="s">
+      <c r="K19" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="L19" s="44">
+      <c r="L19" s="43">
         <v>1</v>
       </c>
-      <c r="M19" s="44">
+      <c r="M19" s="43">
         <v>20</v>
       </c>
-      <c r="N19" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O19" s="45">
+      <c r="N19" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O19" s="44">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="P19" s="45">
+      <c r="P19" s="44">
         <f t="shared" ref="P19:P20" si="5">O19*M19</f>
         <v>0.40399999999999997</v>
       </c>
-      <c r="Q19" s="84"/>
-      <c r="R19" s="49"/>
-    </row>
-    <row r="20" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="48"/>
+    </row>
+    <row r="20" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="69"/>
       <c r="B20" s="40">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I20" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J20" s="44" t="s">
+      <c r="I20" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J20" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="K20" s="44" t="s">
+      <c r="K20" s="43" t="s">
         <v>251</v>
       </c>
-      <c r="L20" s="44">
+      <c r="L20" s="43">
         <v>2</v>
       </c>
-      <c r="M20" s="44">
+      <c r="M20" s="43">
         <v>100</v>
       </c>
-      <c r="N20" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O20" s="45">
+      <c r="N20" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O20" s="44">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="P20" s="45">
+      <c r="P20" s="44">
         <f t="shared" si="5"/>
         <v>0.37</v>
       </c>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="49"/>
-    </row>
-    <row r="21" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="70"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="48"/>
+    </row>
+    <row r="21" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="69"/>
       <c r="B21" s="39">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="37" t="s">
@@ -3286,7 +3301,7 @@
       <c r="M21" s="37">
         <v>100</v>
       </c>
-      <c r="N21" s="52" t="s">
+      <c r="N21" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O21" s="38">
@@ -3296,120 +3311,120 @@
         <f>O21*M21</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="Q21" s="90"/>
-      <c r="R21" s="49"/>
-    </row>
-    <row r="22" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="70"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="48"/>
+    </row>
+    <row r="22" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="69"/>
       <c r="B22" s="40">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="44" t="s">
+      <c r="G22" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I22" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J22" s="44" t="s">
+      <c r="I22" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J22" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="43" t="s">
         <v>253</v>
       </c>
-      <c r="L22" s="44">
+      <c r="L22" s="43">
         <v>1</v>
       </c>
-      <c r="M22" s="44">
+      <c r="M22" s="43">
         <v>100</v>
       </c>
-      <c r="N22" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O22" s="45">
+      <c r="N22" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O22" s="44">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="P22" s="45">
+      <c r="P22" s="44">
         <f t="shared" ref="P22" si="6">O22*M22</f>
         <v>0.32</v>
       </c>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="49"/>
-    </row>
-    <row r="23" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="70"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="48"/>
+    </row>
+    <row r="23" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="69"/>
       <c r="B23" s="40">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="44" t="s">
+      <c r="E23" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="44" t="s">
+      <c r="F23" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="I23" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J23" s="44" t="s">
+      <c r="I23" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J23" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="K23" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L23" s="44">
+      <c r="K23" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L23" s="43">
         <v>1</v>
       </c>
-      <c r="M23" s="44">
+      <c r="M23" s="43">
         <v>5</v>
       </c>
-      <c r="N23" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O23" s="45">
+      <c r="N23" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O23" s="44">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="P23" s="45">
+      <c r="P23" s="44">
         <f t="shared" ref="P23" si="7">O23*M23</f>
         <v>0.43200000000000005</v>
       </c>
-      <c r="Q23" s="84"/>
-      <c r="R23" s="49"/>
-    </row>
-    <row r="24" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A24" s="70"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="48"/>
+    </row>
+    <row r="24" spans="1:18" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A24" s="69"/>
       <c r="B24" s="39">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="49" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="37" t="s">
@@ -3442,7 +3457,7 @@
       <c r="M24" s="37">
         <v>20</v>
       </c>
-      <c r="N24" s="52" t="s">
+      <c r="N24" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O24" s="38">
@@ -3452,68 +3467,68 @@
         <f>O24*M24</f>
         <v>0.52600000000000002</v>
       </c>
-      <c r="Q24" s="90"/>
-      <c r="R24" s="49"/>
-    </row>
-    <row r="25" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A25" s="70"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="48"/>
+    </row>
+    <row r="25" spans="1:18" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A25" s="69"/>
       <c r="B25" s="40">
         <f t="shared" ref="B25" si="8">ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E25" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="F25" s="43" t="s">
         <v>298</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="G25" s="43" t="s">
         <v>299</v>
       </c>
-      <c r="G25" s="44" t="s">
+      <c r="H25" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="H25" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="I25" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J25" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="K25" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L25" s="44">
+      <c r="K25" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L25" s="43">
         <v>1</v>
       </c>
-      <c r="M25" s="44">
+      <c r="M25" s="43">
         <v>20</v>
       </c>
-      <c r="N25" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O25" s="44">
+      <c r="N25" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O25" s="43">
         <v>3.8100000000000002E-2</v>
       </c>
-      <c r="P25" s="45">
+      <c r="P25" s="44">
         <f>O25*M25</f>
         <v>0.76200000000000001</v>
       </c>
-      <c r="Q25" s="115"/>
-      <c r="R25" s="44"/>
-    </row>
-    <row r="26" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A26" s="70"/>
+      <c r="Q25" s="94"/>
+      <c r="R25" s="43"/>
+    </row>
+    <row r="26" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A26" s="69"/>
       <c r="B26" s="39">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="49" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="37" t="s">
@@ -3537,7 +3552,7 @@
       <c r="J26" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="K26" s="44" t="s">
+      <c r="K26" s="43" t="s">
         <v>267</v>
       </c>
       <c r="L26" s="37">
@@ -3546,7 +3561,7 @@
       <c r="M26" s="37">
         <v>20</v>
       </c>
-      <c r="N26" s="52" t="s">
+      <c r="N26" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O26" s="38">
@@ -3556,171 +3571,171 @@
         <f>O26*M26</f>
         <v>0.64400000000000002</v>
       </c>
-      <c r="Q26" s="90"/>
-      <c r="R26" s="49"/>
-    </row>
-    <row r="27" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="70"/>
+      <c r="Q26" s="87"/>
+      <c r="R26" s="48"/>
+    </row>
+    <row r="27" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="69"/>
       <c r="B27" s="40">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="E27" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="44" t="s">
+      <c r="F27" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="44" t="s">
+      <c r="G27" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="I27" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J27" s="44" t="s">
+      <c r="I27" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J27" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="K27" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L27" s="44">
+      <c r="K27" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L27" s="43">
         <v>1</v>
       </c>
-      <c r="M27" s="44">
+      <c r="M27" s="43">
         <v>50</v>
       </c>
-      <c r="N27" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O27" s="45">
+      <c r="N27" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O27" s="44">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="P27" s="45">
+      <c r="P27" s="44">
         <f t="shared" ref="P27" si="9">O27*M27</f>
         <v>0.44500000000000001</v>
       </c>
-      <c r="Q27" s="84"/>
-      <c r="R27" s="49"/>
-    </row>
-    <row r="28" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="70"/>
+      <c r="Q27" s="82"/>
+      <c r="R27" s="48"/>
+    </row>
+    <row r="28" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="69"/>
       <c r="B28" s="39">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="53" t="s">
         <v>302</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="37" t="s">
+      <c r="F28" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="G28" s="53" t="s">
         <v>303</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="L28" s="37">
+      <c r="H28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="J28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="K28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="L28" s="53">
         <v>1</v>
       </c>
-      <c r="M28" s="37">
+      <c r="M28" s="53">
         <v>5</v>
       </c>
-      <c r="N28" s="52" t="s">
-        <v>267</v>
-      </c>
-      <c r="O28" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="P28" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q28" s="90"/>
-      <c r="R28" s="49"/>
-    </row>
-    <row r="29" spans="1:18" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A29" s="70"/>
+      <c r="N28" s="121" t="s">
+        <v>267</v>
+      </c>
+      <c r="O28" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="P28" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="57"/>
+    </row>
+    <row r="29" spans="1:18" s="71" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A29" s="69"/>
       <c r="B29" s="40">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="44" t="s">
+      <c r="D29" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="E29" s="43" t="s">
         <v>305</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="F29" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="G29" s="43" t="s">
         <v>306</v>
       </c>
-      <c r="F29" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="G29" s="44" t="s">
+      <c r="H29" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="I29" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J29" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="I29" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="K29" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L29" s="44">
+      <c r="K29" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L29" s="43">
         <v>3</v>
       </c>
-      <c r="M29" s="44">
+      <c r="M29" s="43">
         <v>20</v>
       </c>
-      <c r="N29" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O29" s="45">
+      <c r="N29" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O29" s="44">
         <v>2.52E-2</v>
       </c>
-      <c r="P29" s="45">
+      <c r="P29" s="44">
         <f t="shared" ref="P29" si="10">O29*M29</f>
         <v>0.504</v>
       </c>
-      <c r="Q29" s="84"/>
-      <c r="R29" s="49"/>
-    </row>
-    <row r="30" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A30" s="70"/>
+      <c r="Q29" s="82"/>
+      <c r="R29" s="48"/>
+    </row>
+    <row r="30" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A30" s="69"/>
       <c r="B30" s="39">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="49" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="37" t="s">
@@ -3744,7 +3759,7 @@
       <c r="J30" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="K30" s="44" t="s">
+      <c r="K30" s="43" t="s">
         <v>267</v>
       </c>
       <c r="L30" s="37">
@@ -3753,7 +3768,7 @@
       <c r="M30" s="37">
         <v>2</v>
       </c>
-      <c r="N30" s="52" t="s">
+      <c r="N30" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O30" s="38" t="s">
@@ -3762,92 +3777,92 @@
       <c r="P30" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="Q30" s="116" t="s">
-        <v>341</v>
-      </c>
-      <c r="R30" s="49"/>
-    </row>
-    <row r="31" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="70"/>
+      <c r="Q30" s="95" t="s">
+        <v>340</v>
+      </c>
+      <c r="R30" s="48"/>
+    </row>
+    <row r="31" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="69"/>
       <c r="B31" s="40">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="D31" s="44" t="s">
+      <c r="C31" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="D31" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="44" t="s">
+      <c r="F31" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="G31" s="44" t="s">
+      <c r="G31" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H31" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="I31" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J31" s="44" t="s">
+      <c r="I31" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J31" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="K31" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L31" s="44">
+      <c r="K31" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L31" s="43">
         <v>1</v>
       </c>
-      <c r="M31" s="44">
+      <c r="M31" s="43">
         <v>2</v>
       </c>
-      <c r="N31" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O31" s="45">
+      <c r="N31" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O31" s="44">
         <v>0.9546</v>
       </c>
-      <c r="P31" s="45">
+      <c r="P31" s="44">
         <f t="shared" ref="P31" si="11">O31*M31</f>
         <v>1.9092</v>
       </c>
-      <c r="Q31" s="84"/>
-      <c r="R31" s="49"/>
-    </row>
-    <row r="32" spans="1:18" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A32" s="70"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="48"/>
+    </row>
+    <row r="32" spans="1:18" s="71" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A32" s="69"/>
       <c r="B32" s="39">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="49" t="s">
+        <v>309</v>
+      </c>
+      <c r="D32" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="E32" s="37" t="s">
         <v>311</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>312</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>268</v>
       </c>
       <c r="G32" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>313</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>314</v>
       </c>
       <c r="K32" s="37" t="s">
         <v>267</v>
@@ -3858,7 +3873,7 @@
       <c r="M32" s="37">
         <v>10</v>
       </c>
-      <c r="N32" s="52" t="s">
+      <c r="N32" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O32" s="38">
@@ -3868,171 +3883,171 @@
         <f>O32*M32</f>
         <v>0.38200000000000001</v>
       </c>
-      <c r="Q32" s="90"/>
-      <c r="R32" s="49"/>
-    </row>
-    <row r="33" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="70"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="48"/>
+    </row>
+    <row r="33" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="69"/>
       <c r="B33" s="40">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D33" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="43" t="s">
         <v>86</v>
       </c>
       <c r="F33" s="37" t="s">
         <v>268</v>
       </c>
-      <c r="G33" s="44" t="s">
+      <c r="G33" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="I33" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J33" s="44" t="s">
+      <c r="I33" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J33" s="43" t="s">
         <v>219</v>
       </c>
-      <c r="K33" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L33" s="44">
+      <c r="K33" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L33" s="43">
         <v>1</v>
       </c>
-      <c r="M33" s="44">
+      <c r="M33" s="43">
         <v>2</v>
       </c>
-      <c r="N33" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O33" s="45">
+      <c r="N33" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O33" s="44">
         <v>0.29110000000000003</v>
       </c>
-      <c r="P33" s="45">
+      <c r="P33" s="44">
         <f t="shared" ref="P33" si="12">O33*M33</f>
         <v>0.58220000000000005</v>
       </c>
-      <c r="Q33" s="84"/>
-      <c r="R33" s="49"/>
-    </row>
-    <row r="34" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="70"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="48"/>
+    </row>
+    <row r="34" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="69"/>
       <c r="B34" s="39">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="54" t="s">
+      <c r="E34" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="54" t="s">
+      <c r="F34" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="G34" s="54" t="s">
+      <c r="G34" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="H34" s="55" t="s">
-        <v>267</v>
-      </c>
-      <c r="I34" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="J34" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="K34" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="L34" s="54">
+      <c r="H34" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="I34" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="J34" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="K34" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="L34" s="53">
         <v>13</v>
       </c>
-      <c r="M34" s="54" t="s">
-        <v>267</v>
-      </c>
-      <c r="N34" s="54" t="s">
-        <v>267</v>
-      </c>
-      <c r="O34" s="57" t="s">
-        <v>267</v>
-      </c>
-      <c r="P34" s="57" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q34" s="117"/>
-      <c r="R34" s="58"/>
-    </row>
-    <row r="35" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A35" s="70"/>
+      <c r="M34" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="N34" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="O34" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="P34" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q34" s="96"/>
+      <c r="R34" s="57"/>
+    </row>
+    <row r="35" spans="1:18" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="69"/>
       <c r="B35" s="40">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="44" t="s">
+      <c r="F35" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="G35" s="44" t="s">
+      <c r="G35" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="H35" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="I35" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J35" s="44" t="s">
+      <c r="I35" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J35" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="K35" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L35" s="44">
+      <c r="K35" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L35" s="43">
         <v>1</v>
       </c>
-      <c r="M35" s="44">
+      <c r="M35" s="43">
         <v>10</v>
       </c>
-      <c r="N35" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O35" s="45">
+      <c r="N35" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O35" s="44">
         <v>4.6899999999999997E-2</v>
       </c>
-      <c r="P35" s="45">
+      <c r="P35" s="44">
         <f t="shared" ref="P35" si="13">O35*M35</f>
         <v>0.46899999999999997</v>
       </c>
-      <c r="Q35" s="84"/>
-      <c r="R35" s="49"/>
-    </row>
-    <row r="36" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="70"/>
+      <c r="Q35" s="82"/>
+      <c r="R35" s="48"/>
+    </row>
+    <row r="36" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="69"/>
       <c r="B36" s="39">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="50" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -4056,7 +4071,7 @@
       <c r="J36" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="K36" s="44" t="s">
+      <c r="K36" s="43" t="s">
         <v>267</v>
       </c>
       <c r="L36" s="37">
@@ -4065,7 +4080,7 @@
       <c r="M36" s="37">
         <v>20</v>
       </c>
-      <c r="N36" s="52" t="s">
+      <c r="N36" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O36" s="38">
@@ -4075,155 +4090,155 @@
         <f>O36*M36</f>
         <v>0.69799999999999995</v>
       </c>
-      <c r="Q36" s="90"/>
-      <c r="R36" s="49"/>
-    </row>
-    <row r="37" spans="1:18" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A37" s="70"/>
+      <c r="Q36" s="87"/>
+      <c r="R36" s="48"/>
+    </row>
+    <row r="37" spans="1:18" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="69"/>
       <c r="B37" s="40">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="44" t="s">
-        <v>327</v>
-      </c>
-      <c r="E37" s="44" t="s">
+      <c r="D37" s="43" t="s">
+        <v>326</v>
+      </c>
+      <c r="E37" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F37" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G37" s="44" t="s">
+      <c r="G37" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I37" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J37" s="44" t="s">
+      <c r="I37" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J37" s="43" t="s">
         <v>222</v>
       </c>
-      <c r="K37" s="44" t="s">
+      <c r="K37" s="43" t="s">
         <v>254</v>
       </c>
-      <c r="L37" s="44">
+      <c r="L37" s="43">
         <v>11</v>
       </c>
-      <c r="M37" s="44">
+      <c r="M37" s="43">
         <v>100</v>
       </c>
-      <c r="N37" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O37" s="45">
+      <c r="N37" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O37" s="44">
         <v>1E-3</v>
       </c>
-      <c r="P37" s="45">
+      <c r="P37" s="44">
         <f t="shared" ref="P37" si="14">O37*M37</f>
         <v>0.1</v>
       </c>
-      <c r="Q37" s="114" t="s">
-        <v>295</v>
-      </c>
-      <c r="R37" s="49"/>
-    </row>
-    <row r="38" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="70"/>
+      <c r="Q37" s="93" t="s">
+        <v>294</v>
+      </c>
+      <c r="R37" s="48"/>
+    </row>
+    <row r="38" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="69"/>
       <c r="B38" s="40">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="44" t="s">
+      <c r="D38" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E38" s="44" t="s">
+      <c r="E38" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="44" t="s">
+      <c r="F38" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G38" s="44" t="s">
+      <c r="G38" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I38" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J38" s="44" t="s">
+      <c r="I38" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J38" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="K38" s="44" t="s">
+      <c r="K38" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="L38" s="44">
+      <c r="L38" s="43">
         <v>3</v>
       </c>
-      <c r="M38" s="44">
+      <c r="M38" s="43">
         <v>100</v>
       </c>
-      <c r="N38" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O38" s="45">
+      <c r="N38" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O38" s="44">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="P38" s="45">
+      <c r="P38" s="44">
         <f t="shared" ref="P38" si="15">O38*M38</f>
         <v>0.11</v>
       </c>
-      <c r="Q38" s="84"/>
-      <c r="R38" s="49"/>
-    </row>
-    <row r="39" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="70"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="48"/>
+    </row>
+    <row r="39" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="69"/>
       <c r="B39" s="39">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="43" t="s">
         <v>323</v>
       </c>
-      <c r="F39" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="G39" s="44" t="s">
+      <c r="H39" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="I39" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J39" s="43" t="s">
         <v>324</v>
       </c>
-      <c r="H39" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J39" s="44" t="s">
+      <c r="K39" s="43" t="s">
         <v>325</v>
       </c>
-      <c r="K39" s="44" t="s">
-        <v>326</v>
-      </c>
-      <c r="L39" s="44">
+      <c r="L39" s="43">
         <v>1</v>
       </c>
       <c r="M39" s="37">
         <v>100</v>
       </c>
-      <c r="N39" s="52" t="s">
+      <c r="N39" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O39" s="38">
@@ -4233,16 +4248,16 @@
         <f>O39*M39</f>
         <v>0.13</v>
       </c>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="49"/>
-    </row>
-    <row r="40" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="70"/>
+      <c r="Q39" s="87"/>
+      <c r="R39" s="48"/>
+    </row>
+    <row r="40" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="69"/>
       <c r="B40" s="39">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="37" t="s">
@@ -4275,7 +4290,7 @@
       <c r="M40" s="37">
         <v>100</v>
       </c>
-      <c r="N40" s="52" t="s">
+      <c r="N40" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O40" s="38">
@@ -4285,68 +4300,68 @@
         <f>O40*M40</f>
         <v>0.11</v>
       </c>
-      <c r="Q40" s="90"/>
-      <c r="R40" s="49"/>
-    </row>
-    <row r="41" spans="1:18" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A41" s="70"/>
+      <c r="Q40" s="87"/>
+      <c r="R40" s="48"/>
+    </row>
+    <row r="41" spans="1:18" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A41" s="69"/>
       <c r="B41" s="40">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="44" t="s">
+      <c r="D41" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="F41" s="44" t="s">
+      <c r="E41" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="F41" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="G41" s="44" t="s">
+      <c r="G41" s="55" t="s">
         <v>289</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I41" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J41" s="44" t="s">
-        <v>290</v>
-      </c>
-      <c r="K41" s="44" t="s">
+      <c r="I41" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="J41" s="43" t="s">
+        <v>327</v>
+      </c>
+      <c r="K41" s="43" t="s">
         <v>257</v>
       </c>
-      <c r="L41" s="44">
+      <c r="L41" s="43">
         <v>1</v>
       </c>
-      <c r="M41" s="44">
-        <v>20</v>
-      </c>
-      <c r="N41" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O41" s="45">
-        <v>2.7699999999999999E-2</v>
-      </c>
-      <c r="P41" s="45">
+      <c r="M41" s="43">
+        <v>50</v>
+      </c>
+      <c r="N41" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O41" s="44">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="P41" s="44">
         <f t="shared" ref="P41" si="16">O41*M41</f>
-        <v>0.55399999999999994</v>
-      </c>
-      <c r="Q41" s="84"/>
-      <c r="R41" s="49"/>
-    </row>
-    <row r="42" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="70"/>
+        <v>0.27499999999999997</v>
+      </c>
+      <c r="Q41" s="82"/>
+      <c r="R41" s="48"/>
+    </row>
+    <row r="42" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="69"/>
       <c r="B42" s="39">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="37" t="s">
@@ -4379,7 +4394,7 @@
       <c r="M42" s="37">
         <v>100</v>
       </c>
-      <c r="N42" s="52" t="s">
+      <c r="N42" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O42" s="38">
@@ -4389,68 +4404,68 @@
         <f>O42*M42</f>
         <v>0.12</v>
       </c>
-      <c r="Q42" s="90"/>
-      <c r="R42" s="49"/>
-    </row>
-    <row r="43" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="70"/>
+      <c r="Q42" s="87"/>
+      <c r="R42" s="48"/>
+    </row>
+    <row r="43" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="69"/>
       <c r="B43" s="40">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="44" t="s">
+      <c r="D43" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E43" s="44" t="s">
+      <c r="E43" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="44" t="s">
+      <c r="F43" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G43" s="44" t="s">
+      <c r="G43" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="H43" s="44" t="s">
+      <c r="H43" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I43" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J43" s="44" t="s">
+      <c r="I43" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J43" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="K43" s="44" t="s">
+      <c r="K43" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="L43" s="44">
+      <c r="L43" s="43">
         <v>2</v>
       </c>
-      <c r="M43" s="44">
+      <c r="M43" s="43">
         <v>100</v>
       </c>
-      <c r="N43" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O43" s="45">
+      <c r="N43" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O43" s="44">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="P43" s="45">
+      <c r="P43" s="44">
         <f t="shared" ref="P43" si="17">O43*M43</f>
         <v>0.31</v>
       </c>
-      <c r="Q43" s="84"/>
-      <c r="R43" s="49"/>
-    </row>
-    <row r="44" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="70"/>
+      <c r="Q43" s="82"/>
+      <c r="R43" s="48"/>
+    </row>
+    <row r="44" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="69"/>
       <c r="B44" s="39">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="50" t="s">
+      <c r="C44" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="37" t="s">
@@ -4483,7 +4498,7 @@
       <c r="M44" s="37">
         <v>100</v>
       </c>
-      <c r="N44" s="52" t="s">
+      <c r="N44" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O44" s="38">
@@ -4493,68 +4508,68 @@
         <f>O44*M44</f>
         <v>0.11</v>
       </c>
-      <c r="Q44" s="90"/>
-      <c r="R44" s="49"/>
-    </row>
-    <row r="45" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="70"/>
+      <c r="Q44" s="87"/>
+      <c r="R44" s="48"/>
+    </row>
+    <row r="45" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="69"/>
       <c r="B45" s="40">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D45" s="44" t="s">
+      <c r="D45" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="44" t="s">
+      <c r="E45" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="F45" s="44" t="s">
+      <c r="F45" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G45" s="44" t="s">
+      <c r="G45" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I45" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J45" s="44" t="s">
+      <c r="I45" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J45" s="43" t="s">
         <v>227</v>
       </c>
-      <c r="K45" s="44" t="s">
+      <c r="K45" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="L45" s="44">
+      <c r="L45" s="43">
         <v>2</v>
       </c>
-      <c r="M45" s="44">
+      <c r="M45" s="43">
         <v>100</v>
       </c>
-      <c r="N45" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O45" s="45">
+      <c r="N45" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O45" s="44">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P45" s="45">
+      <c r="P45" s="44">
         <f t="shared" ref="P45" si="18">O45*M45</f>
         <v>0.12</v>
       </c>
-      <c r="Q45" s="84"/>
-      <c r="R45" s="49"/>
-    </row>
-    <row r="46" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="70"/>
+      <c r="Q45" s="82"/>
+      <c r="R45" s="48"/>
+    </row>
+    <row r="46" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="69"/>
       <c r="B46" s="39">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="37" t="s">
@@ -4587,7 +4602,7 @@
       <c r="M46" s="37">
         <v>100</v>
       </c>
-      <c r="N46" s="52" t="s">
+      <c r="N46" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O46" s="38">
@@ -4597,68 +4612,68 @@
         <f>O46*M46</f>
         <v>0.18</v>
       </c>
-      <c r="Q46" s="90"/>
-      <c r="R46" s="49"/>
-    </row>
-    <row r="47" spans="1:18" s="129" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="121"/>
-      <c r="B47" s="122">
+      <c r="Q46" s="87"/>
+      <c r="R46" s="48"/>
+    </row>
+    <row r="47" spans="1:18" s="108" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="100"/>
+      <c r="B47" s="101">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="123" t="s">
+      <c r="C47" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="124" t="s">
+      <c r="D47" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="124" t="s">
+      <c r="E47" s="103" t="s">
         <v>98</v>
       </c>
-      <c r="F47" s="124" t="s">
+      <c r="F47" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="G47" s="124" t="s">
+      <c r="G47" s="103" t="s">
         <v>167</v>
       </c>
-      <c r="H47" s="124" t="s">
+      <c r="H47" s="103" t="s">
         <v>181</v>
       </c>
-      <c r="I47" s="124" t="s">
-        <v>267</v>
-      </c>
-      <c r="J47" s="124" t="s">
+      <c r="I47" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="J47" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="K47" s="124" t="s">
+      <c r="K47" s="103" t="s">
         <v>263</v>
       </c>
-      <c r="L47" s="124">
+      <c r="L47" s="103">
         <v>1</v>
       </c>
-      <c r="M47" s="124">
+      <c r="M47" s="103">
         <v>20</v>
       </c>
-      <c r="N47" s="125" t="s">
-        <v>281</v>
-      </c>
-      <c r="O47" s="126">
+      <c r="N47" s="104" t="s">
+        <v>281</v>
+      </c>
+      <c r="O47" s="105">
         <v>2.75E-2</v>
       </c>
-      <c r="P47" s="126">
+      <c r="P47" s="105">
         <f t="shared" ref="P47" si="19">O47*M47</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q47" s="127"/>
-      <c r="R47" s="128"/>
-    </row>
-    <row r="48" spans="1:18" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="70"/>
+      <c r="Q47" s="106"/>
+      <c r="R47" s="107"/>
+    </row>
+    <row r="48" spans="1:18" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="69"/>
       <c r="B48" s="39">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="C48" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="37" t="s">
@@ -4691,7 +4706,7 @@
       <c r="M48" s="37">
         <v>50</v>
       </c>
-      <c r="N48" s="52" t="s">
+      <c r="N48" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O48" s="38">
@@ -4701,113 +4716,113 @@
         <f>O48*M48</f>
         <v>0.44</v>
       </c>
-      <c r="Q48" s="90"/>
-      <c r="R48" s="49"/>
-    </row>
-    <row r="49" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="70"/>
+      <c r="Q48" s="87"/>
+      <c r="R48" s="48"/>
+    </row>
+    <row r="49" spans="1:19" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="69"/>
       <c r="B49" s="39">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="D49" s="54" t="s">
-        <v>315</v>
-      </c>
-      <c r="E49" s="54" t="s">
+      <c r="D49" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="E49" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="F49" s="54" t="s">
+      <c r="F49" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="G49" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="H49" s="55" t="s">
-        <v>267</v>
-      </c>
-      <c r="I49" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="J49" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="K49" s="54" t="s">
-        <v>267</v>
-      </c>
-      <c r="L49" s="54">
+      <c r="G49" s="53" t="s">
+        <v>346</v>
+      </c>
+      <c r="H49" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="I49" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="J49" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="K49" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="L49" s="53">
         <v>6</v>
       </c>
-      <c r="M49" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="N49" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="O49" s="57" t="s">
-        <v>267</v>
-      </c>
-      <c r="P49" s="57" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q49" s="117"/>
-      <c r="R49" s="58"/>
-    </row>
-    <row r="50" spans="1:19" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A50" s="70"/>
+      <c r="M49" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="N49" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="O49" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="P49" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q49" s="96"/>
+      <c r="R49" s="57"/>
+    </row>
+    <row r="50" spans="1:19" s="71" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A50" s="69"/>
       <c r="B50" s="40">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="51" t="s">
+      <c r="C50" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="44" t="s">
-        <v>316</v>
-      </c>
-      <c r="E50" s="44" t="s">
-        <v>345</v>
-      </c>
-      <c r="F50" s="44" t="s">
+      <c r="D50" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="F50" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="G50" s="44" t="s">
-        <v>344</v>
-      </c>
-      <c r="H50" s="44" t="s">
+      <c r="G50" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="H50" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="I50" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J50" s="44" t="s">
-        <v>343</v>
+      <c r="I50" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J50" s="43" t="s">
+        <v>342</v>
       </c>
       <c r="K50" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L50" s="44">
+      <c r="L50" s="43">
         <v>2</v>
       </c>
-      <c r="M50" s="44">
+      <c r="M50" s="43">
         <v>20</v>
       </c>
-      <c r="N50" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O50" s="45">
+      <c r="N50" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O50" s="44">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="P50" s="45">
+      <c r="P50" s="44">
         <f t="shared" ref="P50:P52" si="20">O50*M50</f>
         <v>0.39200000000000002</v>
       </c>
-      <c r="Q50" s="114" t="s">
-        <v>342</v>
-      </c>
-      <c r="R50" s="44"/>
+      <c r="Q50" s="93" t="s">
+        <v>341</v>
+      </c>
+      <c r="R50" s="43"/>
     </row>
     <row r="51" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
@@ -4815,29 +4830,29 @@
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="51" t="s">
+      <c r="C51" s="50" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>317</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>318</v>
       </c>
       <c r="F51" s="37" t="s">
         <v>268</v>
       </c>
       <c r="G51" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="H51" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="I51" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>320</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>321</v>
       </c>
       <c r="K51" s="37" t="s">
         <v>267</v>
@@ -4848,79 +4863,79 @@
       <c r="M51" s="37">
         <v>2</v>
       </c>
-      <c r="N51" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="O51" s="45">
+      <c r="N51" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="O51" s="44">
         <v>0.42799999999999999</v>
       </c>
       <c r="P51" s="38">
         <f>O51*M51</f>
         <v>0.85599999999999998</v>
       </c>
-      <c r="Q51" s="118"/>
+      <c r="Q51" s="97"/>
       <c r="R51" s="37"/>
-      <c r="S51" s="72"/>
-    </row>
-    <row r="52" spans="1:19" s="72" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A52" s="70"/>
+      <c r="S51" s="71"/>
+    </row>
+    <row r="52" spans="1:19" s="71" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A52" s="69"/>
       <c r="B52" s="40">
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="51" t="s">
+      <c r="C52" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="43" t="s">
         <v>266</v>
       </c>
-      <c r="E52" s="44" t="s">
+      <c r="E52" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="F52" s="44" t="s">
+      <c r="F52" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="G52" s="44" t="s">
+      <c r="G52" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="H52" s="44" t="s">
+      <c r="H52" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="I52" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J52" s="44" t="s">
+      <c r="I52" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J52" s="43" t="s">
         <v>235</v>
       </c>
       <c r="K52" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L52" s="44">
+      <c r="L52" s="43">
         <v>1</v>
       </c>
-      <c r="M52" s="44">
+      <c r="M52" s="43">
         <v>10</v>
       </c>
-      <c r="N52" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O52" s="45">
+      <c r="N52" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O52" s="44">
         <v>6.2100000000000002E-2</v>
       </c>
-      <c r="P52" s="45">
+      <c r="P52" s="44">
         <f t="shared" si="20"/>
         <v>0.621</v>
       </c>
-      <c r="Q52" s="84"/>
-      <c r="R52" s="49"/>
-    </row>
-    <row r="53" spans="1:19" s="72" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A53" s="70"/>
+      <c r="Q52" s="82"/>
+      <c r="R52" s="48"/>
+    </row>
+    <row r="53" spans="1:19" s="71" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A53" s="69"/>
       <c r="B53" s="39">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="37" t="s">
@@ -4953,7 +4968,7 @@
       <c r="M53" s="37">
         <v>2</v>
       </c>
-      <c r="N53" s="52" t="s">
+      <c r="N53" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O53" s="38">
@@ -4963,68 +4978,68 @@
         <f>O53*M53</f>
         <v>0.32419999999999999</v>
       </c>
-      <c r="Q53" s="90"/>
-      <c r="R53" s="49"/>
-    </row>
-    <row r="54" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="70"/>
+      <c r="Q53" s="87"/>
+      <c r="R53" s="48"/>
+    </row>
+    <row r="54" spans="1:19" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="69"/>
       <c r="B54" s="40">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="51" t="s">
+      <c r="C54" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="D54" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="E54" s="44" t="s">
+      <c r="E54" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="F54" s="44" t="s">
+      <c r="F54" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="G54" s="44" t="s">
+      <c r="G54" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="H54" s="44" t="s">
+      <c r="H54" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="I54" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J54" s="44" t="s">
+      <c r="I54" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J54" s="43" t="s">
         <v>287</v>
       </c>
       <c r="K54" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L54" s="44">
+      <c r="L54" s="43">
         <v>1</v>
       </c>
-      <c r="M54" s="44">
+      <c r="M54" s="43">
         <v>5</v>
       </c>
-      <c r="N54" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O54" s="45">
+      <c r="N54" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O54" s="44">
         <v>0.1341</v>
       </c>
-      <c r="P54" s="45">
+      <c r="P54" s="44">
         <f t="shared" ref="P54" si="21">O54*M54</f>
         <v>0.67049999999999998</v>
       </c>
-      <c r="Q54" s="84"/>
-      <c r="R54" s="49"/>
-    </row>
-    <row r="55" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A55" s="70"/>
+      <c r="Q54" s="82"/>
+      <c r="R54" s="48"/>
+    </row>
+    <row r="55" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A55" s="69"/>
       <c r="B55" s="39">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="49" t="s">
         <v>16</v>
       </c>
       <c r="D55" s="37" t="s">
@@ -5057,7 +5072,7 @@
       <c r="M55" s="37">
         <v>5</v>
       </c>
-      <c r="N55" s="52" t="s">
+      <c r="N55" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O55" s="38">
@@ -5067,68 +5082,68 @@
         <f>O55*M55</f>
         <v>0.97699999999999998</v>
       </c>
-      <c r="Q55" s="90"/>
-      <c r="R55" s="49"/>
-    </row>
-    <row r="56" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A56" s="70"/>
+      <c r="Q55" s="87"/>
+      <c r="R55" s="48"/>
+    </row>
+    <row r="56" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A56" s="69"/>
       <c r="B56" s="40">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="51" t="s">
+      <c r="C56" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="E56" s="44" t="s">
+      <c r="E56" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="F56" s="44" t="s">
+      <c r="F56" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="G56" s="44" t="s">
+      <c r="G56" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="H56" s="44" t="s">
+      <c r="H56" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="I56" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J56" s="44" t="s">
+      <c r="I56" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J56" s="43" t="s">
         <v>233</v>
       </c>
       <c r="K56" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L56" s="44">
+      <c r="L56" s="43">
         <v>1</v>
       </c>
-      <c r="M56" s="44">
+      <c r="M56" s="43">
         <v>2</v>
       </c>
-      <c r="N56" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O56" s="45">
+      <c r="N56" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O56" s="44">
         <v>0.43909999999999999</v>
       </c>
-      <c r="P56" s="45">
+      <c r="P56" s="44">
         <f t="shared" ref="P56" si="22">O56*M56</f>
         <v>0.87819999999999998</v>
       </c>
-      <c r="Q56" s="84"/>
-      <c r="R56" s="49"/>
-    </row>
-    <row r="57" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A57" s="70"/>
+      <c r="Q56" s="82"/>
+      <c r="R56" s="48"/>
+    </row>
+    <row r="57" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A57" s="69"/>
       <c r="B57" s="39">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="37" t="s">
@@ -5161,7 +5176,7 @@
       <c r="M57" s="37">
         <v>5</v>
       </c>
-      <c r="N57" s="52" t="s">
+      <c r="N57" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O57" s="38">
@@ -5171,16 +5186,16 @@
         <f>O57*M57</f>
         <v>0.77400000000000002</v>
       </c>
-      <c r="Q57" s="90"/>
-      <c r="R57" s="49"/>
-    </row>
-    <row r="58" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A58" s="70"/>
+      <c r="Q57" s="87"/>
+      <c r="R57" s="48"/>
+    </row>
+    <row r="58" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A58" s="69"/>
       <c r="B58" s="39">
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
-      <c r="C58" s="50" t="s">
+      <c r="C58" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="37" t="s">
@@ -5213,7 +5228,7 @@
       <c r="M58" s="37">
         <v>2</v>
       </c>
-      <c r="N58" s="52" t="s">
+      <c r="N58" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O58" s="38">
@@ -5223,68 +5238,68 @@
         <f>O58*M58</f>
         <v>10.2424</v>
       </c>
-      <c r="Q58" s="90"/>
-      <c r="R58" s="49"/>
-    </row>
-    <row r="59" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A59" s="70"/>
+      <c r="Q58" s="87"/>
+      <c r="R58" s="48"/>
+    </row>
+    <row r="59" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A59" s="69"/>
       <c r="B59" s="40">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="51" t="s">
+      <c r="C59" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="44" t="s">
+      <c r="D59" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="E59" s="44" t="s">
+      <c r="E59" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="44" t="s">
+      <c r="F59" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="G59" s="44" t="s">
+      <c r="G59" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="H59" s="44" t="s">
+      <c r="H59" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="I59" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J59" s="44" t="s">
+      <c r="I59" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J59" s="43" t="s">
         <v>237</v>
       </c>
       <c r="K59" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L59" s="44">
+      <c r="L59" s="43">
         <v>1</v>
       </c>
-      <c r="M59" s="44">
+      <c r="M59" s="43">
         <v>5</v>
       </c>
-      <c r="N59" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O59" s="45">
+      <c r="N59" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O59" s="44">
         <v>0.15670000000000001</v>
       </c>
-      <c r="P59" s="45">
+      <c r="P59" s="44">
         <f t="shared" ref="P59" si="23">O59*M59</f>
         <v>0.78350000000000009</v>
       </c>
-      <c r="Q59" s="84"/>
-      <c r="R59" s="49"/>
-    </row>
-    <row r="60" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A60" s="70"/>
+      <c r="Q59" s="82"/>
+      <c r="R59" s="48"/>
+    </row>
+    <row r="60" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A60" s="69"/>
       <c r="B60" s="39">
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="C60" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="37" t="s">
@@ -5317,7 +5332,7 @@
       <c r="M60" s="37">
         <v>2</v>
       </c>
-      <c r="N60" s="52" t="s">
+      <c r="N60" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O60" s="38">
@@ -5327,68 +5342,68 @@
         <f>O60*M60</f>
         <v>1.9378</v>
       </c>
-      <c r="Q60" s="90"/>
-      <c r="R60" s="49"/>
-    </row>
-    <row r="61" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="70"/>
+      <c r="Q60" s="87"/>
+      <c r="R60" s="48"/>
+    </row>
+    <row r="61" spans="1:19" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="69"/>
       <c r="B61" s="40">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="51" t="s">
+      <c r="C61" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E61" s="44" t="s">
+      <c r="E61" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="F61" s="44" t="s">
+      <c r="F61" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="G61" s="44" t="s">
+      <c r="G61" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="H61" s="44" t="s">
+      <c r="H61" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="I61" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J61" s="44" t="s">
+      <c r="I61" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J61" s="43" t="s">
         <v>239</v>
       </c>
       <c r="K61" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L61" s="44">
+      <c r="L61" s="43">
         <v>1</v>
       </c>
-      <c r="M61" s="44">
+      <c r="M61" s="43">
         <v>2</v>
       </c>
-      <c r="N61" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="O61" s="45">
+      <c r="N61" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="O61" s="44">
         <v>0.28870000000000001</v>
       </c>
-      <c r="P61" s="45">
+      <c r="P61" s="44">
         <f t="shared" ref="P61" si="24">O61*M61</f>
         <v>0.57740000000000002</v>
       </c>
-      <c r="Q61" s="84"/>
-      <c r="R61" s="49"/>
-    </row>
-    <row r="62" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A62" s="70"/>
+      <c r="Q61" s="82"/>
+      <c r="R61" s="48"/>
+    </row>
+    <row r="62" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A62" s="69"/>
       <c r="B62" s="39">
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="50" t="s">
+      <c r="C62" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="37" t="s">
@@ -5421,7 +5436,7 @@
       <c r="M62" s="37">
         <v>2</v>
       </c>
-      <c r="N62" s="52" t="s">
+      <c r="N62" s="51" t="s">
         <v>281</v>
       </c>
       <c r="O62" s="38">
@@ -5431,288 +5446,288 @@
         <f>O62*M62</f>
         <v>4.1302000000000003</v>
       </c>
-      <c r="Q62" s="90"/>
-      <c r="R62" s="49"/>
-    </row>
-    <row r="63" spans="1:19" s="72" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A63" s="70"/>
-      <c r="B63" s="59">
+      <c r="Q62" s="87"/>
+      <c r="R62" s="48"/>
+    </row>
+    <row r="63" spans="1:19" s="71" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A63" s="69"/>
+      <c r="B63" s="58">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="60" t="s">
+      <c r="C63" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="49" t="s">
+      <c r="D63" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="E63" s="49" t="s">
+      <c r="E63" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="F63" s="49" t="s">
+      <c r="F63" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="G63" s="49" t="s">
+      <c r="G63" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="H63" s="49" t="s">
+      <c r="H63" s="48" t="s">
         <v>201</v>
       </c>
-      <c r="I63" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J63" s="49" t="s">
+      <c r="I63" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J63" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="K63" s="61" t="s">
-        <v>267</v>
-      </c>
-      <c r="L63" s="49">
+      <c r="K63" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="L63" s="48">
         <v>1</v>
       </c>
-      <c r="M63" s="49">
+      <c r="M63" s="48">
         <v>2</v>
       </c>
-      <c r="N63" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="O63" s="63">
+      <c r="N63" s="61" t="s">
+        <v>281</v>
+      </c>
+      <c r="O63" s="62">
         <v>1.2919</v>
       </c>
-      <c r="P63" s="63">
+      <c r="P63" s="62">
         <f t="shared" ref="P63" si="25">O63*M63</f>
         <v>2.5838000000000001</v>
       </c>
-      <c r="Q63" s="92"/>
-      <c r="R63" s="49"/>
-    </row>
-    <row r="64" spans="1:19" s="72" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="70"/>
-      <c r="B64" s="59">
+      <c r="Q63" s="89"/>
+      <c r="R63" s="48"/>
+    </row>
+    <row r="64" spans="1:19" s="71" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="69"/>
+      <c r="B64" s="58">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="60" t="s">
-        <v>329</v>
-      </c>
-      <c r="D64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="F64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="H64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="I64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="K64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="L64" s="49">
+      <c r="C64" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="D64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="F64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="H64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="L64" s="48">
         <v>1</v>
       </c>
-      <c r="M64" s="49"/>
-      <c r="N64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="O64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="P64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q64" s="119" t="s">
-        <v>337</v>
-      </c>
-      <c r="R64" s="49"/>
-    </row>
-    <row r="65" spans="1:18" s="72" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="70"/>
-      <c r="B65" s="59">
+      <c r="M64" s="48"/>
+      <c r="N64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="O64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="P64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q64" s="98" t="s">
+        <v>336</v>
+      </c>
+      <c r="R64" s="48"/>
+    </row>
+    <row r="65" spans="1:18" s="71" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="69"/>
+      <c r="B65" s="58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>330</v>
-      </c>
-      <c r="D65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="F65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="H65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="I65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="K65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="L65" s="49">
+      <c r="C65" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="D65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="H65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="L65" s="48">
         <v>1</v>
       </c>
-      <c r="M65" s="49"/>
-      <c r="N65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="O65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="P65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q65" s="119" t="s">
-        <v>337</v>
-      </c>
-      <c r="R65" s="49"/>
-    </row>
-    <row r="66" spans="1:18" s="72" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="70"/>
-      <c r="B66" s="59">
+      <c r="M65" s="48"/>
+      <c r="N65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="O65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="P65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q65" s="98" t="s">
+        <v>336</v>
+      </c>
+      <c r="R65" s="48"/>
+    </row>
+    <row r="66" spans="1:18" s="71" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="69"/>
+      <c r="B66" s="58">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="60" t="s">
+      <c r="C66" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K66" s="48"/>
+      <c r="L66" s="48">
+        <v>1</v>
+      </c>
+      <c r="M66" s="48"/>
+      <c r="N66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="O66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="P66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q66" s="98" t="s">
         <v>336</v>
       </c>
-      <c r="D66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="F66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="H66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="I66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="K66" s="49"/>
-      <c r="L66" s="49">
-        <v>1</v>
-      </c>
-      <c r="M66" s="49"/>
-      <c r="N66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="O66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="P66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q66" s="119" t="s">
-        <v>337</v>
-      </c>
-      <c r="R66" s="49"/>
-    </row>
-    <row r="67" spans="1:18" s="72" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="70"/>
-      <c r="B67" s="59">
+      <c r="R66" s="48"/>
+    </row>
+    <row r="67" spans="1:18" s="71" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="69"/>
+      <c r="B67" s="58">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="60" t="s">
+      <c r="C67" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="D67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="D67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E67" s="49" t="s">
+      <c r="F67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G67" s="48" t="s">
         <v>332</v>
       </c>
-      <c r="F67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G67" s="49" t="s">
+      <c r="H67" s="48" t="s">
         <v>333</v>
       </c>
-      <c r="H67" s="49" t="s">
+      <c r="I67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J67" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="I67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J67" s="49" t="s">
-        <v>335</v>
-      </c>
-      <c r="K67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="L67" s="49">
+      <c r="K67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="L67" s="48">
         <v>1</v>
       </c>
-      <c r="M67" s="49">
+      <c r="M67" s="48">
         <v>2</v>
       </c>
-      <c r="N67" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="O67" s="63">
+      <c r="N67" s="61" t="s">
+        <v>281</v>
+      </c>
+      <c r="O67" s="62">
         <v>0.1202</v>
       </c>
-      <c r="P67" s="88">
+      <c r="P67" s="85">
         <f>O67*M67</f>
         <v>0.2404</v>
       </c>
-      <c r="Q67" s="92"/>
-      <c r="R67" s="120"/>
+      <c r="Q67" s="89"/>
+      <c r="R67" s="99"/>
     </row>
     <row r="68" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
-      <c r="B68" s="75"/>
-      <c r="C68" s="76"/>
-      <c r="D68" s="77"/>
-      <c r="E68" s="78"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="80"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="80"/>
-      <c r="J68" s="79"/>
-      <c r="K68" s="80"/>
-      <c r="L68" s="80"/>
-      <c r="M68" s="106" t="s">
+      <c r="B68" s="74"/>
+      <c r="C68" s="75"/>
+      <c r="D68" s="76"/>
+      <c r="E68" s="77"/>
+      <c r="F68" s="78"/>
+      <c r="G68" s="79"/>
+      <c r="H68" s="78"/>
+      <c r="I68" s="79"/>
+      <c r="J68" s="78"/>
+      <c r="K68" s="79"/>
+      <c r="L68" s="79"/>
+      <c r="M68" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="N68" s="107"/>
-      <c r="O68" s="107"/>
+      <c r="N68" s="114"/>
+      <c r="O68" s="114"/>
       <c r="P68" s="41">
         <f>SUM(P10:P67)</f>
-        <v>47.065000000000019</v>
-      </c>
-      <c r="Q68" s="108"/>
-      <c r="R68" s="109"/>
+        <v>46.786000000000008</v>
+      </c>
+      <c r="Q68" s="115"/>
+      <c r="R68" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5765,15 +5780,15 @@
     <hyperlink ref="N63" r:id="rId41"/>
     <hyperlink ref="N18" r:id="rId42"/>
     <hyperlink ref="N54" r:id="rId43"/>
-    <hyperlink ref="N41" r:id="rId44"/>
-    <hyperlink ref="N25" r:id="rId45"/>
-    <hyperlink ref="N29" r:id="rId46"/>
-    <hyperlink ref="N32" r:id="rId47"/>
-    <hyperlink ref="N39" r:id="rId48"/>
-    <hyperlink ref="N51" r:id="rId49"/>
-    <hyperlink ref="N67" r:id="rId50"/>
-    <hyperlink ref="N15" r:id="rId51"/>
-    <hyperlink ref="N50" r:id="rId52"/>
+    <hyperlink ref="N25" r:id="rId44"/>
+    <hyperlink ref="N29" r:id="rId45"/>
+    <hyperlink ref="N32" r:id="rId46"/>
+    <hyperlink ref="N39" r:id="rId47"/>
+    <hyperlink ref="N51" r:id="rId48"/>
+    <hyperlink ref="N67" r:id="rId49"/>
+    <hyperlink ref="N15" r:id="rId50"/>
+    <hyperlink ref="N50" r:id="rId51"/>
+    <hyperlink ref="N41" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId53"/>
@@ -5818,15 +5833,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="103"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="110"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5836,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="45" t="s">
         <v>279</v>
       </c>
       <c r="G2" s="12"/>
@@ -5861,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="46" t="s">
         <v>280</v>
       </c>
       <c r="G3" s="13"/>
@@ -5876,7 +5891,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="104"/>
+      <c r="S3" s="111"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5886,7 +5901,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="46" t="s">
         <v>280</v>
       </c>
       <c r="G4" s="14"/>
@@ -5901,7 +5916,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="105"/>
+      <c r="S4" s="112"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5911,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="47" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="15"/>
@@ -5926,7 +5941,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="105"/>
+      <c r="S5" s="112"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5947,7 +5962,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="105"/>
+      <c r="S6" s="112"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5968,7 +5983,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="105"/>
+      <c r="S7" s="112"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5989,7 +6004,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="105"/>
+      <c r="S8" s="112"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6029,13 +6044,13 @@
       <c r="M9" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="N9" s="89" t="s">
+      <c r="N9" s="86" t="s">
         <v>273</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="P9" s="94" t="s">
+      <c r="P9" s="122" t="s">
         <v>275</v>
       </c>
       <c r="Q9" s="30" t="s">
@@ -6044,7 +6059,7 @@
       <c r="R9" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="S9" s="30" t="s">
+      <c r="S9" s="91" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6054,7 +6069,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="37" t="s">
@@ -6088,21 +6103,21 @@
         <f>L10*5</f>
         <v>15</v>
       </c>
-      <c r="N10" s="90">
+      <c r="N10" s="87">
         <v>50</v>
       </c>
-      <c r="O10" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P10" s="95">
+      <c r="O10" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P10" s="123">
         <v>1.89E-2</v>
       </c>
-      <c r="Q10" s="81">
+      <c r="Q10" s="80">
         <f>P10*N10</f>
         <v>0.94500000000000006</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="43"/>
+      <c r="S10" s="133"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
@@ -6110,55 +6125,55 @@
         <f t="shared" ref="B11:B67" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G11" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="I11" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J11" s="44" t="s">
+      <c r="I11" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J11" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="K11" s="44" t="s">
+      <c r="K11" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="L11" s="44">
+      <c r="L11" s="43">
         <v>2</v>
       </c>
-      <c r="M11" s="44">
+      <c r="M11" s="43">
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>10</v>
       </c>
-      <c r="N11" s="84">
+      <c r="N11" s="82">
         <v>11</v>
       </c>
-      <c r="O11" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P11" s="96">
+      <c r="O11" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P11" s="124">
         <v>1.4064000000000001</v>
       </c>
-      <c r="Q11" s="81">
+      <c r="Q11" s="80">
         <f t="shared" ref="Q11:Q63" si="2">P11*N11</f>
         <v>15.470400000000001</v>
       </c>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="83"/>
     </row>
     <row r="12" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
@@ -6166,7 +6181,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
@@ -6200,21 +6215,21 @@
         <f>L12*5</f>
         <v>70</v>
       </c>
-      <c r="N12" s="90">
+      <c r="N12" s="87">
         <v>100</v>
       </c>
-      <c r="O12" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P12" s="95">
+      <c r="O12" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P12" s="123">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="Q12" s="81">
+      <c r="Q12" s="80">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="R12" s="37"/>
-      <c r="S12" s="49"/>
+      <c r="S12" s="129"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
@@ -6222,55 +6237,55 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I13" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J13" s="44" t="s">
+      <c r="I13" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J13" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="K13" s="44" t="s">
+      <c r="K13" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="L13" s="44">
+      <c r="L13" s="43">
         <v>1</v>
       </c>
-      <c r="M13" s="44">
+      <c r="M13" s="43">
         <f t="shared" ref="M13" si="3">L13*5</f>
         <v>5</v>
       </c>
-      <c r="N13" s="84">
+      <c r="N13" s="82">
         <v>100</v>
       </c>
-      <c r="O13" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P13" s="96">
+      <c r="O13" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P13" s="124">
         <v>2.8E-3</v>
       </c>
-      <c r="Q13" s="81">
+      <c r="Q13" s="80">
         <f t="shared" si="2"/>
         <v>0.27999999999999997</v>
       </c>
-      <c r="R13" s="44"/>
-      <c r="S13" s="49"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="129"/>
     </row>
     <row r="14" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -6278,11 +6293,11 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>71</v>
@@ -6312,21 +6327,21 @@
         <f>L14*5</f>
         <v>110</v>
       </c>
-      <c r="N14" s="90">
+      <c r="N14" s="87">
         <v>200</v>
       </c>
-      <c r="O14" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P14" s="95">
+      <c r="O14" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P14" s="123">
         <v>1.8E-3</v>
       </c>
-      <c r="Q14" s="81">
+      <c r="Q14" s="80">
         <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
       <c r="R14" s="37"/>
-      <c r="S14" s="49"/>
+      <c r="S14" s="129"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -6334,55 +6349,55 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="56" t="s">
+      <c r="G15" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I15" s="44" t="s">
+      <c r="I15" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="J15" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="J15" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="K15" s="44" t="s">
+      <c r="K15" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="43">
         <v>2</v>
       </c>
-      <c r="M15" s="44">
+      <c r="M15" s="43">
         <f t="shared" ref="M15" si="4">L15*5</f>
         <v>10</v>
       </c>
-      <c r="N15" s="84">
+      <c r="N15" s="82">
         <v>20</v>
       </c>
-      <c r="O15" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P15" s="45">
+      <c r="O15" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P15" s="94">
         <v>1.77E-2</v>
       </c>
-      <c r="Q15" s="81">
+      <c r="Q15" s="80">
         <f t="shared" si="2"/>
         <v>0.35399999999999998</v>
       </c>
-      <c r="R15" s="44"/>
-      <c r="S15" s="49"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="129"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -6390,7 +6405,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
@@ -6424,21 +6439,21 @@
         <f>L16*5</f>
         <v>10</v>
       </c>
-      <c r="N16" s="90">
+      <c r="N16" s="87">
         <v>15</v>
       </c>
-      <c r="O16" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P16" s="95">
+      <c r="O16" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P16" s="123">
         <v>0.42320000000000002</v>
       </c>
-      <c r="Q16" s="81">
+      <c r="Q16" s="80">
         <f t="shared" si="2"/>
         <v>6.3480000000000008</v>
       </c>
       <c r="R16" s="37"/>
-      <c r="S16" s="49"/>
+      <c r="S16" s="129"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -6446,55 +6461,55 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="F17" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J17" s="44" t="s">
+      <c r="I17" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J17" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K17" s="43" t="s">
         <v>249</v>
       </c>
-      <c r="L17" s="44">
+      <c r="L17" s="43">
         <v>6</v>
       </c>
-      <c r="M17" s="44">
+      <c r="M17" s="43">
         <f t="shared" ref="M17" si="5">L17*5</f>
         <v>30</v>
       </c>
-      <c r="N17" s="84">
+      <c r="N17" s="82">
         <v>40</v>
       </c>
-      <c r="O17" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P17" s="96">
+      <c r="O17" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P17" s="124">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="Q17" s="81">
+      <c r="Q17" s="80">
         <f t="shared" si="2"/>
         <v>0.95200000000000007</v>
       </c>
-      <c r="R17" s="44"/>
-      <c r="S17" s="49"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="129"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -6502,7 +6517,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="37" t="s">
@@ -6514,7 +6529,7 @@
       <c r="F18" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="54" t="s">
+      <c r="G18" s="53" t="s">
         <v>148</v>
       </c>
       <c r="H18" s="37" t="s">
@@ -6536,21 +6551,21 @@
         <f>L18*5</f>
         <v>15</v>
       </c>
-      <c r="N18" s="90">
+      <c r="N18" s="87">
         <v>50</v>
       </c>
-      <c r="O18" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P18" s="95">
+      <c r="O18" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P18" s="123">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q18" s="81">
+      <c r="Q18" s="80">
         <f t="shared" si="2"/>
         <v>0.27499999999999997</v>
       </c>
       <c r="R18" s="37"/>
-      <c r="S18" s="49"/>
+      <c r="S18" s="129"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -6558,55 +6573,55 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="G19" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I19" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J19" s="44" t="s">
+      <c r="I19" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J19" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="K19" s="44" t="s">
+      <c r="K19" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="L19" s="44">
+      <c r="L19" s="43">
         <v>1</v>
       </c>
-      <c r="M19" s="44">
+      <c r="M19" s="43">
         <f t="shared" ref="M19" si="6">L19*5</f>
         <v>5</v>
       </c>
-      <c r="N19" s="84">
+      <c r="N19" s="82">
         <v>20</v>
       </c>
-      <c r="O19" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P19" s="96">
+      <c r="O19" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P19" s="124">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="Q19" s="81">
+      <c r="Q19" s="80">
         <f t="shared" si="2"/>
         <v>0.40399999999999997</v>
       </c>
-      <c r="R19" s="44"/>
-      <c r="S19" s="49"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="129"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -6614,55 +6629,55 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I20" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J20" s="44" t="s">
+      <c r="I20" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J20" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="K20" s="44" t="s">
+      <c r="K20" s="43" t="s">
         <v>251</v>
       </c>
-      <c r="L20" s="44">
+      <c r="L20" s="43">
         <v>2</v>
       </c>
-      <c r="M20" s="44">
+      <c r="M20" s="43">
         <f t="shared" ref="M20" si="7">L20*5</f>
         <v>10</v>
       </c>
-      <c r="N20" s="84">
+      <c r="N20" s="82">
         <v>100</v>
       </c>
-      <c r="O20" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P20" s="96">
+      <c r="O20" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P20" s="124">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="Q20" s="81">
+      <c r="Q20" s="80">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
-      <c r="R20" s="44"/>
-      <c r="S20" s="49"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="129"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -6670,7 +6685,7 @@
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="37" t="s">
@@ -6704,21 +6719,21 @@
         <f>L21*5</f>
         <v>10</v>
       </c>
-      <c r="N21" s="90">
+      <c r="N21" s="87">
         <v>100</v>
       </c>
-      <c r="O21" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P21" s="95">
+      <c r="O21" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P21" s="123">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Q21" s="81">
+      <c r="Q21" s="80">
         <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="R21" s="37"/>
-      <c r="S21" s="49"/>
+      <c r="S21" s="129"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
@@ -6726,55 +6741,55 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="44" t="s">
+      <c r="G22" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I22" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J22" s="44" t="s">
+      <c r="I22" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J22" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="43" t="s">
         <v>253</v>
       </c>
-      <c r="L22" s="44">
+      <c r="L22" s="43">
         <v>1</v>
       </c>
-      <c r="M22" s="44">
+      <c r="M22" s="43">
         <f t="shared" ref="M22" si="8">L22*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="84">
+      <c r="N22" s="82">
         <v>100</v>
       </c>
-      <c r="O22" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P22" s="96">
+      <c r="O22" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P22" s="124">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="Q22" s="81">
+      <c r="Q22" s="80">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="R22" s="44"/>
-      <c r="S22" s="49"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="129"/>
     </row>
     <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -6782,55 +6797,55 @@
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="44" t="s">
+      <c r="E23" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="44" t="s">
+      <c r="F23" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="I23" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J23" s="44" t="s">
+      <c r="I23" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J23" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="K23" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L23" s="44">
+      <c r="K23" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L23" s="43">
         <v>1</v>
       </c>
       <c r="M23" s="37">
         <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="90">
+      <c r="N23" s="87">
         <v>10</v>
       </c>
-      <c r="O23" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P23" s="96">
+      <c r="O23" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P23" s="124">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="Q23" s="81">
+      <c r="Q23" s="80">
         <f t="shared" si="2"/>
         <v>0.8640000000000001</v>
       </c>
       <c r="R23" s="37"/>
-      <c r="S23" s="49"/>
+      <c r="S23" s="129"/>
     </row>
     <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -6838,7 +6853,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="49" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="37" t="s">
@@ -6868,25 +6883,25 @@
       <c r="L24" s="37">
         <v>1</v>
       </c>
-      <c r="M24" s="44">
+      <c r="M24" s="43">
         <f t="shared" ref="M24" si="9">L24*5</f>
         <v>5</v>
       </c>
-      <c r="N24" s="84">
+      <c r="N24" s="82">
         <v>10</v>
       </c>
-      <c r="O24" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P24" s="95">
+      <c r="O24" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P24" s="123">
         <v>2.63E-2</v>
       </c>
-      <c r="Q24" s="81">
+      <c r="Q24" s="80">
         <f t="shared" si="2"/>
         <v>0.26300000000000001</v>
       </c>
-      <c r="R24" s="44"/>
-      <c r="S24" s="49"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="129"/>
     </row>
     <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -6894,55 +6909,55 @@
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E25" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="F25" s="43" t="s">
         <v>298</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="G25" s="43" t="s">
         <v>299</v>
       </c>
-      <c r="G25" s="44" t="s">
+      <c r="H25" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="H25" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="I25" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J25" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="K25" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L25" s="44">
+      <c r="K25" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L25" s="43">
         <v>1</v>
       </c>
       <c r="M25" s="37">
         <f>L25*5</f>
         <v>5</v>
       </c>
-      <c r="N25" s="90">
+      <c r="N25" s="87">
         <v>20</v>
       </c>
-      <c r="O25" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P25" s="85">
+      <c r="O25" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P25" s="125">
         <v>3.8100000000000002E-2</v>
       </c>
-      <c r="Q25" s="81">
+      <c r="Q25" s="80">
         <f t="shared" si="2"/>
         <v>0.76200000000000001</v>
       </c>
       <c r="R25" s="37"/>
-      <c r="S25" s="49"/>
+      <c r="S25" s="129"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
@@ -6950,7 +6965,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="49" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="37" t="s">
@@ -6974,31 +6989,31 @@
       <c r="J26" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="K26" s="44" t="s">
+      <c r="K26" s="43" t="s">
         <v>267</v>
       </c>
       <c r="L26" s="37">
         <v>2</v>
       </c>
-      <c r="M26" s="44">
+      <c r="M26" s="43">
         <f t="shared" ref="M26" si="10">L26*5</f>
         <v>10</v>
       </c>
-      <c r="N26" s="84">
+      <c r="N26" s="82">
         <v>10</v>
       </c>
-      <c r="O26" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P26" s="95">
+      <c r="O26" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P26" s="123">
         <v>3.2199999999999999E-2</v>
       </c>
-      <c r="Q26" s="81">
+      <c r="Q26" s="80">
         <f t="shared" si="2"/>
         <v>0.32200000000000001</v>
       </c>
-      <c r="R26" s="44"/>
-      <c r="S26" s="49"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="129"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
@@ -7006,55 +7021,55 @@
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="E27" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="44" t="s">
+      <c r="F27" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="44" t="s">
+      <c r="G27" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="I27" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J27" s="44" t="s">
+      <c r="I27" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J27" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="K27" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L27" s="44">
+      <c r="K27" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L27" s="43">
         <v>1</v>
       </c>
       <c r="M27" s="37">
         <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N27" s="90">
+      <c r="N27" s="87">
         <v>20</v>
       </c>
-      <c r="O27" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P27" s="96">
+      <c r="O27" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P27" s="124">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="Q27" s="81">
+      <c r="Q27" s="80">
         <f t="shared" si="2"/>
         <v>0.17799999999999999</v>
       </c>
       <c r="R27" s="37"/>
-      <c r="S27" s="49"/>
+      <c r="S27" s="129"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -7062,45 +7077,52 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="53" t="s">
         <v>302</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="37" t="s">
+      <c r="F28" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="G28" s="53" t="s">
         <v>303</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="L28" s="37">
+      <c r="H28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="J28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="K28" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="L28" s="53">
         <v>1</v>
       </c>
-      <c r="M28" s="44">
+      <c r="M28" s="55">
         <f t="shared" ref="M28" si="11">L28*5</f>
         <v>5</v>
       </c>
-      <c r="N28" s="84">
+      <c r="N28" s="88">
         <v>50</v>
       </c>
-      <c r="O28" s="52"/>
-      <c r="P28" s="95"/>
-      <c r="Q28" s="81">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="44"/>
-      <c r="S28" s="49"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="126" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q28" s="81" t="s">
+        <v>267</v>
+      </c>
+      <c r="R28" s="55"/>
+      <c r="S28" s="134"/>
     </row>
     <row r="29" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
@@ -7108,55 +7130,55 @@
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="44" t="s">
+      <c r="D29" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="E29" s="43" t="s">
         <v>305</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="F29" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="G29" s="43" t="s">
         <v>306</v>
       </c>
-      <c r="F29" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="G29" s="44" t="s">
+      <c r="H29" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="I29" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J29" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="I29" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="K29" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L29" s="44">
+      <c r="K29" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L29" s="43">
         <v>3</v>
       </c>
       <c r="M29" s="37">
         <f>L29*5</f>
         <v>15</v>
       </c>
-      <c r="N29" s="90">
+      <c r="N29" s="87">
         <v>20</v>
       </c>
-      <c r="O29" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P29" s="96">
+      <c r="O29" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P29" s="124">
         <v>2.52E-2</v>
       </c>
-      <c r="Q29" s="81">
+      <c r="Q29" s="80">
         <f t="shared" si="2"/>
         <v>0.504</v>
       </c>
       <c r="R29" s="37"/>
-      <c r="S29" s="49"/>
+      <c r="S29" s="129"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
@@ -7164,7 +7186,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="49" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="37" t="s">
@@ -7188,31 +7210,32 @@
       <c r="J30" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="K30" s="44" t="s">
+      <c r="K30" s="43" t="s">
         <v>267</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
       </c>
-      <c r="M30" s="44">
+      <c r="M30" s="43">
         <f t="shared" ref="M30" si="12">L30*5</f>
         <v>5</v>
       </c>
-      <c r="N30" s="84">
+      <c r="N30" s="82">
         <v>6</v>
       </c>
-      <c r="O30" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P30" s="95">
-        <v>1.4796</v>
-      </c>
-      <c r="Q30" s="81">
-        <f t="shared" si="2"/>
-        <v>8.877600000000001</v>
-      </c>
-      <c r="R30" s="44"/>
-      <c r="S30" s="49"/>
+      <c r="O30" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P30" s="123" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q30" s="80" t="s">
+        <v>267</v>
+      </c>
+      <c r="R30" s="72" t="s">
+        <v>340</v>
+      </c>
+      <c r="S30" s="129"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
@@ -7220,55 +7243,55 @@
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="D31" s="44" t="s">
+      <c r="C31" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="D31" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="44" t="s">
+      <c r="F31" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="G31" s="44" t="s">
+      <c r="G31" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H31" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="I31" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J31" s="44" t="s">
+      <c r="I31" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J31" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="K31" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L31" s="44">
+      <c r="K31" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L31" s="43">
         <v>1</v>
       </c>
       <c r="M31" s="37">
         <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="90">
+      <c r="N31" s="87">
         <v>6</v>
       </c>
-      <c r="O31" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P31" s="96">
+      <c r="O31" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P31" s="124">
         <v>0.9546</v>
       </c>
-      <c r="Q31" s="81">
+      <c r="Q31" s="80">
         <f t="shared" si="2"/>
         <v>5.7275999999999998</v>
       </c>
       <c r="R31" s="37"/>
-      <c r="S31" s="49"/>
+      <c r="S31" s="129"/>
     </row>
     <row r="32" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
@@ -7276,29 +7299,29 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="49" t="s">
+        <v>309</v>
+      </c>
+      <c r="D32" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="E32" s="37" t="s">
         <v>311</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>312</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>268</v>
       </c>
       <c r="G32" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>313</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>314</v>
       </c>
       <c r="K32" s="37" t="s">
         <v>267</v>
@@ -7306,25 +7329,25 @@
       <c r="L32" s="37">
         <v>1</v>
       </c>
-      <c r="M32" s="44">
+      <c r="M32" s="43">
         <f t="shared" ref="M32" si="13">L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="84">
+      <c r="N32" s="82">
         <v>6</v>
       </c>
-      <c r="O32" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P32" s="95">
+      <c r="O32" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P32" s="123">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="Q32" s="81">
+      <c r="Q32" s="80">
         <f t="shared" si="2"/>
         <v>0.22919999999999999</v>
       </c>
-      <c r="R32" s="44"/>
-      <c r="S32" s="49"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="129"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
@@ -7332,55 +7355,55 @@
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D33" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="43" t="s">
         <v>86</v>
       </c>
       <c r="F33" s="37" t="s">
         <v>268</v>
       </c>
-      <c r="G33" s="44" t="s">
+      <c r="G33" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="I33" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J33" s="44" t="s">
+      <c r="I33" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J33" s="43" t="s">
         <v>219</v>
       </c>
-      <c r="K33" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L33" s="44">
+      <c r="K33" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L33" s="43">
         <v>1</v>
       </c>
       <c r="M33" s="37">
         <f>L33*5</f>
         <v>5</v>
       </c>
-      <c r="N33" s="90">
+      <c r="N33" s="87">
         <v>10</v>
       </c>
-      <c r="O33" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P33" s="96">
+      <c r="O33" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P33" s="124">
         <v>0.29110000000000003</v>
       </c>
-      <c r="Q33" s="81">
+      <c r="Q33" s="80">
         <f t="shared" si="2"/>
         <v>2.9110000000000005</v>
       </c>
       <c r="R33" s="37"/>
-      <c r="S33" s="49"/>
+      <c r="S33" s="129"/>
     </row>
     <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
@@ -7388,54 +7411,54 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="54" t="s">
+      <c r="E34" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="54" t="s">
+      <c r="F34" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="G34" s="54" t="s">
+      <c r="G34" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="H34" s="55" t="s">
-        <v>267</v>
-      </c>
-      <c r="I34" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="J34" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="K34" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="L34" s="54">
+      <c r="H34" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="I34" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="J34" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="K34" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="L34" s="53">
         <v>13</v>
       </c>
-      <c r="M34" s="56">
+      <c r="M34" s="55">
         <f t="shared" ref="M34" si="14">L34*5</f>
         <v>65</v>
       </c>
-      <c r="N34" s="91">
+      <c r="N34" s="88">
         <v>6</v>
       </c>
-      <c r="O34" s="54" t="s">
-        <v>267</v>
-      </c>
-      <c r="P34" s="97" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q34" s="82" t="s">
-        <v>267</v>
-      </c>
-      <c r="R34" s="44"/>
-      <c r="S34" s="49"/>
+      <c r="O34" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="P34" s="126" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q34" s="81" t="s">
+        <v>267</v>
+      </c>
+      <c r="R34" s="43"/>
+      <c r="S34" s="129"/>
     </row>
     <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
@@ -7443,55 +7466,55 @@
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="44" t="s">
+      <c r="F35" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="G35" s="44" t="s">
+      <c r="G35" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="H35" s="44" t="s">
+      <c r="H35" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="I35" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J35" s="44" t="s">
+      <c r="I35" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J35" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="K35" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="L35" s="44">
+      <c r="K35" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L35" s="43">
         <v>1</v>
       </c>
       <c r="M35" s="37">
         <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="90">
+      <c r="N35" s="87">
         <v>10</v>
       </c>
-      <c r="O35" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P35" s="96">
+      <c r="O35" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P35" s="124">
         <v>4.6899999999999997E-2</v>
       </c>
-      <c r="Q35" s="81">
+      <c r="Q35" s="80">
         <f t="shared" si="2"/>
         <v>0.46899999999999997</v>
       </c>
-      <c r="R35" s="54"/>
-      <c r="S35" s="58"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="134"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
@@ -7499,7 +7522,7 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="50" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -7523,31 +7546,31 @@
       <c r="J36" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="K36" s="44" t="s">
+      <c r="K36" s="43" t="s">
         <v>267</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
       </c>
-      <c r="M36" s="44">
+      <c r="M36" s="43">
         <f t="shared" ref="M36" si="15">L36*5</f>
         <v>5</v>
       </c>
-      <c r="N36" s="84">
+      <c r="N36" s="82">
         <v>20</v>
       </c>
-      <c r="O36" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P36" s="95">
+      <c r="O36" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P36" s="123">
         <v>3.49E-2</v>
       </c>
-      <c r="Q36" s="81">
+      <c r="Q36" s="80">
         <f t="shared" si="2"/>
         <v>0.69799999999999995</v>
       </c>
-      <c r="R36" s="44"/>
-      <c r="S36" s="49"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="129"/>
     </row>
     <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
@@ -7555,57 +7578,57 @@
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="44" t="s">
-        <v>327</v>
-      </c>
-      <c r="E37" s="44" t="s">
+      <c r="D37" s="43" t="s">
+        <v>326</v>
+      </c>
+      <c r="E37" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F37" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G37" s="44" t="s">
+      <c r="G37" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I37" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J37" s="44" t="s">
+      <c r="I37" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J37" s="43" t="s">
         <v>222</v>
       </c>
-      <c r="K37" s="44" t="s">
+      <c r="K37" s="43" t="s">
         <v>254</v>
       </c>
-      <c r="L37" s="44">
+      <c r="L37" s="43">
         <v>11</v>
       </c>
       <c r="M37" s="37">
         <f>L37*5</f>
         <v>55</v>
       </c>
-      <c r="N37" s="90">
+      <c r="N37" s="87">
         <v>100</v>
       </c>
-      <c r="O37" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P37" s="96">
+      <c r="O37" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P37" s="124">
         <v>1E-3</v>
       </c>
-      <c r="Q37" s="81">
+      <c r="Q37" s="80">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R37" s="73" t="s">
-        <v>295</v>
-      </c>
-      <c r="S37" s="49"/>
+      <c r="R37" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="S37" s="129"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
@@ -7613,55 +7636,55 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="44" t="s">
+      <c r="D38" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E38" s="44" t="s">
+      <c r="E38" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="44" t="s">
+      <c r="F38" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G38" s="44" t="s">
+      <c r="G38" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="H38" s="44" t="s">
+      <c r="H38" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I38" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J38" s="44" t="s">
+      <c r="I38" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J38" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="K38" s="44" t="s">
+      <c r="K38" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="L38" s="44">
+      <c r="L38" s="43">
         <v>3</v>
       </c>
-      <c r="M38" s="44">
+      <c r="M38" s="43">
         <f t="shared" ref="M38" si="16">L38*5</f>
         <v>15</v>
       </c>
-      <c r="N38" s="84">
+      <c r="N38" s="82">
         <v>100</v>
       </c>
-      <c r="O38" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P38" s="96">
+      <c r="O38" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P38" s="124">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q38" s="81">
+      <c r="Q38" s="80">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
-      <c r="R38" s="73"/>
-      <c r="S38" s="49"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="129"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
@@ -7669,55 +7692,55 @@
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="43" t="s">
         <v>323</v>
       </c>
-      <c r="F39" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="G39" s="44" t="s">
+      <c r="H39" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="I39" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J39" s="43" t="s">
         <v>324</v>
       </c>
-      <c r="H39" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J39" s="44" t="s">
+      <c r="K39" s="43" t="s">
         <v>325</v>
       </c>
-      <c r="K39" s="44" t="s">
-        <v>326</v>
-      </c>
-      <c r="L39" s="44">
+      <c r="L39" s="43">
         <v>1</v>
       </c>
       <c r="M39" s="37">
         <f>L39*5</f>
         <v>5</v>
       </c>
-      <c r="N39" s="90">
+      <c r="N39" s="87">
         <v>100</v>
       </c>
-      <c r="O39" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P39" s="95">
+      <c r="O39" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P39" s="123">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q39" s="81">
+      <c r="Q39" s="80">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
       <c r="R39" s="37"/>
-      <c r="S39" s="49"/>
+      <c r="S39" s="129"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
@@ -7725,7 +7748,7 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="37" t="s">
@@ -7755,25 +7778,25 @@
       <c r="L40" s="37">
         <v>2</v>
       </c>
-      <c r="M40" s="44">
+      <c r="M40" s="43">
         <f t="shared" ref="M40" si="17">L40*5</f>
         <v>10</v>
       </c>
-      <c r="N40" s="84">
+      <c r="N40" s="82">
         <v>100</v>
       </c>
-      <c r="O40" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P40" s="95">
+      <c r="O40" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P40" s="123">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q40" s="81">
+      <c r="Q40" s="80">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
-      <c r="R40" s="44"/>
-      <c r="S40" s="49"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="129"/>
     </row>
     <row r="41" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
@@ -7781,55 +7804,55 @@
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="44" t="s">
+      <c r="D41" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="F41" s="44" t="s">
+      <c r="E41" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="F41" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="G41" s="56" t="s">
+      <c r="G41" s="55" t="s">
         <v>289</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I41" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="J41" s="44" t="s">
-        <v>328</v>
-      </c>
-      <c r="K41" s="44" t="s">
+      <c r="I41" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="J41" s="43" t="s">
+        <v>327</v>
+      </c>
+      <c r="K41" s="43" t="s">
         <v>257</v>
       </c>
-      <c r="L41" s="44">
+      <c r="L41" s="43">
         <v>1</v>
       </c>
       <c r="M41" s="37">
         <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="90">
+      <c r="N41" s="87">
         <v>50</v>
       </c>
-      <c r="O41" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P41" s="96">
+      <c r="O41" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P41" s="124">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q41" s="81">
+      <c r="Q41" s="80">
         <f t="shared" si="2"/>
         <v>0.27499999999999997</v>
       </c>
       <c r="R41" s="37"/>
-      <c r="S41" s="49"/>
+      <c r="S41" s="129"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
@@ -7837,7 +7860,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="37" t="s">
@@ -7871,21 +7894,21 @@
         <f>L42*5</f>
         <v>25</v>
       </c>
-      <c r="N42" s="90">
+      <c r="N42" s="87">
         <v>100</v>
       </c>
-      <c r="O42" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P42" s="95">
+      <c r="O42" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P42" s="123">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q42" s="81">
+      <c r="Q42" s="80">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
       <c r="R42" s="37"/>
-      <c r="S42" s="49"/>
+      <c r="S42" s="129"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
@@ -7893,55 +7916,55 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="44" t="s">
+      <c r="D43" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E43" s="44" t="s">
+      <c r="E43" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="44" t="s">
+      <c r="F43" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G43" s="44" t="s">
+      <c r="G43" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="H43" s="44" t="s">
+      <c r="H43" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I43" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J43" s="44" t="s">
+      <c r="I43" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J43" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="K43" s="44" t="s">
+      <c r="K43" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="L43" s="44">
+      <c r="L43" s="43">
         <v>2</v>
       </c>
-      <c r="M43" s="44">
+      <c r="M43" s="43">
         <f t="shared" ref="M43" si="18">L43*5</f>
         <v>10</v>
       </c>
-      <c r="N43" s="84">
+      <c r="N43" s="82">
         <v>100</v>
       </c>
-      <c r="O43" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P43" s="96">
+      <c r="O43" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P43" s="124">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="Q43" s="81">
+      <c r="Q43" s="80">
         <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
-      <c r="R43" s="44"/>
-      <c r="S43" s="49"/>
+      <c r="R43" s="43"/>
+      <c r="S43" s="129"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
@@ -7949,7 +7972,7 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="50" t="s">
+      <c r="C44" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="37" t="s">
@@ -7983,21 +8006,21 @@
         <f>L44*5</f>
         <v>15</v>
       </c>
-      <c r="N44" s="90">
+      <c r="N44" s="87">
         <v>100</v>
       </c>
-      <c r="O44" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P44" s="95">
+      <c r="O44" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P44" s="123">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q44" s="81">
+      <c r="Q44" s="80">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
       <c r="R44" s="37"/>
-      <c r="S44" s="49"/>
+      <c r="S44" s="129"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
@@ -8005,55 +8028,55 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D45" s="44" t="s">
+      <c r="D45" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="44" t="s">
+      <c r="E45" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="F45" s="44" t="s">
+      <c r="F45" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G45" s="44" t="s">
+      <c r="G45" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I45" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J45" s="44" t="s">
+      <c r="I45" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J45" s="43" t="s">
         <v>227</v>
       </c>
-      <c r="K45" s="44" t="s">
+      <c r="K45" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="L45" s="44">
+      <c r="L45" s="43">
         <v>2</v>
       </c>
-      <c r="M45" s="44">
+      <c r="M45" s="43">
         <f t="shared" ref="M45" si="19">L45*5</f>
         <v>10</v>
       </c>
-      <c r="N45" s="84">
+      <c r="N45" s="82">
         <v>100</v>
       </c>
-      <c r="O45" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P45" s="96">
+      <c r="O45" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P45" s="124">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q45" s="81">
+      <c r="Q45" s="80">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="R45" s="44"/>
-      <c r="S45" s="49"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="129"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
@@ -8061,7 +8084,7 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="37" t="s">
@@ -8095,21 +8118,21 @@
         <f>L46*5</f>
         <v>10</v>
       </c>
-      <c r="N46" s="90">
+      <c r="N46" s="87">
         <v>100</v>
       </c>
-      <c r="O46" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P46" s="95">
+      <c r="O46" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P46" s="123">
         <v>1.8E-3</v>
       </c>
-      <c r="Q46" s="81">
+      <c r="Q46" s="80">
         <f t="shared" si="2"/>
         <v>0.18</v>
       </c>
       <c r="R46" s="37"/>
-      <c r="S46" s="49"/>
+      <c r="S46" s="129"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
@@ -8117,55 +8140,55 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="44" t="s">
+      <c r="E47" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="F47" s="44" t="s">
+      <c r="F47" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G47" s="44" t="s">
+      <c r="G47" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="H47" s="44" t="s">
+      <c r="H47" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="I47" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J47" s="44" t="s">
+      <c r="I47" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J47" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="K47" s="44" t="s">
+      <c r="K47" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="L47" s="44">
+      <c r="L47" s="43">
         <v>1</v>
       </c>
-      <c r="M47" s="44">
+      <c r="M47" s="43">
         <f t="shared" ref="M47" si="20">L47*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="84">
+      <c r="N47" s="82">
         <v>20</v>
       </c>
-      <c r="O47" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P47" s="96">
+      <c r="O47" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P47" s="124">
         <v>2.75E-2</v>
       </c>
-      <c r="Q47" s="81">
+      <c r="Q47" s="80">
         <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="R47" s="44"/>
-      <c r="S47" s="49"/>
+      <c r="R47" s="43"/>
+      <c r="S47" s="129"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
@@ -8173,7 +8196,7 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="C48" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="37" t="s">
@@ -8207,21 +8230,21 @@
         <f>L48*5</f>
         <v>5</v>
       </c>
-      <c r="N48" s="90">
+      <c r="N48" s="87">
         <v>50</v>
       </c>
-      <c r="O48" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P48" s="95">
+      <c r="O48" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P48" s="123">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="Q48" s="81">
+      <c r="Q48" s="80">
         <f t="shared" si="2"/>
         <v>0.44</v>
       </c>
       <c r="R48" s="37"/>
-      <c r="S48" s="49"/>
+      <c r="S48" s="129"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
@@ -8229,54 +8252,54 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="D49" s="54" t="s">
-        <v>315</v>
-      </c>
-      <c r="E49" s="54" t="s">
+      <c r="D49" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="E49" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="F49" s="54" t="s">
+      <c r="F49" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="G49" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="H49" s="55" t="s">
-        <v>267</v>
-      </c>
-      <c r="I49" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="J49" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="K49" s="54" t="s">
-        <v>267</v>
-      </c>
-      <c r="L49" s="54">
+      <c r="G49" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="H49" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="I49" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="J49" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="K49" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="L49" s="53">
         <v>6</v>
       </c>
-      <c r="M49" s="44">
+      <c r="M49" s="43">
         <f t="shared" ref="M49" si="21">L49*5</f>
         <v>30</v>
       </c>
-      <c r="N49" s="84">
+      <c r="N49" s="82">
         <v>20</v>
       </c>
-      <c r="O49" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="P49" s="97" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q49" s="81" t="s">
-        <v>267</v>
-      </c>
-      <c r="R49" s="44"/>
-      <c r="S49" s="49"/>
+      <c r="O49" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="P49" s="126" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q49" s="80" t="s">
+        <v>267</v>
+      </c>
+      <c r="R49" s="43"/>
+      <c r="S49" s="129"/>
     </row>
     <row r="50" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
@@ -8284,55 +8307,55 @@
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="51" t="s">
+      <c r="C50" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="44" t="s">
-        <v>316</v>
-      </c>
-      <c r="E50" s="44" t="s">
-        <v>345</v>
-      </c>
-      <c r="F50" s="44" t="s">
+      <c r="D50" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="F50" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="G50" s="44" t="s">
-        <v>344</v>
-      </c>
-      <c r="H50" s="44" t="s">
+      <c r="G50" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="H50" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="I50" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J50" s="44" t="s">
-        <v>343</v>
+      <c r="I50" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J50" s="43" t="s">
+        <v>342</v>
       </c>
       <c r="K50" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L50" s="44">
+      <c r="L50" s="43">
         <v>2</v>
       </c>
       <c r="M50" s="37">
         <f>L50*5</f>
         <v>10</v>
       </c>
-      <c r="N50" s="90">
+      <c r="N50" s="87">
         <v>20</v>
       </c>
-      <c r="O50" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P50" s="45">
+      <c r="O50" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P50" s="94">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="Q50" s="81">
+      <c r="Q50" s="80">
         <f t="shared" si="2"/>
         <v>0.39200000000000002</v>
       </c>
       <c r="R50" s="37"/>
-      <c r="S50" s="49"/>
+      <c r="S50" s="129"/>
     </row>
     <row r="51" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
@@ -8340,29 +8363,29 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="51" t="s">
+      <c r="C51" s="50" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>317</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>318</v>
       </c>
       <c r="F51" s="37" t="s">
         <v>268</v>
       </c>
       <c r="G51" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="H51" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="I51" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>320</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>321</v>
       </c>
       <c r="K51" s="37" t="s">
         <v>267</v>
@@ -8370,25 +8393,25 @@
       <c r="L51" s="37">
         <v>1</v>
       </c>
-      <c r="M51" s="44">
+      <c r="M51" s="43">
         <f t="shared" ref="M51" si="22">L51*5</f>
         <v>5</v>
       </c>
-      <c r="N51" s="84">
+      <c r="N51" s="82">
         <v>6</v>
       </c>
-      <c r="O51" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P51" s="98">
+      <c r="O51" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P51" s="127">
         <v>0.42799999999999999</v>
       </c>
-      <c r="Q51" s="81">
+      <c r="Q51" s="80">
         <f t="shared" si="2"/>
         <v>2.5680000000000001</v>
       </c>
-      <c r="R51" s="44"/>
-      <c r="S51" s="49"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="129"/>
     </row>
     <row r="52" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
@@ -8396,55 +8419,55 @@
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="51" t="s">
+      <c r="C52" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="43" t="s">
         <v>266</v>
       </c>
-      <c r="E52" s="44" t="s">
+      <c r="E52" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="F52" s="44" t="s">
-        <v>346</v>
-      </c>
-      <c r="G52" s="44" t="s">
+      <c r="F52" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="G52" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="H52" s="44" t="s">
+      <c r="H52" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="I52" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J52" s="44" t="s">
+      <c r="I52" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J52" s="43" t="s">
         <v>235</v>
       </c>
       <c r="K52" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L52" s="44">
+      <c r="L52" s="43">
         <v>1</v>
       </c>
       <c r="M52" s="37">
         <f>L52*5</f>
         <v>5</v>
       </c>
-      <c r="N52" s="90">
+      <c r="N52" s="87">
         <v>10</v>
       </c>
-      <c r="O52" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P52" s="96">
+      <c r="O52" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P52" s="124">
         <v>6.2100000000000002E-2</v>
       </c>
-      <c r="Q52" s="81">
+      <c r="Q52" s="80">
         <f t="shared" si="2"/>
         <v>0.621</v>
       </c>
       <c r="R52" s="37"/>
-      <c r="S52" s="49"/>
+      <c r="S52" s="129"/>
     </row>
     <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
@@ -8452,7 +8475,7 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="37" t="s">
@@ -8482,25 +8505,25 @@
       <c r="L53" s="37">
         <v>1</v>
       </c>
-      <c r="M53" s="44">
+      <c r="M53" s="43">
         <f t="shared" ref="M53" si="23">L53*5</f>
         <v>5</v>
       </c>
-      <c r="N53" s="84">
+      <c r="N53" s="82">
         <v>6</v>
       </c>
-      <c r="O53" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P53" s="95">
+      <c r="O53" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P53" s="123">
         <v>0.16209999999999999</v>
       </c>
-      <c r="Q53" s="81">
+      <c r="Q53" s="80">
         <f t="shared" si="2"/>
         <v>0.97259999999999991</v>
       </c>
-      <c r="R53" s="44"/>
-      <c r="S53" s="49"/>
+      <c r="R53" s="43"/>
+      <c r="S53" s="129"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
@@ -8508,55 +8531,55 @@
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="51" t="s">
+      <c r="C54" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="D54" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="E54" s="44" t="s">
+      <c r="E54" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="F54" s="44" t="s">
+      <c r="F54" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="G54" s="44" t="s">
+      <c r="G54" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="H54" s="44" t="s">
+      <c r="H54" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="I54" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J54" s="44" t="s">
+      <c r="I54" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J54" s="43" t="s">
         <v>287</v>
       </c>
       <c r="K54" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L54" s="44">
+      <c r="L54" s="43">
         <v>1</v>
       </c>
       <c r="M54" s="37">
         <f>L54*5</f>
         <v>5</v>
       </c>
-      <c r="N54" s="84">
+      <c r="N54" s="82">
         <v>10</v>
       </c>
-      <c r="O54" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P54" s="96">
+      <c r="O54" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P54" s="124">
         <v>0.1341</v>
       </c>
-      <c r="Q54" s="81">
+      <c r="Q54" s="80">
         <f t="shared" si="2"/>
         <v>1.341</v>
       </c>
-      <c r="R54" s="54"/>
-      <c r="S54" s="58"/>
+      <c r="R54" s="53"/>
+      <c r="S54" s="134"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
@@ -8564,7 +8587,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="49" t="s">
         <v>16</v>
       </c>
       <c r="D55" s="37" t="s">
@@ -8594,25 +8617,25 @@
       <c r="L55" s="37">
         <v>1</v>
       </c>
-      <c r="M55" s="44">
+      <c r="M55" s="43">
         <f t="shared" ref="M55" si="24">L55*5</f>
         <v>5</v>
       </c>
-      <c r="N55" s="84">
+      <c r="N55" s="82">
         <v>10</v>
       </c>
-      <c r="O55" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P55" s="95">
+      <c r="O55" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P55" s="123">
         <v>0.19539999999999999</v>
       </c>
-      <c r="Q55" s="81">
+      <c r="Q55" s="80">
         <f t="shared" si="2"/>
         <v>1.954</v>
       </c>
-      <c r="R55" s="44"/>
-      <c r="S55" s="49"/>
+      <c r="R55" s="43"/>
+      <c r="S55" s="129"/>
     </row>
     <row r="56" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
@@ -8620,55 +8643,55 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="51" t="s">
+      <c r="C56" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="E56" s="44" t="s">
+      <c r="E56" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="F56" s="44" t="s">
+      <c r="F56" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="G56" s="44" t="s">
+      <c r="G56" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="H56" s="44" t="s">
+      <c r="H56" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="I56" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J56" s="44" t="s">
+      <c r="I56" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J56" s="43" t="s">
         <v>233</v>
       </c>
       <c r="K56" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L56" s="44">
+      <c r="L56" s="43">
         <v>1</v>
       </c>
-      <c r="M56" s="44">
+      <c r="M56" s="43">
         <f t="shared" ref="M56" si="25">L56*5</f>
         <v>5</v>
       </c>
-      <c r="N56" s="84">
+      <c r="N56" s="82">
         <v>6</v>
       </c>
-      <c r="O56" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P56" s="96">
+      <c r="O56" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P56" s="124">
         <v>0.43909999999999999</v>
       </c>
-      <c r="Q56" s="81">
+      <c r="Q56" s="80">
         <f t="shared" si="2"/>
         <v>2.6345999999999998</v>
       </c>
-      <c r="R56" s="44"/>
-      <c r="S56" s="49"/>
+      <c r="R56" s="43"/>
+      <c r="S56" s="129"/>
     </row>
     <row r="57" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
@@ -8676,7 +8699,7 @@
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="37" t="s">
@@ -8710,21 +8733,21 @@
         <f>L57*5</f>
         <v>5</v>
       </c>
-      <c r="N57" s="90">
+      <c r="N57" s="87">
         <v>10</v>
       </c>
-      <c r="O57" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P57" s="95">
+      <c r="O57" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P57" s="123">
         <v>0.15479999999999999</v>
       </c>
-      <c r="Q57" s="81">
+      <c r="Q57" s="80">
         <f t="shared" si="2"/>
         <v>1.548</v>
       </c>
       <c r="R57" s="37"/>
-      <c r="S57" s="49"/>
+      <c r="S57" s="129"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
@@ -8732,7 +8755,7 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="50" t="s">
+      <c r="C58" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="37" t="s">
@@ -8762,25 +8785,25 @@
       <c r="L58" s="37">
         <v>1</v>
       </c>
-      <c r="M58" s="44">
+      <c r="M58" s="43">
         <f t="shared" ref="M58" si="26">L58*5</f>
         <v>5</v>
       </c>
-      <c r="N58" s="84">
+      <c r="N58" s="82">
         <v>6</v>
       </c>
-      <c r="O58" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P58" s="95">
+      <c r="O58" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P58" s="123">
         <v>5.1212</v>
       </c>
-      <c r="Q58" s="81">
+      <c r="Q58" s="80">
         <f t="shared" si="2"/>
         <v>30.7272</v>
       </c>
-      <c r="R58" s="44"/>
-      <c r="S58" s="49"/>
+      <c r="R58" s="43"/>
+      <c r="S58" s="129"/>
     </row>
     <row r="59" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
@@ -8788,55 +8811,55 @@
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="51" t="s">
+      <c r="C59" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="44" t="s">
+      <c r="D59" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="E59" s="44" t="s">
+      <c r="E59" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="44" t="s">
+      <c r="F59" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="G59" s="44" t="s">
+      <c r="G59" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="H59" s="44" t="s">
+      <c r="H59" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="I59" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J59" s="44" t="s">
+      <c r="I59" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J59" s="43" t="s">
         <v>237</v>
       </c>
       <c r="K59" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L59" s="44">
+      <c r="L59" s="43">
         <v>1</v>
       </c>
       <c r="M59" s="37">
         <f>L59*5</f>
         <v>5</v>
       </c>
-      <c r="N59" s="90">
+      <c r="N59" s="87">
         <v>10</v>
       </c>
-      <c r="O59" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P59" s="96">
+      <c r="O59" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P59" s="124">
         <v>0.15670000000000001</v>
       </c>
-      <c r="Q59" s="81">
+      <c r="Q59" s="80">
         <f t="shared" si="2"/>
         <v>1.5670000000000002</v>
       </c>
       <c r="R59" s="37"/>
-      <c r="S59" s="49"/>
+      <c r="S59" s="129"/>
     </row>
     <row r="60" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
@@ -8844,7 +8867,7 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="C60" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="37" t="s">
@@ -8874,25 +8897,25 @@
       <c r="L60" s="37">
         <v>1</v>
       </c>
-      <c r="M60" s="44">
+      <c r="M60" s="43">
         <f t="shared" ref="M60" si="27">L60*5</f>
         <v>5</v>
       </c>
-      <c r="N60" s="84">
+      <c r="N60" s="82">
         <v>6</v>
       </c>
-      <c r="O60" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P60" s="95">
+      <c r="O60" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P60" s="123">
         <v>0.96889999999999998</v>
       </c>
-      <c r="Q60" s="81">
+      <c r="Q60" s="80">
         <f t="shared" si="2"/>
         <v>5.8133999999999997</v>
       </c>
-      <c r="R60" s="44"/>
-      <c r="S60" s="49"/>
+      <c r="R60" s="43"/>
+      <c r="S60" s="129"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
@@ -8900,55 +8923,55 @@
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="51" t="s">
+      <c r="C61" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E61" s="44" t="s">
+      <c r="E61" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="F61" s="44" t="s">
+      <c r="F61" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="G61" s="44" t="s">
+      <c r="G61" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="H61" s="44" t="s">
+      <c r="H61" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="I61" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="J61" s="44" t="s">
+      <c r="I61" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="J61" s="43" t="s">
         <v>239</v>
       </c>
       <c r="K61" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L61" s="44">
+      <c r="L61" s="43">
         <v>1</v>
       </c>
       <c r="M61" s="37">
         <f>L61*5</f>
         <v>5</v>
       </c>
-      <c r="N61" s="90">
+      <c r="N61" s="87">
         <v>6</v>
       </c>
-      <c r="O61" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="P61" s="96">
+      <c r="O61" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="P61" s="124">
         <v>0.28870000000000001</v>
       </c>
-      <c r="Q61" s="81">
+      <c r="Q61" s="80">
         <f t="shared" si="2"/>
         <v>1.7322000000000002</v>
       </c>
       <c r="R61" s="37"/>
-      <c r="S61" s="49"/>
+      <c r="S61" s="129"/>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
@@ -8956,7 +8979,7 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="50" t="s">
+      <c r="C62" s="49" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="37" t="s">
@@ -8990,21 +9013,21 @@
         <f>L62*5</f>
         <v>5</v>
       </c>
-      <c r="N62" s="90">
+      <c r="N62" s="87">
         <v>6</v>
       </c>
-      <c r="O62" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="P62" s="95">
+      <c r="O62" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="P62" s="123">
         <v>2.0651000000000002</v>
       </c>
-      <c r="Q62" s="81">
+      <c r="Q62" s="80">
         <f t="shared" si="2"/>
         <v>12.390600000000001</v>
       </c>
       <c r="R62" s="37"/>
-      <c r="S62" s="49"/>
+      <c r="S62" s="129"/>
     </row>
     <row r="63" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
@@ -9012,55 +9035,55 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="60" t="s">
+      <c r="C63" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="49" t="s">
+      <c r="D63" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="E63" s="49" t="s">
+      <c r="E63" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="F63" s="49" t="s">
+      <c r="F63" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="G63" s="49" t="s">
+      <c r="G63" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="H63" s="49" t="s">
+      <c r="H63" s="48" t="s">
         <v>201</v>
       </c>
-      <c r="I63" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J63" s="49" t="s">
+      <c r="I63" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J63" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="K63" s="61" t="s">
-        <v>267</v>
-      </c>
-      <c r="L63" s="49">
+      <c r="K63" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="L63" s="48">
         <v>1</v>
       </c>
-      <c r="M63" s="49">
+      <c r="M63" s="48">
         <f t="shared" ref="M63:M67" si="28">L63*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="92">
+      <c r="N63" s="89">
         <v>6</v>
       </c>
-      <c r="O63" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="P63" s="99">
+      <c r="O63" s="61" t="s">
+        <v>281</v>
+      </c>
+      <c r="P63" s="128">
         <v>1.2919</v>
       </c>
-      <c r="Q63" s="86">
+      <c r="Q63" s="84">
         <f t="shared" si="2"/>
         <v>7.7514000000000003</v>
       </c>
-      <c r="R63" s="49"/>
-      <c r="S63" s="49"/>
+      <c r="R63" s="48"/>
+      <c r="S63" s="129"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
@@ -9068,54 +9091,54 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="60" t="s">
-        <v>329</v>
-      </c>
-      <c r="D64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="F64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="H64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="I64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="K64" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="L64" s="49">
+      <c r="C64" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="D64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="F64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="H64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K64" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="L64" s="48">
         <v>1</v>
       </c>
-      <c r="M64" s="49">
+      <c r="M64" s="48">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N64" s="93" t="s">
-        <v>267</v>
-      </c>
-      <c r="O64" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="P64" s="100" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q64" s="87" t="s">
-        <v>267</v>
-      </c>
-      <c r="R64" s="83"/>
-      <c r="S64" s="83"/>
+      <c r="N64" s="90" t="s">
+        <v>267</v>
+      </c>
+      <c r="O64" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="P64" s="124" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q64" s="131" t="s">
+        <v>267</v>
+      </c>
+      <c r="R64" s="43"/>
+      <c r="S64" s="130"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
@@ -9123,54 +9146,54 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>330</v>
-      </c>
-      <c r="D65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="F65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="H65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="I65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="K65" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="L65" s="49">
+      <c r="C65" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="D65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="H65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K65" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="L65" s="48">
         <v>1</v>
       </c>
-      <c r="M65" s="49">
+      <c r="M65" s="48">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N65" s="90" t="s">
-        <v>267</v>
-      </c>
-      <c r="O65" s="52" t="s">
-        <v>267</v>
-      </c>
-      <c r="P65" s="95" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q65" s="81" t="s">
+      <c r="N65" s="87" t="s">
+        <v>267</v>
+      </c>
+      <c r="O65" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="P65" s="123" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q65" s="80" t="s">
         <v>267</v>
       </c>
       <c r="R65" s="37"/>
-      <c r="S65" s="49"/>
+      <c r="S65" s="129"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
@@ -9178,54 +9201,54 @@
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="60" t="s">
-        <v>336</v>
-      </c>
-      <c r="D66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="F66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="H66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="I66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="K66" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="L66" s="49">
+      <c r="C66" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K66" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="L66" s="48">
         <v>1</v>
       </c>
-      <c r="M66" s="49">
+      <c r="M66" s="48">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N66" s="90" t="s">
-        <v>267</v>
-      </c>
-      <c r="O66" s="52" t="s">
-        <v>267</v>
-      </c>
-      <c r="P66" s="95" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q66" s="81" t="s">
+      <c r="N66" s="87" t="s">
+        <v>267</v>
+      </c>
+      <c r="O66" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="P66" s="123" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q66" s="80" t="s">
         <v>267</v>
       </c>
       <c r="R66" s="37"/>
-      <c r="S66" s="49"/>
+      <c r="S66" s="129"/>
     </row>
     <row r="67" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
@@ -9233,81 +9256,81 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="60" t="s">
+      <c r="C67" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="D67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="D67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="E67" s="49" t="s">
+      <c r="F67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="G67" s="48" t="s">
         <v>332</v>
       </c>
-      <c r="F67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="G67" s="49" t="s">
+      <c r="H67" s="48" t="s">
         <v>333</v>
       </c>
-      <c r="H67" s="49" t="s">
+      <c r="I67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J67" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="I67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="J67" s="49" t="s">
-        <v>335</v>
-      </c>
-      <c r="K67" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="L67" s="49">
+      <c r="K67" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="L67" s="48">
         <v>1</v>
       </c>
-      <c r="M67" s="49">
+      <c r="M67" s="48">
         <f t="shared" si="28"/>
         <v>5</v>
       </c>
-      <c r="N67" s="90">
+      <c r="N67" s="87">
         <v>6</v>
       </c>
-      <c r="O67" s="101" t="s">
-        <v>281</v>
-      </c>
-      <c r="P67" s="95">
+      <c r="O67" s="92" t="s">
+        <v>281</v>
+      </c>
+      <c r="P67" s="123">
         <v>0.1202</v>
       </c>
-      <c r="Q67" s="81">
+      <c r="Q67" s="132">
         <f>P67*N67</f>
         <v>0.72120000000000006</v>
       </c>
-      <c r="R67" s="37"/>
-      <c r="S67" s="49"/>
+      <c r="R67" s="135"/>
+      <c r="S67" s="129"/>
     </row>
     <row r="68" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
-      <c r="B68" s="64"/>
-      <c r="C68" s="65"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="69"/>
-      <c r="H68" s="68"/>
-      <c r="I68" s="69"/>
-      <c r="J68" s="68"/>
-      <c r="K68" s="69"/>
-      <c r="L68" s="69"/>
-      <c r="M68" s="69"/>
-      <c r="N68" s="106" t="s">
+      <c r="B68" s="63"/>
+      <c r="C68" s="64"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="68"/>
+      <c r="H68" s="67"/>
+      <c r="I68" s="68"/>
+      <c r="J68" s="67"/>
+      <c r="K68" s="68"/>
+      <c r="L68" s="68"/>
+      <c r="M68" s="68"/>
+      <c r="N68" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="O68" s="107"/>
-      <c r="P68" s="107"/>
+      <c r="O68" s="114"/>
+      <c r="P68" s="114"/>
       <c r="Q68" s="41">
         <f>SUM(Q10:Q67)</f>
-        <v>124.12300000000002</v>
-      </c>
-      <c r="R68" s="110"/>
-      <c r="S68" s="111"/>
+        <v>115.24540000000002</v>
+      </c>
+      <c r="R68" s="117"/>
+      <c r="S68" s="118"/>
     </row>
     <row r="69" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -9323,20 +9346,20 @@
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
       <c r="M69" s="10"/>
-      <c r="N69" s="106" t="s">
+      <c r="N69" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="O69" s="107"/>
-      <c r="P69" s="107"/>
+      <c r="O69" s="114"/>
+      <c r="P69" s="114"/>
       <c r="Q69" s="42">
         <f>Q68/5</f>
-        <v>24.824600000000004</v>
-      </c>
-      <c r="R69" s="112"/>
-      <c r="S69" s="113"/>
+        <v>23.049080000000004</v>
+      </c>
+      <c r="R69" s="119"/>
+      <c r="S69" s="120"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P70" s="74"/>
+      <c r="P70" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
